--- a/data/TTC/班別時間對照表/TTC_TD_當月班別時間對照表.xlsx
+++ b/data/TTC/班別時間對照表/TTC_TD_當月班別時間對照表.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1415" uniqueCount="558">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1580" uniqueCount="571">
   <si>
     <t>班別代號</t>
   </si>
@@ -349,9 +349,6 @@
     <t>CD0811</t>
   </si>
   <si>
-    <t>CD0812</t>
-  </si>
-  <si>
     <t>CD0851</t>
   </si>
   <si>
@@ -373,31 +370,31 @@
     <t>CD5905</t>
   </si>
   <si>
-    <t>CD5906</t>
-  </si>
-  <si>
     <t>DS</t>
   </si>
   <si>
+    <t>DSUI</t>
+  </si>
+  <si>
     <t>DTT</t>
   </si>
   <si>
     <t>DTT1</t>
   </si>
   <si>
+    <t>FAC</t>
+  </si>
+  <si>
     <t>LUTS</t>
   </si>
   <si>
     <t>M</t>
   </si>
   <si>
-    <t>MT2</t>
-  </si>
-  <si>
     <t>NGRSD</t>
   </si>
   <si>
-    <t>OGC3</t>
+    <t>OGC4</t>
   </si>
   <si>
     <t>OGT3</t>
@@ -421,31 +418,28 @@
     <t>TOWN</t>
   </si>
   <si>
-    <t>TRN</t>
-  </si>
-  <si>
     <t>TTC1</t>
   </si>
   <si>
     <t>WRSL</t>
   </si>
   <si>
-    <t>3:57</t>
-  </si>
-  <si>
     <t>3:59</t>
   </si>
   <si>
     <t>4:53</t>
   </si>
   <si>
+    <t>4:10</t>
+  </si>
+  <si>
+    <t>4:11</t>
+  </si>
+  <si>
     <t>4:15</t>
   </si>
   <si>
-    <t>4:14</t>
-  </si>
-  <si>
-    <t>4:10</t>
+    <t>6:49</t>
   </si>
   <si>
     <t>4:50</t>
@@ -454,1240 +448,1285 @@
     <t>5:02</t>
   </si>
   <si>
+    <t>4:34</t>
+  </si>
+  <si>
+    <t>5:09</t>
+  </si>
+  <si>
+    <t>6:53</t>
+  </si>
+  <si>
+    <t>11:06</t>
+  </si>
+  <si>
+    <t>5:22</t>
+  </si>
+  <si>
+    <t>6:03</t>
+  </si>
+  <si>
+    <t>6:09</t>
+  </si>
+  <si>
+    <t>7:59</t>
+  </si>
+  <si>
+    <t>4:31</t>
+  </si>
+  <si>
+    <t>6:35</t>
+  </si>
+  <si>
+    <t>7:08</t>
+  </si>
+  <si>
+    <t>8:45</t>
+  </si>
+  <si>
+    <t>8:59</t>
+  </si>
+  <si>
+    <t>10:59</t>
+  </si>
+  <si>
+    <t>11:16</t>
+  </si>
+  <si>
+    <t>11:53</t>
+  </si>
+  <si>
+    <t>11:45</t>
+  </si>
+  <si>
+    <t>11:48</t>
+  </si>
+  <si>
+    <t>9:33</t>
+  </si>
+  <si>
+    <t>9:36</t>
+  </si>
+  <si>
+    <t>11:59</t>
+  </si>
+  <si>
+    <t>4:04</t>
+  </si>
+  <si>
+    <t>4:24</t>
+  </si>
+  <si>
+    <t>10:53</t>
+  </si>
+  <si>
+    <t>10:04</t>
+  </si>
+  <si>
+    <t>5:58</t>
+  </si>
+  <si>
     <t>6:59</t>
   </si>
   <si>
+    <t>4:41</t>
+  </si>
+  <si>
     <t>4:47</t>
   </si>
   <si>
-    <t>5:09</t>
+    <t>10:00</t>
+  </si>
+  <si>
+    <t>10:35</t>
+  </si>
+  <si>
+    <t>10:13</t>
+  </si>
+  <si>
+    <t>4:52</t>
+  </si>
+  <si>
+    <t>5:57</t>
+  </si>
+  <si>
+    <t>12:00</t>
+  </si>
+  <si>
+    <t>12:22</t>
+  </si>
+  <si>
+    <t>15:58</t>
+  </si>
+  <si>
+    <t>12:59</t>
+  </si>
+  <si>
+    <t>13:04</t>
+  </si>
+  <si>
+    <t>12:04</t>
+  </si>
+  <si>
+    <t>13:03</t>
+  </si>
+  <si>
+    <t>13:16</t>
+  </si>
+  <si>
+    <t>13:15</t>
+  </si>
+  <si>
+    <t>13:53</t>
+  </si>
+  <si>
+    <t>14:08</t>
+  </si>
+  <si>
+    <t>14:48</t>
+  </si>
+  <si>
+    <t>14:56</t>
+  </si>
+  <si>
+    <t>15:04</t>
+  </si>
+  <si>
+    <t>16:46</t>
+  </si>
+  <si>
+    <t>14:59</t>
+  </si>
+  <si>
+    <t>15:39</t>
+  </si>
+  <si>
+    <t>16:21</t>
+  </si>
+  <si>
+    <t>12:53</t>
+  </si>
+  <si>
+    <t>13:25</t>
+  </si>
+  <si>
+    <t>14:04</t>
+  </si>
+  <si>
+    <t>15:03</t>
+  </si>
+  <si>
+    <t>15:25</t>
+  </si>
+  <si>
+    <t>15:48</t>
+  </si>
+  <si>
+    <t>17:35</t>
+  </si>
+  <si>
+    <t>15:51</t>
+  </si>
+  <si>
+    <t>15:59</t>
+  </si>
+  <si>
+    <t>13:06</t>
+  </si>
+  <si>
+    <t>16:04</t>
+  </si>
+  <si>
+    <t>17:11</t>
+  </si>
+  <si>
+    <t>16:07</t>
+  </si>
+  <si>
+    <t>17:12</t>
+  </si>
+  <si>
+    <t>16:13</t>
+  </si>
+  <si>
+    <t>16:50</t>
+  </si>
+  <si>
+    <t>16:28</t>
+  </si>
+  <si>
+    <t>16:48</t>
+  </si>
+  <si>
+    <t>16:53</t>
+  </si>
+  <si>
+    <t>14:25</t>
+  </si>
+  <si>
+    <t>17:02</t>
+  </si>
+  <si>
+    <t>17:04</t>
+  </si>
+  <si>
+    <t>17:08</t>
+  </si>
+  <si>
+    <t>15:35</t>
+  </si>
+  <si>
+    <t>17:45</t>
+  </si>
+  <si>
+    <t>17:55</t>
+  </si>
+  <si>
+    <t>12:12</t>
+  </si>
+  <si>
+    <t>16:22</t>
+  </si>
+  <si>
+    <t>17:26</t>
+  </si>
+  <si>
+    <t>12:01</t>
+  </si>
+  <si>
+    <t>12:28</t>
+  </si>
+  <si>
+    <t>16:25</t>
+  </si>
+  <si>
+    <t>14:00</t>
+  </si>
+  <si>
+    <t>14:55</t>
+  </si>
+  <si>
+    <t>15:00</t>
+  </si>
+  <si>
+    <t>14:37</t>
+  </si>
+  <si>
+    <t>14:28</t>
+  </si>
+  <si>
+    <t>15:01</t>
+  </si>
+  <si>
+    <t>15:12</t>
+  </si>
+  <si>
+    <t>15:21</t>
+  </si>
+  <si>
+    <t>17:25</t>
+  </si>
+  <si>
+    <t>17:30</t>
+  </si>
+  <si>
+    <t>15:23</t>
+  </si>
+  <si>
+    <t>15:45</t>
+  </si>
+  <si>
+    <t>16:45</t>
+  </si>
+  <si>
+    <t>15:37</t>
+  </si>
+  <si>
+    <t>16:05</t>
+  </si>
+  <si>
+    <t>15:41</t>
+  </si>
+  <si>
+    <t>16:52</t>
+  </si>
+  <si>
+    <t>17:00</t>
+  </si>
+  <si>
+    <t>17:01</t>
+  </si>
+  <si>
+    <t>16:58</t>
+  </si>
+  <si>
+    <t>17:27</t>
+  </si>
+  <si>
+    <t>5:28</t>
+  </si>
+  <si>
+    <t>8:53</t>
+  </si>
+  <si>
+    <t>9:22</t>
+  </si>
+  <si>
+    <t>9:59</t>
+  </si>
+  <si>
+    <t>11:25</t>
+  </si>
+  <si>
+    <t>12:41</t>
+  </si>
+  <si>
+    <t>12:50</t>
+  </si>
+  <si>
+    <t>6:37</t>
+  </si>
+  <si>
+    <t>10:07</t>
+  </si>
+  <si>
+    <t>15:07</t>
+  </si>
+  <si>
+    <t>10:32</t>
+  </si>
+  <si>
+    <t>11:07</t>
+  </si>
+  <si>
+    <t>15:53</t>
+  </si>
+  <si>
+    <t>11:21</t>
+  </si>
+  <si>
+    <t>16:08</t>
+  </si>
+  <si>
+    <t>12:56</t>
+  </si>
+  <si>
+    <t>17:22</t>
+  </si>
+  <si>
+    <t>8:30</t>
+  </si>
+  <si>
+    <t>8:00</t>
+  </si>
+  <si>
+    <t>21:30</t>
+  </si>
+  <si>
+    <t>7:30</t>
+  </si>
+  <si>
+    <t>4:00</t>
+  </si>
+  <si>
+    <t>15:30</t>
+  </si>
+  <si>
+    <t>13:00</t>
+  </si>
+  <si>
+    <t>13:35</t>
+  </si>
+  <si>
+    <t>13:40</t>
+  </si>
+  <si>
+    <t>12:40</t>
+  </si>
+  <si>
+    <t>12:45</t>
+  </si>
+  <si>
+    <t>12:35</t>
+  </si>
+  <si>
+    <t>12:37</t>
+  </si>
+  <si>
+    <t>13:14</t>
+  </si>
+  <si>
+    <t>12:10</t>
+  </si>
+  <si>
+    <t>12:51</t>
+  </si>
+  <si>
+    <t>12:47</t>
+  </si>
+  <si>
+    <t>14:49</t>
+  </si>
+  <si>
+    <t>12:54</t>
+  </si>
+  <si>
+    <t>14:35</t>
+  </si>
+  <si>
+    <t>13:52</t>
+  </si>
+  <si>
+    <t>12:34</t>
+  </si>
+  <si>
+    <t>14:53</t>
+  </si>
+  <si>
+    <t>21:04</t>
+  </si>
+  <si>
+    <t>13:54</t>
+  </si>
+  <si>
+    <t>14:54</t>
+  </si>
+  <si>
+    <t>12:15</t>
+  </si>
+  <si>
+    <t>14:03</t>
+  </si>
+  <si>
+    <t>14:45</t>
+  </si>
+  <si>
+    <t>17:37</t>
+  </si>
+  <si>
+    <t>13:34</t>
+  </si>
+  <si>
+    <t>12:32</t>
+  </si>
+  <si>
+    <t>16:31</t>
+  </si>
+  <si>
+    <t>17:32</t>
+  </si>
+  <si>
+    <t>18:59</t>
+  </si>
+  <si>
+    <t>20:04</t>
+  </si>
+  <si>
+    <t>20:17</t>
+  </si>
+  <si>
+    <t>20:01</t>
+  </si>
+  <si>
+    <t>19:45</t>
+  </si>
+  <si>
+    <t>20:27</t>
+  </si>
+  <si>
+    <t>21:41</t>
+  </si>
+  <si>
+    <t>20:48</t>
+  </si>
+  <si>
+    <t>19:48</t>
+  </si>
+  <si>
+    <t>17:33</t>
+  </si>
+  <si>
+    <t>21:03</t>
+  </si>
+  <si>
+    <t>18:00</t>
+  </si>
+  <si>
+    <t>20:59</t>
+  </si>
+  <si>
+    <t>13:20</t>
+  </si>
+  <si>
+    <t>12:24</t>
+  </si>
+  <si>
+    <t>18:53</t>
+  </si>
+  <si>
+    <t>18:04</t>
+  </si>
+  <si>
+    <t>13:58</t>
+  </si>
+  <si>
+    <t>16:23</t>
+  </si>
+  <si>
+    <t>13:59</t>
+  </si>
+  <si>
+    <t>14:43</t>
+  </si>
+  <si>
+    <t>14:32</t>
+  </si>
+  <si>
+    <t>13:22</t>
+  </si>
+  <si>
+    <t>13:45</t>
+  </si>
+  <si>
+    <t>13:47</t>
+  </si>
+  <si>
+    <t>15:08</t>
+  </si>
+  <si>
+    <t>14:09</t>
+  </si>
+  <si>
+    <t>19:55</t>
+  </si>
+  <si>
+    <t>18:54</t>
+  </si>
+  <si>
+    <t>19:18</t>
+  </si>
+  <si>
+    <t>19:53</t>
+  </si>
+  <si>
+    <t>12:03</t>
+  </si>
+  <si>
+    <t>12:52</t>
+  </si>
+  <si>
+    <t>16:43</t>
+  </si>
+  <si>
+    <t>20:00</t>
+  </si>
+  <si>
+    <t>20:41</t>
+  </si>
+  <si>
+    <t>25:30</t>
+  </si>
+  <si>
+    <t>22:03</t>
+  </si>
+  <si>
+    <t>22:22</t>
+  </si>
+  <si>
+    <t>21:15</t>
+  </si>
+  <si>
+    <t>22:08</t>
+  </si>
+  <si>
+    <t>23:01</t>
+  </si>
+  <si>
+    <t>23:03</t>
+  </si>
+  <si>
+    <t>22:56</t>
+  </si>
+  <si>
+    <t>23:46</t>
+  </si>
+  <si>
+    <t>24:46</t>
+  </si>
+  <si>
+    <t>24:21</t>
+  </si>
+  <si>
+    <t>22:04</t>
+  </si>
+  <si>
+    <t>24:32</t>
+  </si>
+  <si>
+    <t>23:51</t>
+  </si>
+  <si>
+    <t>25:01</t>
+  </si>
+  <si>
+    <t>24:30</t>
+  </si>
+  <si>
+    <t>25:35</t>
+  </si>
+  <si>
+    <t>24:50</t>
+  </si>
+  <si>
+    <t>21:06</t>
+  </si>
+  <si>
+    <t>25:11</t>
+  </si>
+  <si>
+    <t>25:25</t>
+  </si>
+  <si>
+    <t>23:41</t>
+  </si>
+  <si>
+    <t>25:02</t>
+  </si>
+  <si>
+    <t>25:13</t>
+  </si>
+  <si>
+    <t>25:20</t>
+  </si>
+  <si>
+    <t>23:35</t>
+  </si>
+  <si>
+    <t>25:45</t>
+  </si>
+  <si>
+    <t>25:55</t>
+  </si>
+  <si>
+    <t>24:22</t>
+  </si>
+  <si>
+    <t>24:51</t>
+  </si>
+  <si>
+    <t>22:30</t>
+  </si>
+  <si>
+    <t>22:55</t>
+  </si>
+  <si>
+    <t>22:37</t>
+  </si>
+  <si>
+    <t>23:27</t>
+  </si>
+  <si>
+    <t>23:23</t>
+  </si>
+  <si>
+    <t>25:00</t>
+  </si>
+  <si>
+    <t>24:52</t>
+  </si>
+  <si>
+    <t>25:07</t>
+  </si>
+  <si>
+    <t>13:28</t>
+  </si>
+  <si>
+    <t>15:06</t>
+  </si>
+  <si>
+    <t>17:03</t>
+  </si>
+  <si>
+    <t>17:40</t>
+  </si>
+  <si>
+    <t>17:59</t>
+  </si>
+  <si>
+    <t>19:32</t>
+  </si>
+  <si>
+    <t>21:28</t>
+  </si>
+  <si>
+    <t>15:15</t>
+  </si>
+  <si>
+    <t>16:06</t>
+  </si>
+  <si>
+    <t>19:04</t>
+  </si>
+  <si>
+    <t>19:03</t>
+  </si>
+  <si>
+    <t>19:17</t>
+  </si>
+  <si>
+    <t>19:08</t>
+  </si>
+  <si>
+    <t>24:28</t>
+  </si>
+  <si>
+    <t>19:40</t>
+  </si>
+  <si>
+    <t>20:03</t>
+  </si>
+  <si>
+    <t>25:50</t>
+  </si>
+  <si>
+    <t>20:56</t>
+  </si>
+  <si>
+    <t>16:00</t>
+  </si>
+  <si>
+    <t>31:30</t>
+  </si>
+  <si>
+    <t>23:30</t>
+  </si>
+  <si>
+    <t>16:30</t>
+  </si>
+  <si>
+    <t>21:00</t>
+  </si>
+  <si>
+    <t>9:41</t>
+  </si>
+  <si>
+    <t>8:41</t>
+  </si>
+  <si>
+    <t>8:46</t>
+  </si>
+  <si>
+    <t>8:36</t>
+  </si>
+  <si>
+    <t>8:38</t>
+  </si>
+  <si>
+    <t>9:15</t>
   </si>
   <si>
     <t>8:40</t>
   </si>
   <si>
+    <t>8:37</t>
+  </si>
+  <si>
+    <t>8:32</t>
+  </si>
+  <si>
+    <t>8:49</t>
+  </si>
+  <si>
+    <t>8:44</t>
+  </si>
+  <si>
+    <t>8:04</t>
+  </si>
+  <si>
+    <t>9:45</t>
+  </si>
+  <si>
+    <t>9:42</t>
+  </si>
+  <si>
+    <t>9:06</t>
+  </si>
+  <si>
+    <t>8:26</t>
+  </si>
+  <si>
+    <t>9:58</t>
+  </si>
+  <si>
+    <t>9:32</t>
+  </si>
+  <si>
+    <t>8:05</t>
+  </si>
+  <si>
+    <t>9:38</t>
+  </si>
+  <si>
+    <t>9:03</t>
+  </si>
+  <si>
+    <t>8:24</t>
+  </si>
+  <si>
     <t>8:22</t>
   </si>
   <si>
-    <t>5:22</t>
-  </si>
-  <si>
-    <t>6:03</t>
-  </si>
-  <si>
-    <t>7:59</t>
-  </si>
-  <si>
-    <t>5:59</t>
-  </si>
-  <si>
-    <t>6:09</t>
-  </si>
-  <si>
-    <t>4:29</t>
-  </si>
-  <si>
-    <t>7:08</t>
-  </si>
-  <si>
-    <t>7:36</t>
-  </si>
-  <si>
-    <t>8:45</t>
-  </si>
-  <si>
-    <t>10:59</t>
-  </si>
-  <si>
-    <t>11:03</t>
-  </si>
-  <si>
-    <t>11:16</t>
-  </si>
-  <si>
-    <t>11:45</t>
-  </si>
-  <si>
-    <t>11:48</t>
+    <t>9:23</t>
+  </si>
+  <si>
+    <t>9:20</t>
+  </si>
+  <si>
+    <t>8:33</t>
+  </si>
+  <si>
+    <t>9:05</t>
+  </si>
+  <si>
+    <t>9:01</t>
+  </si>
+  <si>
+    <t>8:42</t>
+  </si>
+  <si>
+    <t>8:16</t>
+  </si>
+  <si>
+    <t>9:53</t>
+  </si>
+  <si>
+    <t>9:00</t>
+  </si>
+  <si>
+    <t>8:29</t>
+  </si>
+  <si>
+    <t>9:56</t>
+  </si>
+  <si>
+    <t>8:52</t>
+  </si>
+  <si>
+    <t>9:21</t>
+  </si>
+  <si>
+    <t>8:55</t>
+  </si>
+  <si>
+    <t>9:24</t>
+  </si>
+  <si>
+    <t>8:23</t>
+  </si>
+  <si>
+    <t>8:13</t>
+  </si>
+  <si>
+    <t>9:13</t>
+  </si>
+  <si>
+    <t>9:07</t>
+  </si>
+  <si>
+    <t>9:12</t>
+  </si>
+  <si>
+    <t>8:18</t>
+  </si>
+  <si>
+    <t>8:25</t>
+  </si>
+  <si>
+    <t>8:12</t>
+  </si>
+  <si>
+    <t>8:19</t>
+  </si>
+  <si>
+    <t>9:55</t>
+  </si>
+  <si>
+    <t>9:02</t>
+  </si>
+  <si>
+    <t>8:57</t>
+  </si>
+  <si>
+    <t>9:54</t>
+  </si>
+  <si>
+    <t>9:04</t>
+  </si>
+  <si>
+    <t>8:10</t>
+  </si>
+  <si>
+    <t>8:15</t>
+  </si>
+  <si>
+    <t>8:03</t>
+  </si>
+  <si>
+    <t>8:51</t>
+  </si>
+  <si>
+    <t>9:18</t>
+  </si>
+  <si>
+    <t>8:17</t>
+  </si>
+  <si>
+    <t>9:16</t>
+  </si>
+  <si>
+    <t>8:07</t>
+  </si>
+  <si>
+    <t>8:08</t>
+  </si>
+  <si>
+    <t>8:35</t>
+  </si>
+  <si>
+    <t>8:31</t>
+  </si>
+  <si>
+    <t>9:30</t>
+  </si>
+  <si>
+    <t>8:21</t>
+  </si>
+  <si>
+    <t>8:28</t>
+  </si>
+  <si>
+    <t>9:37</t>
+  </si>
+  <si>
+    <t>8:27</t>
+  </si>
+  <si>
+    <t>8:43</t>
+  </si>
+  <si>
+    <t>8:34</t>
+  </si>
+  <si>
+    <t>8:11</t>
+  </si>
+  <si>
+    <t>8:20</t>
+  </si>
+  <si>
+    <t>8:09</t>
+  </si>
+  <si>
+    <t>8:56</t>
+  </si>
+  <si>
+    <t>8:14</t>
+  </si>
+  <si>
+    <t>8:01</t>
   </si>
   <si>
     <t>9:28</t>
   </si>
   <si>
-    <t>12:50</t>
-  </si>
-  <si>
-    <t>9:25</t>
-  </si>
-  <si>
-    <t>11:59</t>
-  </si>
-  <si>
-    <t>4:24</t>
-  </si>
-  <si>
-    <t>11:04</t>
-  </si>
-  <si>
-    <t>10:32</t>
-  </si>
-  <si>
-    <t>4:41</t>
-  </si>
-  <si>
-    <t>5:18</t>
-  </si>
-  <si>
-    <t>6:13</t>
-  </si>
-  <si>
-    <t>6:49</t>
-  </si>
-  <si>
-    <t>10:00</t>
-  </si>
-  <si>
-    <t>10:21</t>
-  </si>
-  <si>
-    <t>10:35</t>
-  </si>
-  <si>
-    <t>11:53</t>
-  </si>
-  <si>
-    <t>12:00</t>
-  </si>
-  <si>
-    <t>15:07</t>
-  </si>
-  <si>
-    <t>4:52</t>
-  </si>
-  <si>
-    <t>10:26</t>
-  </si>
-  <si>
-    <t>12:22</t>
-  </si>
-  <si>
-    <t>12:59</t>
-  </si>
-  <si>
-    <t>13:23</t>
-  </si>
-  <si>
-    <t>13:03</t>
-  </si>
-  <si>
-    <t>13:08</t>
-  </si>
-  <si>
-    <t>13:16</t>
-  </si>
-  <si>
-    <t>13:06</t>
-  </si>
-  <si>
-    <t>13:53</t>
-  </si>
-  <si>
-    <t>14:08</t>
-  </si>
-  <si>
-    <t>15:50</t>
-  </si>
-  <si>
-    <t>17:53</t>
-  </si>
-  <si>
-    <t>14:56</t>
-  </si>
-  <si>
-    <t>14:59</t>
-  </si>
-  <si>
-    <t>16:21</t>
-  </si>
-  <si>
-    <t>16:27</t>
-  </si>
-  <si>
-    <t>16:53</t>
-  </si>
-  <si>
-    <t>12:06</t>
-  </si>
-  <si>
-    <t>15:03</t>
-  </si>
-  <si>
-    <t>13:21</t>
-  </si>
-  <si>
-    <t>15:48</t>
-  </si>
-  <si>
-    <t>17:08</t>
-  </si>
-  <si>
-    <t>15:51</t>
-  </si>
-  <si>
-    <t>15:58</t>
-  </si>
-  <si>
-    <t>15:59</t>
-  </si>
-  <si>
-    <t>16:04</t>
-  </si>
-  <si>
-    <t>16:07</t>
-  </si>
-  <si>
-    <t>16:08</t>
-  </si>
-  <si>
-    <t>16:13</t>
-  </si>
-  <si>
-    <t>16:28</t>
-  </si>
-  <si>
-    <t>16:09</t>
-  </si>
-  <si>
-    <t>14:48</t>
-  </si>
-  <si>
-    <t>17:04</t>
-  </si>
-  <si>
-    <t>17:27</t>
-  </si>
-  <si>
-    <t>17:13</t>
-  </si>
-  <si>
-    <t>17:11</t>
-  </si>
-  <si>
-    <t>17:12</t>
-  </si>
-  <si>
-    <t>17:35</t>
-  </si>
-  <si>
-    <t>17:45</t>
-  </si>
-  <si>
-    <t>13:42</t>
-  </si>
-  <si>
-    <t>12:12</t>
-  </si>
-  <si>
-    <t>15:01</t>
-  </si>
-  <si>
-    <t>17:52</t>
-  </si>
-  <si>
-    <t>12:03</t>
-  </si>
-  <si>
-    <t>12:28</t>
-  </si>
-  <si>
-    <t>16:33</t>
-  </si>
-  <si>
-    <t>18:21</t>
-  </si>
-  <si>
-    <t>14:00</t>
-  </si>
-  <si>
-    <t>14:55</t>
-  </si>
-  <si>
-    <t>16:41</t>
-  </si>
-  <si>
-    <t>13:33</t>
-  </si>
-  <si>
-    <t>12:36</t>
-  </si>
-  <si>
-    <t>15:00</t>
-  </si>
-  <si>
-    <t>15:41</t>
-  </si>
-  <si>
-    <t>15:08</t>
-  </si>
-  <si>
-    <t>15:12</t>
-  </si>
-  <si>
-    <t>17:02</t>
-  </si>
-  <si>
-    <t>15:21</t>
-  </si>
-  <si>
-    <t>15:37</t>
-  </si>
-  <si>
-    <t>17:25</t>
-  </si>
-  <si>
-    <t>17:30</t>
-  </si>
-  <si>
-    <t>15:53</t>
-  </si>
-  <si>
-    <t>15:45</t>
-  </si>
-  <si>
-    <t>16:36</t>
-  </si>
-  <si>
-    <t>16:05</t>
-  </si>
-  <si>
-    <t>16:25</t>
-  </si>
-  <si>
-    <t>16:48</t>
-  </si>
-  <si>
-    <t>17:00</t>
-  </si>
-  <si>
-    <t>16:58</t>
-  </si>
-  <si>
-    <t>16:35</t>
-  </si>
-  <si>
-    <t>12:33</t>
-  </si>
-  <si>
-    <t>8:33</t>
-  </si>
-  <si>
-    <t>9:22</t>
-  </si>
-  <si>
-    <t>9:53</t>
-  </si>
-  <si>
-    <t>12:26</t>
-  </si>
-  <si>
-    <t>6:29</t>
-  </si>
-  <si>
     <t>9:27</t>
   </si>
   <si>
-    <t>9:33</t>
-  </si>
-  <si>
-    <t>12:04</t>
-  </si>
-  <si>
-    <t>5:27</t>
-  </si>
-  <si>
-    <t>9:45</t>
-  </si>
-  <si>
-    <t>10:25</t>
-  </si>
-  <si>
-    <t>10:27</t>
-  </si>
-  <si>
-    <t>8:25</t>
-  </si>
-  <si>
-    <t>11:47</t>
-  </si>
-  <si>
-    <t>12:25</t>
-  </si>
-  <si>
-    <t>12:41</t>
-  </si>
-  <si>
-    <t>14:09</t>
-  </si>
-  <si>
-    <t>13:28</t>
-  </si>
-  <si>
-    <t>16:37</t>
-  </si>
-  <si>
-    <t>14:32</t>
-  </si>
-  <si>
-    <t>18:12</t>
-  </si>
-  <si>
-    <t>8:30</t>
-  </si>
-  <si>
-    <t>8:00</t>
-  </si>
-  <si>
-    <t>9:00</t>
-  </si>
-  <si>
-    <t>7:30</t>
-  </si>
-  <si>
-    <t>4:00</t>
-  </si>
-  <si>
-    <t>15:30</t>
-  </si>
-  <si>
-    <t>11:00</t>
-  </si>
-  <si>
-    <t>13:40</t>
-  </si>
-  <si>
-    <t>11:57</t>
-  </si>
-  <si>
-    <t>13:54</t>
-  </si>
-  <si>
-    <t>12:40</t>
-  </si>
-  <si>
-    <t>13:00</t>
-  </si>
-  <si>
-    <t>12:35</t>
-  </si>
-  <si>
-    <t>13:14</t>
-  </si>
-  <si>
-    <t>12:37</t>
-  </si>
-  <si>
-    <t>12:53</t>
-  </si>
-  <si>
-    <t>12:51</t>
-  </si>
-  <si>
-    <t>12:39</t>
-  </si>
-  <si>
-    <t>12:47</t>
-  </si>
-  <si>
-    <t>12:15</t>
-  </si>
-  <si>
-    <t>12:54</t>
-  </si>
-  <si>
-    <t>14:35</t>
-  </si>
-  <si>
-    <t>15:06</t>
-  </si>
-  <si>
-    <t>16:40</t>
-  </si>
-  <si>
-    <t>13:35</t>
-  </si>
-  <si>
-    <t>14:54</t>
-  </si>
-  <si>
-    <t>14:03</t>
-  </si>
-  <si>
-    <t>17:40</t>
-  </si>
-  <si>
-    <t>15:35</t>
-  </si>
-  <si>
-    <t>14:20</t>
-  </si>
-  <si>
-    <t>14:45</t>
-  </si>
-  <si>
-    <t>13:34</t>
-  </si>
-  <si>
-    <t>16:31</t>
-  </si>
-  <si>
-    <t>17:06</t>
-  </si>
-  <si>
-    <t>16:45</t>
-  </si>
-  <si>
-    <t>18:59</t>
-  </si>
-  <si>
-    <t>19:54</t>
-  </si>
-  <si>
-    <t>20:17</t>
-  </si>
-  <si>
-    <t>19:45</t>
-  </si>
-  <si>
-    <t>21:41</t>
-  </si>
-  <si>
-    <t>21:28</t>
-  </si>
-  <si>
-    <t>20:27</t>
-  </si>
-  <si>
-    <t>20:43</t>
-  </si>
-  <si>
-    <t>18:51</t>
-  </si>
-  <si>
-    <t>21:03</t>
-  </si>
-  <si>
-    <t>22:33</t>
-  </si>
-  <si>
-    <t>20:59</t>
-  </si>
-  <si>
-    <t>12:32</t>
-  </si>
-  <si>
-    <t>14:06</t>
-  </si>
-  <si>
-    <t>19:04</t>
-  </si>
-  <si>
-    <t>13:20</t>
-  </si>
-  <si>
-    <t>13:15</t>
-  </si>
-  <si>
-    <t>18:47</t>
-  </si>
-  <si>
-    <t>13:59</t>
-  </si>
-  <si>
-    <t>12:10</t>
-  </si>
-  <si>
-    <t>13:22</t>
-  </si>
-  <si>
-    <t>14:37</t>
-  </si>
-  <si>
-    <t>14:49</t>
-  </si>
-  <si>
-    <t>19:55</t>
-  </si>
-  <si>
-    <t>20:08</t>
-  </si>
-  <si>
-    <t>18:37</t>
-  </si>
-  <si>
-    <t>18:54</t>
-  </si>
-  <si>
-    <t>19:53</t>
-  </si>
-  <si>
-    <t>20:00</t>
-  </si>
-  <si>
-    <t>23:18</t>
-  </si>
-  <si>
-    <t>12:43</t>
-  </si>
-  <si>
-    <t>13:47</t>
-  </si>
-  <si>
-    <t>13:13</t>
-  </si>
-  <si>
-    <t>12:52</t>
-  </si>
-  <si>
-    <t>13:04</t>
-  </si>
-  <si>
-    <t>18:41</t>
-  </si>
-  <si>
-    <t>20:05</t>
-  </si>
-  <si>
-    <t>20:41</t>
-  </si>
-  <si>
-    <t>21:04</t>
-  </si>
-  <si>
-    <t>22:08</t>
-  </si>
-  <si>
-    <t>22:22</t>
-  </si>
-  <si>
-    <t>21:06</t>
-  </si>
-  <si>
-    <t>22:03</t>
-  </si>
-  <si>
-    <t>24:50</t>
-  </si>
-  <si>
-    <t>26:32</t>
-  </si>
-  <si>
-    <t>22:56</t>
-  </si>
-  <si>
-    <t>24:21</t>
-  </si>
-  <si>
-    <t>25:25</t>
-  </si>
-  <si>
-    <t>25:30</t>
-  </si>
-  <si>
-    <t>20:09</t>
-  </si>
-  <si>
-    <t>23:03</t>
-  </si>
-  <si>
-    <t>23:51</t>
-  </si>
-  <si>
-    <t>24:30</t>
-  </si>
-  <si>
-    <t>25:55</t>
-  </si>
-  <si>
-    <t>24:56</t>
-  </si>
-  <si>
-    <t>25:11</t>
-  </si>
-  <si>
-    <t>23:01</t>
-  </si>
-  <si>
-    <t>25:52</t>
-  </si>
-  <si>
-    <t>25:13</t>
-  </si>
-  <si>
-    <t>25:20</t>
-  </si>
-  <si>
-    <t>25:35</t>
-  </si>
-  <si>
-    <t>25:45</t>
-  </si>
-  <si>
-    <t>21:42</t>
-  </si>
-  <si>
-    <t>20:03</t>
-  </si>
-  <si>
-    <t>22:00</t>
-  </si>
-  <si>
-    <t>22:45</t>
-  </si>
-  <si>
-    <t>22:55</t>
-  </si>
-  <si>
-    <t>23:27</t>
-  </si>
-  <si>
-    <t>24:04</t>
-  </si>
-  <si>
-    <t>22:35</t>
-  </si>
-  <si>
-    <t>24:25</t>
-  </si>
-  <si>
-    <t>25:02</t>
-  </si>
-  <si>
-    <t>23:37</t>
-  </si>
-  <si>
-    <t>25:07</t>
-  </si>
-  <si>
-    <t>25:00</t>
-  </si>
-  <si>
-    <t>24:51</t>
-  </si>
-  <si>
-    <t>24:35</t>
-  </si>
-  <si>
-    <t>18:40</t>
-  </si>
-  <si>
-    <t>20:26</t>
-  </si>
-  <si>
-    <t>24:29</t>
-  </si>
-  <si>
-    <t>19:22</t>
-  </si>
-  <si>
-    <t>21:11</t>
-  </si>
-  <si>
-    <t>13:27</t>
-  </si>
-  <si>
-    <t>18:15</t>
-  </si>
-  <si>
-    <t>18:28</t>
-  </si>
-  <si>
-    <t>20:04</t>
-  </si>
-  <si>
-    <t>22:17</t>
-  </si>
-  <si>
-    <t>23:39</t>
-  </si>
-  <si>
-    <t>21:55</t>
-  </si>
-  <si>
-    <t>21:35</t>
-  </si>
-  <si>
-    <t>25:32</t>
-  </si>
-  <si>
-    <t>23:23</t>
-  </si>
-  <si>
-    <t>26:12</t>
-  </si>
-  <si>
-    <t>16:00</t>
-  </si>
-  <si>
-    <t>18:00</t>
-  </si>
-  <si>
-    <t>23:30</t>
-  </si>
-  <si>
-    <t>16:30</t>
-  </si>
-  <si>
-    <t>19:00</t>
-  </si>
-  <si>
-    <t>9:43</t>
-  </si>
-  <si>
-    <t>9:41</t>
-  </si>
-  <si>
-    <t>9:55</t>
-  </si>
-  <si>
-    <t>8:41</t>
-  </si>
-  <si>
-    <t>9:01</t>
-  </si>
-  <si>
-    <t>8:36</t>
-  </si>
-  <si>
-    <t>9:15</t>
-  </si>
-  <si>
-    <t>8:38</t>
-  </si>
-  <si>
-    <t>8:32</t>
-  </si>
-  <si>
-    <t>8:18</t>
-  </si>
-  <si>
-    <t>8:49</t>
-  </si>
-  <si>
-    <t>8:44</t>
-  </si>
-  <si>
-    <t>8:39</t>
-  </si>
-  <si>
-    <t>8:04</t>
-  </si>
-  <si>
-    <t>9:06</t>
-  </si>
-  <si>
-    <t>8:07</t>
-  </si>
-  <si>
-    <t>9:21</t>
-  </si>
-  <si>
-    <t>8:59</t>
-  </si>
-  <si>
-    <t>8:26</t>
-  </si>
-  <si>
-    <t>9:34</t>
-  </si>
-  <si>
-    <t>9:32</t>
-  </si>
-  <si>
-    <t>9:36</t>
-  </si>
-  <si>
-    <t>8:11</t>
-  </si>
-  <si>
-    <t>9:19</t>
-  </si>
-  <si>
-    <t>9:05</t>
-  </si>
-  <si>
-    <t>9:23</t>
-  </si>
-  <si>
-    <t>9:30</t>
-  </si>
-  <si>
-    <t>8:51</t>
-  </si>
-  <si>
-    <t>9:56</t>
-  </si>
-  <si>
-    <t>8:42</t>
-  </si>
-  <si>
-    <t>8:29</t>
-  </si>
-  <si>
-    <t>8:55</t>
-  </si>
-  <si>
-    <t>8:35</t>
-  </si>
-  <si>
-    <t>9:52</t>
-  </si>
-  <si>
-    <t>8:15</t>
-  </si>
-  <si>
-    <t>8:13</t>
-  </si>
-  <si>
-    <t>9:51</t>
-  </si>
-  <si>
-    <t>9:07</t>
-  </si>
-  <si>
-    <t>9:12</t>
-  </si>
-  <si>
-    <t>9:42</t>
-  </si>
-  <si>
-    <t>9:48</t>
-  </si>
-  <si>
-    <t>8:12</t>
-  </si>
-  <si>
-    <t>8:24</t>
-  </si>
-  <si>
-    <t>8:54</t>
-  </si>
-  <si>
-    <t>9:47</t>
-  </si>
-  <si>
-    <t>8:37</t>
-  </si>
-  <si>
-    <t>8:19</t>
-  </si>
-  <si>
-    <t>9:16</t>
-  </si>
-  <si>
-    <t>9:39</t>
-  </si>
-  <si>
-    <t>8:05</t>
-  </si>
-  <si>
-    <t>9:14</t>
-  </si>
-  <si>
-    <t>8:10</t>
-  </si>
-  <si>
-    <t>8:58</t>
-  </si>
-  <si>
-    <t>8:03</t>
-  </si>
-  <si>
-    <t>9:02</t>
-  </si>
-  <si>
-    <t>8:47</t>
-  </si>
-  <si>
-    <t>8:52</t>
-  </si>
-  <si>
-    <t>9:31</t>
-  </si>
-  <si>
-    <t>9:18</t>
-  </si>
-  <si>
-    <t>8:17</t>
-  </si>
-  <si>
-    <t>8:57</t>
-  </si>
-  <si>
-    <t>8:08</t>
-  </si>
-  <si>
-    <t>9:54</t>
-  </si>
-  <si>
-    <t>8:23</t>
-  </si>
-  <si>
-    <t>9:59</t>
-  </si>
-  <si>
-    <t>9:17</t>
-  </si>
-  <si>
-    <t>9:37</t>
-  </si>
-  <si>
-    <t>9:20</t>
-  </si>
-  <si>
-    <t>8:34</t>
-  </si>
-  <si>
-    <t>8:27</t>
-  </si>
-  <si>
-    <t>8:48</t>
-  </si>
-  <si>
-    <t>9:35</t>
-  </si>
-  <si>
-    <t>9:13</t>
-  </si>
-  <si>
-    <t>9:49</t>
-  </si>
-  <si>
-    <t>8:02</t>
-  </si>
-  <si>
-    <t>9/9(WED)</t>
-  </si>
-  <si>
-    <t>9/15(TUE), 9/16(WED), 9/22(TUE), 9/23(WED), 9/29(TUE), 9/30(WED), 9/8(TUE)</t>
-  </si>
-  <si>
-    <t>9/15(TUE), 9/16(WED), 9/22(TUE), 9/23(WED), 9/30(WED), 9/8(TUE)</t>
-  </si>
-  <si>
-    <t>9/29(TUE)</t>
-  </si>
-  <si>
-    <t>10/1(THU), 10/2(FRI), 9/10(THU), 9/11(FRI), 9/17(THU), 9/18(FRI), 9/24(THU)</t>
-  </si>
-  <si>
-    <t>9/25(FRI)</t>
-  </si>
-  <si>
-    <t>9/14(MON), 9/21(MON), 9/28(MON), 9/7(MON)</t>
-  </si>
-  <si>
-    <t>9/13(SUN), 9/14(MON), 9/20(SUN), 9/21(MON), 9/28(MON), 9/6(SUN), 9/7(MON)</t>
-  </si>
-  <si>
-    <t>9/27(SUN)</t>
-  </si>
-  <si>
-    <t>9/11(FRI), 9/25(FRI)</t>
-  </si>
-  <si>
-    <t>10/2(FRI), 9/18(FRI)</t>
-  </si>
-  <si>
-    <t>10/3(SAT), 9/12(SAT), 9/19(SAT), 9/26(SAT)</t>
-  </si>
-  <si>
-    <t>9/15(TUE), 9/16(WED), 9/22(TUE), 9/23(WED), 9/30(WED), 9/8(TUE), 9/9(WED)</t>
-  </si>
-  <si>
-    <t>9/24(THU)</t>
-  </si>
-  <si>
-    <t>10/1(THU), 10/3(SAT), 9/10(THU), 9/12(SAT), 9/13(SUN), 9/17(THU), 9/19(SAT), 9/20(SUN), 9/27(SUN), 9/6(SUN)</t>
-  </si>
-  <si>
-    <t>9/26(SAT)</t>
-  </si>
-  <si>
-    <t>9/7(MON)</t>
-  </si>
-  <si>
-    <t>9/14(MON), 9/21(MON), 9/28(MON)</t>
-  </si>
-  <si>
-    <t>10/2(FRI), 9/11(FRI), 9/18(FRI)</t>
-  </si>
-  <si>
-    <t>9/13(SUN), 9/20(SUN), 9/27(SUN), 9/6(SUN)</t>
-  </si>
-  <si>
-    <t>9/14(MON), 9/21(MON), 9/7(MON)</t>
-  </si>
-  <si>
-    <t>9/28(MON)</t>
-  </si>
-  <si>
-    <t>9/8(TUE)</t>
-  </si>
-  <si>
-    <t>9/15(TUE), 9/16(WED), 9/22(TUE), 9/23(WED), 9/30(WED)</t>
-  </si>
-  <si>
-    <t>10/1(THU), 9/17(THU)</t>
-  </si>
-  <si>
-    <t>9/10(THU)</t>
-  </si>
-  <si>
-    <t>10/1(THU), 9/10(THU), 9/17(THU), 9/24(THU)</t>
-  </si>
-  <si>
-    <t>9/14(MON), 9/21(MON)</t>
-  </si>
-  <si>
-    <t>10/3(SAT), 9/12(SAT), 9/19(SAT)</t>
-  </si>
-  <si>
-    <t>9/13(SUN), 9/20(SUN), 9/6(SUN)</t>
-  </si>
-  <si>
-    <t>10/2(FRI), 9/11(FRI), 9/18(FRI), 9/25(FRI)</t>
-  </si>
-  <si>
-    <t>9/17(THU), 9/24(THU)</t>
-  </si>
-  <si>
-    <t>10/1(THU), 9/10(THU), 9/17(THU)</t>
-  </si>
-  <si>
-    <t>9/10(THU), 9/13(SUN), 9/15(TUE), 9/16(WED), 9/20(SUN), 9/22(TUE), 9/23(WED), 9/24(THU), 9/30(WED), 9/6(SUN), 9/8(TUE)</t>
-  </si>
-  <si>
-    <t>9/27(SUN), 9/29(TUE)</t>
-  </si>
-  <si>
-    <t>10/1(THU), 10/2(FRI), 9/10(THU), 9/11(FRI), 9/14(MON), 9/17(THU), 9/18(FRI), 9/21(MON), 9/24(THU), 9/25(FRI), 9/28(MON), 9/7(MON)</t>
-  </si>
-  <si>
-    <t>9/13(SUN), 9/15(TUE), 9/16(WED), 9/20(SUN), 9/22(TUE), 9/23(WED), 9/30(WED), 9/6(SUN), 9/8(TUE)</t>
-  </si>
-  <si>
-    <t>9/15(TUE), 9/16(WED), 9/22(TUE), 9/23(WED), 9/9(WED)</t>
-  </si>
-  <si>
-    <t>10/3(SAT), 9/12(SAT)</t>
-  </si>
-  <si>
-    <t>9/16(WED), 9/30(WED), 9/9(WED)</t>
-  </si>
-  <si>
-    <t>9/15(TUE), 9/22(TUE)</t>
-  </si>
-  <si>
-    <t>9/11(FRI)</t>
-  </si>
-  <si>
-    <t>10/1(THU), 10/2(FRI), 9/10(THU), 9/17(THU), 9/18(FRI), 9/24(THU)</t>
-  </si>
-  <si>
-    <t>9/15(TUE), 9/16(WED), 9/22(TUE), 9/23(WED), 9/29(TUE), 9/30(WED)</t>
-  </si>
-  <si>
-    <t>10/1(THU)</t>
-  </si>
-  <si>
-    <t>9/15(TUE), 9/16(WED), 9/22(TUE), 9/23(WED), 9/29(TUE), 9/30(WED), 9/9(WED)</t>
-  </si>
-  <si>
-    <t>10/2(FRI), 9/18(FRI), 9/25(FRI)</t>
-  </si>
-  <si>
-    <t>9/20(SUN), 9/6(SUN)</t>
-  </si>
-  <si>
-    <t>9/13(SUN)</t>
-  </si>
-  <si>
-    <t>9/15(TUE), 9/16(WED), 9/22(TUE), 9/23(WED), 9/30(WED), 9/9(WED)</t>
-  </si>
-  <si>
-    <t>9/15(TUE), 9/16(WED), 9/23(WED), 9/30(WED)</t>
-  </si>
-  <si>
-    <t>9/22(TUE)</t>
-  </si>
-  <si>
-    <t>9/22(TUE), 9/30(WED), 9/8(TUE)</t>
-  </si>
-  <si>
-    <t>9/15(TUE), 9/23(WED)</t>
-  </si>
-  <si>
-    <t>9/25(FRI), 9/27(SUN)</t>
-  </si>
-  <si>
-    <t>9/16(WED), 9/22(TUE), 9/23(WED), 9/29(TUE), 9/30(WED)</t>
-  </si>
-  <si>
-    <t>10/3(SAT), 9/19(SAT), 9/26(SAT)</t>
-  </si>
-  <si>
-    <t>9/16(WED)</t>
-  </si>
-  <si>
-    <t>10/1(THU), 9/17(THU), 9/30(WED)</t>
-  </si>
-  <si>
-    <t>9/16(WED), 9/7(MON)</t>
-  </si>
-  <si>
-    <t>10/1(THU), 10/2(FRI), 9/10(THU), 9/11(FRI), 9/14(MON), 9/22(TUE), 9/23(WED), 9/7(MON), 9/8(TUE)</t>
-  </si>
-  <si>
-    <t>10/1(THU), 9/29(TUE), 9/30(WED), 9/8(TUE)</t>
-  </si>
-  <si>
-    <t>9/14(MON)</t>
-  </si>
-  <si>
-    <t>9/21(MON)</t>
-  </si>
-  <si>
-    <t>9/17(THU)</t>
-  </si>
-  <si>
-    <t>9/30(WED), 9/7(MON)</t>
-  </si>
-  <si>
-    <t>10/2(FRI)</t>
-  </si>
-  <si>
-    <t>10/1(THU), 10/2(FRI), 9/10(THU), 9/11(FRI), 9/14(MON), 9/15(TUE), 9/16(WED), 9/17(THU), 9/18(FRI), 9/21(MON), 9/22(TUE), 9/23(WED), 9/24(THU), 9/25(FRI), 9/28(MON), 9/29(TUE), 9/30(WED), 9/8(TUE), 9/9(WED)</t>
-  </si>
-  <si>
-    <t>9/18(FRI)</t>
-  </si>
-  <si>
-    <t>10/3(SAT), 9/10(THU), 9/11(FRI), 9/12(SAT), 9/13(SUN), 9/16(WED), 9/17(THU), 9/18(FRI), 9/19(SAT), 9/20(SUN), 9/21(MON), 9/22(TUE), 9/23(WED), 9/24(THU), 9/26(SAT), 9/27(SUN), 9/6(SUN), 9/7(MON), 9/8(TUE), 9/9(WED)</t>
-  </si>
-  <si>
-    <t>10/1(THU), 10/2(FRI), 10/3(SAT), 9/10(THU), 9/11(FRI), 9/12(SAT), 9/13(SUN), 9/14(MON), 9/15(TUE), 9/16(WED), 9/17(THU), 9/18(FRI), 9/19(SAT), 9/20(SUN), 9/21(MON), 9/22(TUE), 9/23(WED), 9/24(THU), 9/25(FRI), 9/26(SAT), 9/27(SUN), 9/28(MON), 9/29(TUE), 9/30(WED), 9/6(SUN), 9/7(MON), 9/8(TUE), 9/9(WED)</t>
-  </si>
-  <si>
-    <t>9/14(MON), 9/15(TUE), 9/16(WED), 9/9(WED)</t>
-  </si>
-  <si>
-    <t>9/23(WED)</t>
-  </si>
-  <si>
-    <t>9/15(TUE)</t>
-  </si>
-  <si>
-    <t>9/10(THU), 9/11(FRI), 9/17(THU), 9/18(FRI), 9/22(TUE)</t>
+    <t>10/27(TUE), 10/28(WED)</t>
+  </si>
+  <si>
+    <t>10/13(TUE), 10/14(WED), 10/20(TUE), 10/21(WED), 10/6(TUE), 10/7(WED)</t>
+  </si>
+  <si>
+    <t>10/13(TUE), 10/14(WED), 10/20(TUE), 10/21(WED), 10/27(TUE), 10/28(WED), 10/6(TUE), 10/7(WED)</t>
+  </si>
+  <si>
+    <t>10/15(THU), 10/16(FRI), 10/22(THU), 10/29(THU), 10/30(FRI), 10/9(FRI)</t>
+  </si>
+  <si>
+    <t>10/23(FRI), 10/8(THU)</t>
+  </si>
+  <si>
+    <t>10/12(MON), 10/19(MON), 10/5(MON)</t>
+  </si>
+  <si>
+    <t>10/26(MON)</t>
+  </si>
+  <si>
+    <t>10/11(SUN), 10/12(MON), 10/18(SUN), 10/19(MON), 10/25(SUN), 10/4(SUN), 10/5(MON)</t>
+  </si>
+  <si>
+    <t>10/16(FRI), 10/30(FRI), 10/9(FRI)</t>
+  </si>
+  <si>
+    <t>10/23(FRI)</t>
+  </si>
+  <si>
+    <t>10/10(SAT), 10/17(SAT), 10/24(SAT), 10/31(SAT)</t>
+  </si>
+  <si>
+    <t>10/10(SAT), 10/17(SAT), 10/31(SAT)</t>
+  </si>
+  <si>
+    <t>10/24(SAT)</t>
+  </si>
+  <si>
+    <t>10/27(TUE)</t>
+  </si>
+  <si>
+    <t>10/14(WED)</t>
+  </si>
+  <si>
+    <t>10/13(TUE), 10/20(TUE), 10/21(WED), 10/28(WED), 10/6(TUE), 10/7(WED)</t>
+  </si>
+  <si>
+    <t>10/10(SAT), 10/11(SUN), 10/15(THU), 10/17(SAT), 10/18(SUN), 10/22(THU), 10/25(SUN), 10/29(THU), 10/31(SAT), 10/4(SUN), 10/8(THU)</t>
+  </si>
+  <si>
+    <t>10/9(FRI)</t>
+  </si>
+  <si>
+    <t>10/16(FRI), 10/23(FRI), 10/30(FRI)</t>
+  </si>
+  <si>
+    <t>10/13(TUE), 10/14(WED), 10/20(TUE), 10/21(WED), 10/28(WED), 10/6(TUE), 10/7(WED)</t>
+  </si>
+  <si>
+    <t>10/11(SUN), 10/18(SUN), 10/25(SUN), 10/4(SUN)</t>
+  </si>
+  <si>
+    <t>10/6(TUE)</t>
+  </si>
+  <si>
+    <t>10/13(TUE), 10/20(TUE), 10/28(WED)</t>
+  </si>
+  <si>
+    <t>10/14(WED), 10/21(WED), 10/27(TUE), 10/7(WED)</t>
+  </si>
+  <si>
+    <t>10/15(THU)</t>
+  </si>
+  <si>
+    <t>10/22(THU), 10/29(THU)</t>
+  </si>
+  <si>
+    <t>10/8(THU)</t>
+  </si>
+  <si>
+    <t>10/15(THU), 10/22(THU), 10/29(THU), 10/8(THU)</t>
+  </si>
+  <si>
+    <t>10/19(MON), 10/5(MON)</t>
+  </si>
+  <si>
+    <t>10/17(SAT), 10/31(SAT)</t>
+  </si>
+  <si>
+    <t>10/10(SAT)</t>
+  </si>
+  <si>
+    <t>10/11(SUN)</t>
+  </si>
+  <si>
+    <t>10/18(SUN), 10/4(SUN)</t>
+  </si>
+  <si>
+    <t>10/25(SUN)</t>
+  </si>
+  <si>
+    <t>10/16(FRI), 10/30(FRI)</t>
+  </si>
+  <si>
+    <t>10/15(THU), 10/29(THU), 10/8(THU)</t>
+  </si>
+  <si>
+    <t>10/22(THU)</t>
+  </si>
+  <si>
+    <t>10/29(THU)</t>
+  </si>
+  <si>
+    <t>10/12(MON), 10/19(MON)</t>
+  </si>
+  <si>
+    <t>10/5(MON)</t>
+  </si>
+  <si>
+    <t>10/18(SUN), 10/25(SUN), 10/4(SUN)</t>
+  </si>
+  <si>
+    <t>10/11(SUN), 10/13(TUE), 10/15(THU), 10/18(SUN), 10/20(TUE), 10/21(WED), 10/27(TUE), 10/29(THU), 10/4(SUN)</t>
+  </si>
+  <si>
+    <t>10/28(WED)</t>
+  </si>
+  <si>
+    <t>10/22(THU), 10/6(TUE), 10/7(WED)</t>
+  </si>
+  <si>
+    <t>10/12(MON), 10/15(THU), 10/16(FRI), 10/19(MON), 10/22(THU), 10/23(FRI), 10/29(THU), 10/30(FRI), 10/5(MON), 10/9(FRI)</t>
+  </si>
+  <si>
+    <t>10/12(MON)</t>
+  </si>
+  <si>
+    <t>10/16(FRI), 10/23(FRI)</t>
+  </si>
+  <si>
+    <t>10/30(FRI)</t>
+  </si>
+  <si>
+    <t>10/10(SAT), 10/24(SAT)</t>
+  </si>
+  <si>
+    <t>10/13(TUE), 10/14(WED), 10/18(SUN), 10/20(TUE), 10/21(WED), 10/27(TUE), 10/28(WED), 10/4(SUN), 10/6(TUE), 10/7(WED)</t>
+  </si>
+  <si>
+    <t>10/15(THU), 10/22(THU), 10/29(THU)</t>
+  </si>
+  <si>
+    <t>10/31(SAT)</t>
+  </si>
+  <si>
+    <t>10/13(TUE), 10/20(TUE), 10/7(WED)</t>
+  </si>
+  <si>
+    <t>10/21(WED)</t>
+  </si>
+  <si>
+    <t>10/17(SAT), 10/24(SAT), 10/31(SAT)</t>
+  </si>
+  <si>
+    <t>10/15(THU), 10/16(FRI), 10/22(THU), 10/23(FRI), 10/29(THU), 10/30(FRI)</t>
+  </si>
+  <si>
+    <t>10/18(SUN)</t>
+  </si>
+  <si>
+    <t>10/14(WED), 10/20(TUE), 10/21(WED), 10/6(TUE), 10/7(WED)</t>
+  </si>
+  <si>
+    <t>10/15(THU), 10/22(THU)</t>
+  </si>
+  <si>
+    <t>10/21(WED), 10/6(TUE), 10/7(WED)</t>
+  </si>
+  <si>
+    <t>10/13(TUE), 10/14(WED), 10/20(TUE)</t>
+  </si>
+  <si>
+    <t>10/11(SUN), 10/18(SUN), 10/4(SUN)</t>
+  </si>
+  <si>
+    <t>10/13(TUE), 10/14(WED), 10/20(TUE), 10/21(WED), 10/27(TUE), 10/6(TUE), 10/7(WED)</t>
+  </si>
+  <si>
+    <t>10/23(FRI), 10/30(FRI)</t>
+  </si>
+  <si>
+    <t>10/16(FRI)</t>
+  </si>
+  <si>
+    <t>10/23(FRI), 10/30(FRI), 10/9(FRI)</t>
+  </si>
+  <si>
+    <t>10/19(MON)</t>
+  </si>
+  <si>
+    <t>10/25(SUN), 10/4(SUN)</t>
+  </si>
+  <si>
+    <t>10/15(THU), 10/19(MON), 10/22(THU), 10/29(THU)</t>
+  </si>
+  <si>
+    <t>10/13(TUE)</t>
+  </si>
+  <si>
+    <t>10/14(WED), 10/20(TUE)</t>
+  </si>
+  <si>
+    <t>10/21(WED), 10/27(TUE), 10/6(TUE), 10/7(WED)</t>
+  </si>
+  <si>
+    <t>10/14(WED), 10/21(WED), 10/6(TUE), 10/7(WED)</t>
+  </si>
+  <si>
+    <t>10/20(TUE), 10/27(TUE), 10/28(WED)</t>
+  </si>
+  <si>
+    <t>10/18(SUN), 10/23(FRI), 10/4(SUN)</t>
+  </si>
+  <si>
+    <t>10/21(WED), 10/27(TUE), 10/7(WED)</t>
+  </si>
+  <si>
+    <t>10/17(SAT), 10/24(SAT)</t>
+  </si>
+  <si>
+    <t>10/21(WED), 10/7(WED)</t>
+  </si>
+  <si>
+    <t>10/28(WED), 10/5(MON)</t>
+  </si>
+  <si>
+    <t>10/15(THU), 10/21(WED), 10/22(THU), 10/6(TUE)</t>
+  </si>
+  <si>
+    <t>10/20(TUE)</t>
+  </si>
+  <si>
+    <t>10/13(TUE), 10/14(WED)</t>
+  </si>
+  <si>
+    <t>10/28(WED), 10/6(TUE)</t>
+  </si>
+  <si>
+    <t>10/13(TUE), 10/15(THU), 10/19(MON), 10/20(TUE), 10/6(TUE), 10/7(WED)</t>
+  </si>
+  <si>
+    <t>10/14(WED), 10/15(THU), 10/16(FRI)</t>
+  </si>
+  <si>
+    <t>10/15(THU), 10/19(MON), 10/27(TUE), 10/28(WED), 10/5(MON)</t>
+  </si>
+  <si>
+    <t>10/15(THU), 10/27(TUE), 10/29(THU)</t>
+  </si>
+  <si>
+    <t>10/19(MON), 10/29(THU)</t>
+  </si>
+  <si>
+    <t>10/21(WED), 10/22(THU), 10/29(THU), 10/30(FRI)</t>
+  </si>
+  <si>
+    <t>10/12(MON), 10/13(TUE), 10/14(WED), 10/15(THU), 10/16(FRI), 10/17(SAT), 10/19(MON), 10/20(TUE), 10/21(WED), 10/22(THU), 10/23(FRI), 10/26(MON), 10/27(TUE), 10/28(WED), 10/29(THU), 10/30(FRI), 10/5(MON), 10/6(TUE), 10/7(WED), 10/8(THU), 10/9(FRI)</t>
+  </si>
+  <si>
+    <t>10/16(FRI), 10/19(MON), 10/23(FRI), 10/27(TUE)</t>
+  </si>
+  <si>
+    <t>10/13(TUE), 10/15(THU)</t>
+  </si>
+  <si>
+    <t>10/11(SUN), 10/12(MON), 10/13(TUE), 10/14(WED), 10/15(THU), 10/16(FRI), 10/18(SUN), 10/19(MON), 10/20(TUE), 10/21(WED), 10/22(THU), 10/23(FRI), 10/24(SAT), 10/26(MON), 10/28(WED), 10/29(THU), 10/30(FRI), 10/4(SUN), 10/5(MON), 10/6(TUE), 10/8(THU), 10/9(FRI)</t>
+  </si>
+  <si>
+    <t>10/10(SAT), 10/11(SUN), 10/12(MON), 10/13(TUE), 10/14(WED), 10/15(THU), 10/16(FRI), 10/17(SAT), 10/18(SUN), 10/19(MON), 10/20(TUE), 10/21(WED), 10/22(THU), 10/23(FRI), 10/24(SAT), 10/25(SUN), 10/26(MON), 10/27(TUE), 10/28(WED), 10/29(THU), 10/30(FRI), 10/31(SAT), 10/4(SUN), 10/5(MON), 10/6(TUE), 10/7(WED), 10/8(THU), 10/9(FRI)</t>
+  </si>
+  <si>
+    <t>10/13(TUE), 10/20(TUE)</t>
+  </si>
+  <si>
+    <t>10/13(TUE), 10/22(THU), 10/30(FRI), 10/6(TUE)</t>
   </si>
 </sst>
 </file>
@@ -2045,7 +2084,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E283"/>
+  <dimension ref="A1:E316"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -2070,16 +2109,16 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C2" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="D2" t="s">
-        <v>408</v>
+        <v>163</v>
       </c>
       <c r="E2" t="s">
-        <v>483</v>
+        <v>475</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -2087,16 +2126,16 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C3" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="D3" t="s">
-        <v>409</v>
+        <v>397</v>
       </c>
       <c r="E3" t="s">
-        <v>484</v>
+        <v>476</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -2104,101 +2143,101 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C4" t="s">
-        <v>283</v>
+        <v>164</v>
       </c>
       <c r="D4" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="E4" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C5" t="s">
-        <v>168</v>
+        <v>275</v>
       </c>
       <c r="D5" t="s">
-        <v>276</v>
+        <v>398</v>
       </c>
       <c r="E5" t="s">
-        <v>485</v>
+        <v>478</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C6" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="D6" t="s">
-        <v>410</v>
+        <v>397</v>
       </c>
       <c r="E6" t="s">
-        <v>486</v>
+        <v>479</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C7" t="s">
-        <v>285</v>
+        <v>275</v>
       </c>
       <c r="D7" t="s">
-        <v>411</v>
+        <v>398</v>
       </c>
       <c r="E7" t="s">
-        <v>487</v>
+        <v>480</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C8" t="s">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="D8" t="s">
-        <v>412</v>
+        <v>399</v>
       </c>
       <c r="E8" t="s">
-        <v>488</v>
+        <v>481</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C9" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="D9" t="s">
-        <v>411</v>
+        <v>400</v>
       </c>
       <c r="E9" t="s">
-        <v>489</v>
+        <v>482</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -2206,33 +2245,33 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C10" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="D10" t="s">
-        <v>413</v>
+        <v>398</v>
       </c>
       <c r="E10" t="s">
-        <v>490</v>
+        <v>481</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C11" t="s">
-        <v>288</v>
+        <v>278</v>
       </c>
       <c r="D11" t="s">
-        <v>414</v>
+        <v>401</v>
       </c>
       <c r="E11" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -2240,50 +2279,50 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C12" t="s">
-        <v>289</v>
+        <v>196</v>
       </c>
       <c r="D12" t="s">
-        <v>415</v>
+        <v>267</v>
       </c>
       <c r="E12" t="s">
-        <v>492</v>
+        <v>484</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C13" t="s">
-        <v>290</v>
+        <v>164</v>
       </c>
       <c r="D13" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="E13" t="s">
-        <v>493</v>
+        <v>485</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C14" t="s">
-        <v>168</v>
+        <v>277</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>400</v>
       </c>
       <c r="E14" t="s">
-        <v>494</v>
+        <v>486</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -2291,16 +2330,16 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C15" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="D15" t="s">
-        <v>414</v>
+        <v>402</v>
       </c>
       <c r="E15" t="s">
-        <v>494</v>
+        <v>487</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -2308,16 +2347,16 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C16" t="s">
-        <v>291</v>
+        <v>280</v>
       </c>
       <c r="D16" t="s">
-        <v>413</v>
+        <v>267</v>
       </c>
       <c r="E16" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -2325,33 +2364,33 @@
         <v>13</v>
       </c>
       <c r="B17" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C17" t="s">
-        <v>192</v>
+        <v>281</v>
       </c>
       <c r="D17" t="s">
-        <v>256</v>
+        <v>403</v>
       </c>
       <c r="E17" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B18" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C18" t="s">
-        <v>292</v>
+        <v>281</v>
       </c>
       <c r="D18" t="s">
-        <v>266</v>
+        <v>400</v>
       </c>
       <c r="E18" t="s">
-        <v>496</v>
+        <v>490</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -2359,16 +2398,16 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C19" t="s">
-        <v>293</v>
+        <v>282</v>
       </c>
       <c r="D19" t="s">
-        <v>416</v>
+        <v>404</v>
       </c>
       <c r="E19" t="s">
-        <v>497</v>
+        <v>487</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -2376,16 +2415,16 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C20" t="s">
-        <v>253</v>
+        <v>282</v>
       </c>
       <c r="D20" t="s">
-        <v>417</v>
+        <v>405</v>
       </c>
       <c r="E20" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -2393,16 +2432,16 @@
         <v>15</v>
       </c>
       <c r="B21" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C21" t="s">
-        <v>294</v>
+        <v>282</v>
       </c>
       <c r="D21" t="s">
-        <v>276</v>
+        <v>405</v>
       </c>
       <c r="E21" t="s">
-        <v>499</v>
+        <v>480</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -2413,13 +2452,13 @@
         <v>141</v>
       </c>
       <c r="C22" t="s">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="D22" t="s">
-        <v>416</v>
+        <v>267</v>
       </c>
       <c r="E22" t="s">
-        <v>500</v>
+        <v>481</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -2427,16 +2466,16 @@
         <v>16</v>
       </c>
       <c r="B23" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="C23" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="D23" t="s">
-        <v>418</v>
+        <v>406</v>
       </c>
       <c r="E23" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -2444,16 +2483,16 @@
         <v>16</v>
       </c>
       <c r="B24" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C24" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="D24" t="s">
-        <v>419</v>
+        <v>407</v>
       </c>
       <c r="E24" t="s">
-        <v>501</v>
+        <v>493</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2461,16 +2500,16 @@
         <v>17</v>
       </c>
       <c r="B25" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C25" t="s">
-        <v>295</v>
+        <v>284</v>
       </c>
       <c r="D25" t="s">
-        <v>420</v>
+        <v>407</v>
       </c>
       <c r="E25" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2478,16 +2517,16 @@
         <v>17</v>
       </c>
       <c r="B26" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C26" t="s">
-        <v>295</v>
+        <v>284</v>
       </c>
       <c r="D26" t="s">
-        <v>421</v>
+        <v>408</v>
       </c>
       <c r="E26" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2495,16 +2534,16 @@
         <v>18</v>
       </c>
       <c r="B27" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C27" t="s">
-        <v>296</v>
+        <v>285</v>
       </c>
       <c r="D27" t="s">
-        <v>263</v>
+        <v>409</v>
       </c>
       <c r="E27" t="s">
-        <v>494</v>
+        <v>485</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2512,16 +2551,16 @@
         <v>19</v>
       </c>
       <c r="B28" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C28" t="s">
-        <v>166</v>
+        <v>255</v>
       </c>
       <c r="D28" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="E28" t="s">
-        <v>502</v>
+        <v>495</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2529,16 +2568,16 @@
         <v>20</v>
       </c>
       <c r="B29" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="C29" t="s">
-        <v>192</v>
+        <v>286</v>
       </c>
       <c r="D29" t="s">
-        <v>422</v>
+        <v>410</v>
       </c>
       <c r="E29" t="s">
-        <v>503</v>
+        <v>481</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2546,16 +2585,16 @@
         <v>20</v>
       </c>
       <c r="B30" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C30" t="s">
-        <v>297</v>
+        <v>188</v>
       </c>
       <c r="D30" t="s">
-        <v>423</v>
+        <v>411</v>
       </c>
       <c r="E30" t="s">
-        <v>504</v>
+        <v>480</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2563,16 +2602,16 @@
         <v>21</v>
       </c>
       <c r="B31" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C31" t="s">
-        <v>192</v>
+        <v>287</v>
       </c>
       <c r="D31" t="s">
-        <v>424</v>
+        <v>267</v>
       </c>
       <c r="E31" t="s">
-        <v>505</v>
+        <v>496</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2580,16 +2619,16 @@
         <v>21</v>
       </c>
       <c r="B32" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C32" t="s">
-        <v>293</v>
+        <v>188</v>
       </c>
       <c r="D32" t="s">
-        <v>276</v>
+        <v>156</v>
       </c>
       <c r="E32" t="s">
-        <v>483</v>
+        <v>497</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2597,33 +2636,33 @@
         <v>21</v>
       </c>
       <c r="B33" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C33" t="s">
-        <v>192</v>
+        <v>288</v>
       </c>
       <c r="D33" t="s">
-        <v>425</v>
+        <v>267</v>
       </c>
       <c r="E33" t="s">
-        <v>506</v>
+        <v>498</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B34" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="C34" t="s">
-        <v>298</v>
+        <v>287</v>
       </c>
       <c r="D34" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="E34" t="s">
-        <v>486</v>
+        <v>499</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2631,16 +2670,16 @@
         <v>22</v>
       </c>
       <c r="B35" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C35" t="s">
-        <v>293</v>
+        <v>273</v>
       </c>
       <c r="D35" t="s">
-        <v>254</v>
+        <v>412</v>
       </c>
       <c r="E35" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2648,50 +2687,50 @@
         <v>22</v>
       </c>
       <c r="B36" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C36" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="D36" t="s">
-        <v>426</v>
+        <v>413</v>
       </c>
       <c r="E36" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B37" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C37" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="D37" t="s">
-        <v>417</v>
+        <v>405</v>
       </c>
       <c r="E37" t="s">
-        <v>508</v>
+        <v>502</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B38" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C38" t="s">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="D38" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="E38" t="s">
-        <v>509</v>
+        <v>480</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2699,33 +2738,33 @@
         <v>24</v>
       </c>
       <c r="B39" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C39" t="s">
-        <v>195</v>
+        <v>232</v>
       </c>
       <c r="D39" t="s">
-        <v>427</v>
+        <v>411</v>
       </c>
       <c r="E39" t="s">
-        <v>504</v>
+        <v>481</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B40" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="C40" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="D40" t="s">
-        <v>428</v>
+        <v>415</v>
       </c>
       <c r="E40" t="s">
-        <v>503</v>
+        <v>481</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2733,33 +2772,33 @@
         <v>25</v>
       </c>
       <c r="B41" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C41" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="D41" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="E41" t="s">
-        <v>503</v>
+        <v>480</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B42" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C42" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="D42" t="s">
-        <v>409</v>
+        <v>400</v>
       </c>
       <c r="E42" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2767,84 +2806,84 @@
         <v>26</v>
       </c>
       <c r="B43" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C43" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="D43" t="s">
-        <v>429</v>
+        <v>416</v>
       </c>
       <c r="E43" t="s">
-        <v>504</v>
+        <v>481</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B44" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C44" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="D44" t="s">
-        <v>430</v>
+        <v>417</v>
       </c>
       <c r="E44" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B45" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C45" t="s">
-        <v>305</v>
+        <v>193</v>
       </c>
       <c r="D45" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="E45" t="s">
-        <v>510</v>
+        <v>487</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B46" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C46" t="s">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="D46" t="s">
-        <v>431</v>
+        <v>419</v>
       </c>
       <c r="E46" t="s">
-        <v>498</v>
+        <v>487</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B47" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C47" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="D47" t="s">
-        <v>432</v>
+        <v>420</v>
       </c>
       <c r="E47" t="s">
-        <v>511</v>
+        <v>504</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -2852,50 +2891,50 @@
         <v>28</v>
       </c>
       <c r="B48" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C48" t="s">
-        <v>307</v>
+        <v>212</v>
       </c>
       <c r="D48" t="s">
-        <v>433</v>
+        <v>421</v>
       </c>
       <c r="E48" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B49" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C49" t="s">
-        <v>308</v>
+        <v>240</v>
       </c>
       <c r="D49" t="s">
-        <v>434</v>
+        <v>267</v>
       </c>
       <c r="E49" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B50" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C50" t="s">
-        <v>309</v>
+        <v>299</v>
       </c>
       <c r="D50" t="s">
-        <v>276</v>
+        <v>422</v>
       </c>
       <c r="E50" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -2903,16 +2942,16 @@
         <v>30</v>
       </c>
       <c r="B51" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C51" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="D51" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="E51" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -2920,16 +2959,16 @@
         <v>30</v>
       </c>
       <c r="B52" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C52" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="D52" t="s">
-        <v>435</v>
+        <v>423</v>
       </c>
       <c r="E52" t="s">
-        <v>491</v>
+        <v>508</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -2937,67 +2976,67 @@
         <v>31</v>
       </c>
       <c r="B53" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C53" t="s">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="D53" t="s">
-        <v>412</v>
+        <v>424</v>
       </c>
       <c r="E53" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B54" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="C54" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="D54" t="s">
-        <v>276</v>
+        <v>155</v>
       </c>
       <c r="E54" t="s">
-        <v>514</v>
+        <v>484</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B55" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C55" t="s">
-        <v>314</v>
+        <v>302</v>
       </c>
       <c r="D55" t="s">
-        <v>436</v>
+        <v>418</v>
       </c>
       <c r="E55" t="s">
-        <v>508</v>
+        <v>492</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B56" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C56" t="s">
-        <v>315</v>
+        <v>304</v>
       </c>
       <c r="D56" t="s">
-        <v>408</v>
+        <v>267</v>
       </c>
       <c r="E56" t="s">
-        <v>499</v>
+        <v>510</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -3005,16 +3044,16 @@
         <v>33</v>
       </c>
       <c r="B57" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C57" t="s">
-        <v>316</v>
+        <v>305</v>
       </c>
       <c r="D57" t="s">
-        <v>437</v>
+        <v>425</v>
       </c>
       <c r="E57" t="s">
-        <v>510</v>
+        <v>480</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -3022,16 +3061,16 @@
         <v>33</v>
       </c>
       <c r="B58" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C58" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="D58" t="s">
-        <v>276</v>
+        <v>426</v>
       </c>
       <c r="E58" t="s">
-        <v>504</v>
+        <v>481</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -3039,16 +3078,16 @@
         <v>34</v>
       </c>
       <c r="B59" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C59" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="D59" t="s">
-        <v>438</v>
+        <v>427</v>
       </c>
       <c r="E59" t="s">
-        <v>515</v>
+        <v>499</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -3056,50 +3095,50 @@
         <v>34</v>
       </c>
       <c r="B60" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C60" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="D60" t="s">
-        <v>439</v>
+        <v>428</v>
       </c>
       <c r="E60" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B61" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="C61" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="D61" t="s">
-        <v>433</v>
+        <v>267</v>
       </c>
       <c r="E61" t="s">
-        <v>504</v>
+        <v>511</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B62" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C62" t="s">
-        <v>319</v>
+        <v>302</v>
       </c>
       <c r="D62" t="s">
-        <v>414</v>
+        <v>429</v>
       </c>
       <c r="E62" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -3107,84 +3146,84 @@
         <v>35</v>
       </c>
       <c r="B63" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C63" t="s">
-        <v>320</v>
+        <v>309</v>
       </c>
       <c r="D63" t="s">
-        <v>408</v>
+        <v>267</v>
       </c>
       <c r="E63" t="s">
-        <v>499</v>
+        <v>481</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B64" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="C64" t="s">
-        <v>242</v>
+        <v>310</v>
       </c>
       <c r="D64" t="s">
-        <v>276</v>
+        <v>402</v>
       </c>
       <c r="E64" t="s">
-        <v>491</v>
+        <v>513</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B65" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="C65" t="s">
-        <v>321</v>
+        <v>301</v>
       </c>
       <c r="D65" t="s">
-        <v>277</v>
+        <v>426</v>
       </c>
       <c r="E65" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B66" t="s">
-        <v>138</v>
+        <v>163</v>
       </c>
       <c r="C66" t="s">
-        <v>322</v>
+        <v>311</v>
       </c>
       <c r="D66" t="s">
-        <v>440</v>
+        <v>418</v>
       </c>
       <c r="E66" t="s">
-        <v>483</v>
+        <v>506</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B67" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="C67" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="D67" t="s">
-        <v>254</v>
+        <v>428</v>
       </c>
       <c r="E67" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -3192,16 +3231,16 @@
         <v>37</v>
       </c>
       <c r="B68" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C68" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="D68" t="s">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="E68" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -3209,557 +3248,557 @@
         <v>37</v>
       </c>
       <c r="B69" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C69" t="s">
-        <v>290</v>
+        <v>275</v>
       </c>
       <c r="D69" t="s">
-        <v>276</v>
+        <v>398</v>
       </c>
       <c r="E69" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B70" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C70" t="s">
-        <v>295</v>
+        <v>278</v>
       </c>
       <c r="D70" t="s">
-        <v>439</v>
+        <v>401</v>
       </c>
       <c r="E70" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B71" t="s">
-        <v>139</v>
+        <v>165</v>
       </c>
       <c r="C71" t="s">
-        <v>168</v>
+        <v>228</v>
       </c>
       <c r="D71" t="s">
-        <v>276</v>
+        <v>430</v>
       </c>
       <c r="E71" t="s">
-        <v>502</v>
+        <v>508</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B72" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C72" t="s">
-        <v>294</v>
+        <v>184</v>
       </c>
       <c r="D72" t="s">
-        <v>276</v>
+        <v>431</v>
       </c>
       <c r="E72" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B73" t="s">
-        <v>169</v>
+        <v>137</v>
       </c>
       <c r="C73" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="D73" t="s">
-        <v>425</v>
+        <v>267</v>
       </c>
       <c r="E73" t="s">
-        <v>486</v>
+        <v>518</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B74" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="C74" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="D74" t="s">
-        <v>441</v>
+        <v>432</v>
       </c>
       <c r="E74" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B75" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="C75" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="D75" t="s">
-        <v>276</v>
+        <v>433</v>
       </c>
       <c r="E75" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B76" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="C76" t="s">
-        <v>294</v>
+        <v>164</v>
       </c>
       <c r="D76" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="E76" t="s">
-        <v>510</v>
+        <v>481</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B77" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="C77" t="s">
-        <v>293</v>
+        <v>164</v>
       </c>
       <c r="D77" t="s">
-        <v>416</v>
+        <v>267</v>
       </c>
       <c r="E77" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B78" t="s">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="C78" t="s">
-        <v>324</v>
+        <v>292</v>
       </c>
       <c r="D78" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="E78" t="s">
-        <v>504</v>
+        <v>490</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B79" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C79" t="s">
-        <v>325</v>
+        <v>186</v>
       </c>
       <c r="D79" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="E79" t="s">
-        <v>510</v>
+        <v>488</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B80" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="C80" t="s">
-        <v>326</v>
+        <v>314</v>
       </c>
       <c r="D80" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="E80" t="s">
-        <v>499</v>
+        <v>489</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B81" t="s">
-        <v>171</v>
+        <v>140</v>
       </c>
       <c r="C81" t="s">
-        <v>327</v>
+        <v>292</v>
       </c>
       <c r="D81" t="s">
-        <v>442</v>
+        <v>267</v>
       </c>
       <c r="E81" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B82" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C82" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D82" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="E82" t="s">
-        <v>501</v>
+        <v>480</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B83" t="s">
-        <v>147</v>
+        <v>167</v>
       </c>
       <c r="C83" t="s">
-        <v>186</v>
+        <v>315</v>
       </c>
       <c r="D83" t="s">
-        <v>413</v>
+        <v>267</v>
       </c>
       <c r="E83" t="s">
-        <v>488</v>
+        <v>481</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B84" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="C84" t="s">
-        <v>295</v>
+        <v>186</v>
       </c>
       <c r="D84" t="s">
-        <v>443</v>
+        <v>428</v>
       </c>
       <c r="E84" t="s">
-        <v>494</v>
+        <v>520</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B85" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C85" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="D85" t="s">
-        <v>444</v>
+        <v>423</v>
       </c>
       <c r="E85" t="s">
-        <v>486</v>
+        <v>503</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B86" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="C86" t="s">
-        <v>284</v>
+        <v>316</v>
       </c>
       <c r="D86" t="s">
-        <v>167</v>
+        <v>267</v>
       </c>
       <c r="E86" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B87" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="C87" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="D87" t="s">
-        <v>445</v>
+        <v>267</v>
       </c>
       <c r="E87" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B88" t="s">
-        <v>147</v>
+        <v>169</v>
       </c>
       <c r="C88" t="s">
-        <v>328</v>
+        <v>317</v>
       </c>
       <c r="D88" t="s">
-        <v>446</v>
+        <v>267</v>
       </c>
       <c r="E88" t="s">
-        <v>491</v>
+        <v>522</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B89" t="s">
-        <v>144</v>
+        <v>170</v>
       </c>
       <c r="C89" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="D89" t="s">
-        <v>275</v>
+        <v>434</v>
       </c>
       <c r="E89" t="s">
-        <v>509</v>
+        <v>492</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B90" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="C90" t="s">
-        <v>329</v>
+        <v>284</v>
       </c>
       <c r="D90" t="s">
-        <v>276</v>
+        <v>435</v>
       </c>
       <c r="E90" t="s">
-        <v>488</v>
+        <v>504</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B91" t="s">
-        <v>144</v>
+        <v>171</v>
       </c>
       <c r="C91" t="s">
-        <v>273</v>
+        <v>284</v>
       </c>
       <c r="D91" t="s">
-        <v>447</v>
+        <v>436</v>
       </c>
       <c r="E91" t="s">
-        <v>501</v>
+        <v>523</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B92" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C92" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="D92" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="E92" t="s">
-        <v>486</v>
+        <v>508</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B93" t="s">
-        <v>151</v>
+        <v>172</v>
       </c>
       <c r="C93" t="s">
-        <v>330</v>
+        <v>290</v>
       </c>
       <c r="D93" t="s">
-        <v>276</v>
+        <v>438</v>
       </c>
       <c r="E93" t="s">
-        <v>495</v>
+        <v>524</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B94" t="s">
-        <v>151</v>
+        <v>172</v>
       </c>
       <c r="C94" t="s">
-        <v>282</v>
+        <v>319</v>
       </c>
       <c r="D94" t="s">
-        <v>417</v>
+        <v>439</v>
       </c>
       <c r="E94" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B95" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="C95" t="s">
-        <v>284</v>
+        <v>313</v>
       </c>
       <c r="D95" t="s">
-        <v>416</v>
+        <v>266</v>
       </c>
       <c r="E95" t="s">
-        <v>488</v>
+        <v>525</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B96" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="C96" t="s">
-        <v>306</v>
+        <v>320</v>
       </c>
       <c r="D96" t="s">
-        <v>449</v>
+        <v>427</v>
       </c>
       <c r="E96" t="s">
-        <v>494</v>
+        <v>501</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B97" t="s">
-        <v>155</v>
+        <v>138</v>
       </c>
       <c r="C97" t="s">
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="D97" t="s">
-        <v>159</v>
+        <v>267</v>
       </c>
       <c r="E97" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B98" t="s">
-        <v>174</v>
+        <v>142</v>
       </c>
       <c r="C98" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="D98" t="s">
-        <v>450</v>
+        <v>410</v>
       </c>
       <c r="E98" t="s">
-        <v>505</v>
+        <v>493</v>
       </c>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B99" t="s">
-        <v>175</v>
+        <v>148</v>
       </c>
       <c r="C99" t="s">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="D99" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="E99" t="s">
-        <v>520</v>
+        <v>476</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B100" t="s">
-        <v>175</v>
+        <v>148</v>
       </c>
       <c r="C100" t="s">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="D100" t="s">
-        <v>276</v>
+        <v>435</v>
       </c>
       <c r="E100" t="s">
-        <v>509</v>
+        <v>517</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B101" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="C101" t="s">
-        <v>201</v>
+        <v>291</v>
       </c>
       <c r="D101" t="s">
-        <v>451</v>
+        <v>414</v>
       </c>
       <c r="E101" t="s">
         <v>488</v>
@@ -3767,424 +3806,424 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B102" t="s">
-        <v>175</v>
+        <v>148</v>
       </c>
       <c r="C102" t="s">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="D102" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="E102" t="s">
-        <v>501</v>
+        <v>492</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B103" t="s">
-        <v>176</v>
+        <v>148</v>
       </c>
       <c r="C103" t="s">
-        <v>333</v>
+        <v>291</v>
       </c>
       <c r="D103" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="E103" t="s">
-        <v>521</v>
+        <v>484</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B104" t="s">
-        <v>177</v>
+        <v>148</v>
       </c>
       <c r="C104" t="s">
-        <v>334</v>
+        <v>274</v>
       </c>
       <c r="D104" t="s">
-        <v>452</v>
+        <v>440</v>
       </c>
       <c r="E104" t="s">
-        <v>498</v>
+        <v>509</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B105" t="s">
-        <v>176</v>
+        <v>148</v>
       </c>
       <c r="C105" t="s">
-        <v>335</v>
+        <v>324</v>
       </c>
       <c r="D105" t="s">
-        <v>453</v>
+        <v>441</v>
       </c>
       <c r="E105" t="s">
-        <v>488</v>
+        <v>523</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B106" t="s">
-        <v>178</v>
+        <v>148</v>
       </c>
       <c r="C106" t="s">
-        <v>336</v>
+        <v>296</v>
       </c>
       <c r="D106" t="s">
-        <v>454</v>
+        <v>442</v>
       </c>
       <c r="E106" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="B107" t="s">
-        <v>179</v>
+        <v>141</v>
       </c>
       <c r="C107" t="s">
-        <v>337</v>
+        <v>283</v>
       </c>
       <c r="D107" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="E107" t="s">
-        <v>522</v>
+        <v>477</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B108" t="s">
-        <v>179</v>
+        <v>141</v>
       </c>
       <c r="C108" t="s">
-        <v>312</v>
+        <v>283</v>
       </c>
       <c r="D108" t="s">
-        <v>450</v>
+        <v>267</v>
       </c>
       <c r="E108" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B109" t="s">
-        <v>180</v>
+        <v>141</v>
       </c>
       <c r="C109" t="s">
-        <v>338</v>
+        <v>325</v>
       </c>
       <c r="D109" t="s">
-        <v>276</v>
+        <v>443</v>
       </c>
       <c r="E109" t="s">
-        <v>486</v>
+        <v>501</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B110" t="s">
-        <v>181</v>
+        <v>150</v>
       </c>
       <c r="C110" t="s">
-        <v>339</v>
+        <v>326</v>
       </c>
       <c r="D110" t="s">
-        <v>430</v>
+        <v>267</v>
       </c>
       <c r="E110" t="s">
-        <v>505</v>
+        <v>492</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B111" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C111" t="s">
-        <v>168</v>
+        <v>283</v>
       </c>
       <c r="D111" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="E111" t="s">
-        <v>511</v>
+        <v>493</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B112" t="s">
-        <v>139</v>
+        <v>173</v>
       </c>
       <c r="C112" t="s">
-        <v>340</v>
+        <v>327</v>
       </c>
       <c r="D112" t="s">
-        <v>419</v>
+        <v>444</v>
       </c>
       <c r="E112" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
     </row>
     <row r="113" spans="1:5">
       <c r="A113" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B113" t="s">
-        <v>147</v>
+        <v>173</v>
       </c>
       <c r="C113" t="s">
-        <v>293</v>
+        <v>304</v>
       </c>
       <c r="D113" t="s">
-        <v>276</v>
+        <v>409</v>
       </c>
       <c r="E113" t="s">
-        <v>524</v>
+        <v>505</v>
       </c>
     </row>
     <row r="114" spans="1:5">
       <c r="A114" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B114" t="s">
-        <v>147</v>
+        <v>173</v>
       </c>
       <c r="C114" t="s">
-        <v>341</v>
+        <v>311</v>
       </c>
       <c r="D114" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="E114" t="s">
-        <v>525</v>
+        <v>487</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B115" t="s">
-        <v>147</v>
+        <v>174</v>
       </c>
       <c r="C115" t="s">
-        <v>342</v>
+        <v>328</v>
       </c>
       <c r="D115" t="s">
-        <v>426</v>
+        <v>443</v>
       </c>
       <c r="E115" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B116" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="C116" t="s">
-        <v>343</v>
+        <v>329</v>
       </c>
       <c r="D116" t="s">
-        <v>276</v>
+        <v>423</v>
       </c>
       <c r="E116" t="s">
-        <v>511</v>
+        <v>496</v>
       </c>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B117" t="s">
-        <v>182</v>
+        <v>159</v>
       </c>
       <c r="C117" t="s">
-        <v>344</v>
+        <v>302</v>
       </c>
       <c r="D117" t="s">
-        <v>449</v>
+        <v>418</v>
       </c>
       <c r="E117" t="s">
-        <v>498</v>
+        <v>527</v>
       </c>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="B118" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="C118" t="s">
-        <v>300</v>
+        <v>330</v>
       </c>
       <c r="D118" t="s">
-        <v>159</v>
+        <v>267</v>
       </c>
       <c r="E118" t="s">
-        <v>511</v>
+        <v>528</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B119" t="s">
-        <v>167</v>
+        <v>136</v>
       </c>
       <c r="C119" t="s">
-        <v>345</v>
+        <v>164</v>
       </c>
       <c r="D119" t="s">
-        <v>455</v>
+        <v>267</v>
       </c>
       <c r="E119" t="s">
-        <v>498</v>
+        <v>529</v>
       </c>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B120" t="s">
-        <v>183</v>
+        <v>136</v>
       </c>
       <c r="C120" t="s">
-        <v>346</v>
+        <v>331</v>
       </c>
       <c r="D120" t="s">
-        <v>456</v>
+        <v>408</v>
       </c>
       <c r="E120" t="s">
-        <v>498</v>
+        <v>505</v>
       </c>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B121" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="C121" t="s">
-        <v>347</v>
+        <v>284</v>
       </c>
       <c r="D121" t="s">
-        <v>454</v>
+        <v>436</v>
       </c>
       <c r="E121" t="s">
-        <v>511</v>
+        <v>492</v>
       </c>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B122" t="s">
-        <v>185</v>
+        <v>172</v>
       </c>
       <c r="C122" t="s">
-        <v>348</v>
+        <v>324</v>
       </c>
       <c r="D122" t="s">
-        <v>457</v>
+        <v>428</v>
       </c>
       <c r="E122" t="s">
-        <v>512</v>
+        <v>530</v>
       </c>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B123" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
       <c r="C123" t="s">
-        <v>349</v>
+        <v>282</v>
       </c>
       <c r="D123" t="s">
-        <v>159</v>
+        <v>267</v>
       </c>
       <c r="E123" t="s">
-        <v>491</v>
+        <v>501</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B124" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="C124" t="s">
-        <v>319</v>
+        <v>332</v>
       </c>
       <c r="D124" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="E124" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B125" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="C125" t="s">
-        <v>350</v>
+        <v>290</v>
       </c>
       <c r="D125" t="s">
-        <v>458</v>
+        <v>445</v>
       </c>
       <c r="E125" t="s">
-        <v>483</v>
+        <v>505</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B126" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="C126" t="s">
-        <v>350</v>
+        <v>291</v>
       </c>
       <c r="D126" t="s">
-        <v>422</v>
+        <v>446</v>
       </c>
       <c r="E126" t="s">
         <v>505</v>
@@ -4192,560 +4231,560 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B127" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="C127" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="D127" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="E127" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
     </row>
     <row r="128" spans="1:5">
       <c r="A128" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B128" t="s">
-        <v>190</v>
+        <v>141</v>
       </c>
       <c r="C128" t="s">
-        <v>351</v>
+        <v>333</v>
       </c>
       <c r="D128" t="s">
-        <v>276</v>
+        <v>447</v>
       </c>
       <c r="E128" t="s">
-        <v>496</v>
+        <v>487</v>
       </c>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B129" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="C129" t="s">
-        <v>352</v>
+        <v>334</v>
       </c>
       <c r="D129" t="s">
-        <v>439</v>
+        <v>267</v>
       </c>
       <c r="E129" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B130" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="C130" t="s">
-        <v>352</v>
+        <v>335</v>
       </c>
       <c r="D130" t="s">
-        <v>459</v>
+        <v>443</v>
       </c>
       <c r="E130" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="B131" t="s">
-        <v>192</v>
+        <v>180</v>
       </c>
       <c r="C131" t="s">
-        <v>349</v>
+        <v>336</v>
       </c>
       <c r="D131" t="s">
-        <v>276</v>
+        <v>414</v>
       </c>
       <c r="E131" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B132" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="C132" t="s">
-        <v>353</v>
+        <v>289</v>
       </c>
       <c r="D132" t="s">
-        <v>277</v>
+        <v>415</v>
       </c>
       <c r="E132" t="s">
-        <v>499</v>
+        <v>531</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B133" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="C133" t="s">
-        <v>354</v>
+        <v>337</v>
       </c>
       <c r="D133" t="s">
-        <v>420</v>
+        <v>448</v>
       </c>
       <c r="E133" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="B134" t="s">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="C134" t="s">
-        <v>355</v>
+        <v>289</v>
       </c>
       <c r="D134" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="E134" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="B135" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="C135" t="s">
-        <v>356</v>
+        <v>301</v>
       </c>
       <c r="D135" t="s">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="E135" t="s">
-        <v>506</v>
+        <v>517</v>
       </c>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="B136" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="C136" t="s">
-        <v>356</v>
+        <v>310</v>
       </c>
       <c r="D136" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="E136" t="s">
-        <v>483</v>
+        <v>532</v>
       </c>
     </row>
     <row r="137" spans="1:5">
       <c r="A137" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="B137" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="C137" t="s">
-        <v>357</v>
+        <v>338</v>
       </c>
       <c r="D137" t="s">
-        <v>460</v>
+        <v>411</v>
       </c>
       <c r="E137" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="138" spans="1:5">
       <c r="A138" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B138" t="s">
-        <v>199</v>
+        <v>183</v>
       </c>
       <c r="C138" t="s">
-        <v>358</v>
+        <v>301</v>
       </c>
       <c r="D138" t="s">
-        <v>453</v>
+        <v>267</v>
       </c>
       <c r="E138" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="B139" t="s">
-        <v>200</v>
+        <v>184</v>
       </c>
       <c r="C139" t="s">
-        <v>359</v>
+        <v>310</v>
       </c>
       <c r="D139" t="s">
-        <v>461</v>
+        <v>267</v>
       </c>
       <c r="E139" t="s">
-        <v>488</v>
+        <v>533</v>
       </c>
     </row>
     <row r="140" spans="1:5">
       <c r="A140" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B140" t="s">
-        <v>196</v>
+        <v>182</v>
       </c>
       <c r="C140" t="s">
-        <v>360</v>
+        <v>289</v>
       </c>
       <c r="D140" t="s">
-        <v>421</v>
+        <v>267</v>
       </c>
       <c r="E140" t="s">
-        <v>501</v>
+        <v>509</v>
       </c>
     </row>
     <row r="141" spans="1:5">
       <c r="A141" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="B141" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="C141" t="s">
-        <v>360</v>
+        <v>339</v>
       </c>
       <c r="D141" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="E141" t="s">
-        <v>502</v>
+        <v>492</v>
       </c>
     </row>
     <row r="142" spans="1:5">
       <c r="A142" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="B142" t="s">
-        <v>202</v>
+        <v>187</v>
       </c>
       <c r="C142" t="s">
-        <v>352</v>
+        <v>337</v>
       </c>
       <c r="D142" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="E142" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
     </row>
     <row r="143" spans="1:5">
       <c r="A143" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="B143" t="s">
-        <v>203</v>
+        <v>188</v>
       </c>
       <c r="C143" t="s">
-        <v>361</v>
+        <v>340</v>
       </c>
       <c r="D143" t="s">
-        <v>461</v>
+        <v>267</v>
       </c>
       <c r="E143" t="s">
-        <v>527</v>
+        <v>503</v>
       </c>
     </row>
     <row r="144" spans="1:5">
       <c r="A144" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="B144" t="s">
-        <v>203</v>
+        <v>189</v>
       </c>
       <c r="C144" t="s">
-        <v>353</v>
+        <v>341</v>
       </c>
       <c r="D144" t="s">
-        <v>462</v>
+        <v>436</v>
       </c>
       <c r="E144" t="s">
-        <v>508</v>
+        <v>520</v>
       </c>
     </row>
     <row r="145" spans="1:5">
       <c r="A145" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="B145" t="s">
-        <v>203</v>
+        <v>189</v>
       </c>
       <c r="C145" t="s">
-        <v>362</v>
+        <v>342</v>
       </c>
       <c r="D145" t="s">
-        <v>437</v>
+        <v>450</v>
       </c>
       <c r="E145" t="s">
-        <v>512</v>
+        <v>481</v>
       </c>
     </row>
     <row r="146" spans="1:5">
       <c r="A146" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="B146" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="C146" t="s">
-        <v>363</v>
+        <v>343</v>
       </c>
       <c r="D146" t="s">
-        <v>463</v>
+        <v>267</v>
       </c>
       <c r="E146" t="s">
-        <v>491</v>
+        <v>533</v>
       </c>
     </row>
     <row r="147" spans="1:5">
       <c r="A147" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B147" t="s">
-        <v>205</v>
+        <v>191</v>
       </c>
       <c r="C147" t="s">
-        <v>361</v>
+        <v>344</v>
       </c>
       <c r="D147" t="s">
-        <v>276</v>
+        <v>425</v>
       </c>
       <c r="E147" t="s">
-        <v>505</v>
+        <v>512</v>
       </c>
     </row>
     <row r="148" spans="1:5">
       <c r="A148" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B148" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="C148" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="D148" t="s">
-        <v>464</v>
+        <v>267</v>
       </c>
       <c r="E148" t="s">
-        <v>528</v>
+        <v>501</v>
       </c>
     </row>
     <row r="149" spans="1:5">
       <c r="A149" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="B149" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="C149" t="s">
-        <v>364</v>
+        <v>346</v>
       </c>
       <c r="D149" t="s">
-        <v>460</v>
+        <v>251</v>
       </c>
       <c r="E149" t="s">
-        <v>496</v>
+        <v>534</v>
       </c>
     </row>
     <row r="150" spans="1:5">
       <c r="A150" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="B150" t="s">
-        <v>207</v>
+        <v>194</v>
       </c>
       <c r="C150" t="s">
-        <v>358</v>
+        <v>346</v>
       </c>
       <c r="D150" t="s">
-        <v>465</v>
+        <v>425</v>
       </c>
       <c r="E150" t="s">
-        <v>508</v>
+        <v>535</v>
       </c>
     </row>
     <row r="151" spans="1:5">
       <c r="A151" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="B151" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="C151" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="D151" t="s">
-        <v>435</v>
+        <v>267</v>
       </c>
       <c r="E151" t="s">
-        <v>507</v>
+        <v>475</v>
       </c>
     </row>
     <row r="152" spans="1:5">
       <c r="A152" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B152" t="s">
-        <v>208</v>
+        <v>196</v>
       </c>
       <c r="C152" t="s">
-        <v>365</v>
+        <v>310</v>
       </c>
       <c r="D152" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="E152" t="s">
-        <v>513</v>
+        <v>492</v>
       </c>
     </row>
     <row r="153" spans="1:5">
       <c r="A153" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="B153" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="C153" t="s">
-        <v>357</v>
+        <v>342</v>
       </c>
       <c r="D153" t="s">
-        <v>466</v>
+        <v>416</v>
       </c>
       <c r="E153" t="s">
-        <v>510</v>
+        <v>484</v>
       </c>
     </row>
     <row r="154" spans="1:5">
       <c r="A154" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="B154" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="C154" t="s">
-        <v>358</v>
+        <v>347</v>
       </c>
       <c r="D154" t="s">
-        <v>433</v>
+        <v>267</v>
       </c>
       <c r="E154" t="s">
-        <v>499</v>
+        <v>509</v>
       </c>
     </row>
     <row r="155" spans="1:5">
       <c r="A155" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="B155" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="C155" t="s">
-        <v>362</v>
+        <v>342</v>
       </c>
       <c r="D155" t="s">
-        <v>150</v>
+        <v>267</v>
       </c>
       <c r="E155" t="s">
-        <v>524</v>
+        <v>536</v>
       </c>
     </row>
     <row r="156" spans="1:5">
       <c r="A156" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="B156" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="C156" t="s">
-        <v>362</v>
+        <v>348</v>
       </c>
       <c r="D156" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="E156" t="s">
-        <v>529</v>
+        <v>508</v>
       </c>
     </row>
     <row r="157" spans="1:5">
       <c r="A157" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="B157" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="C157" t="s">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="D157" t="s">
-        <v>468</v>
+        <v>451</v>
       </c>
       <c r="E157" t="s">
-        <v>513</v>
+        <v>500</v>
       </c>
     </row>
     <row r="158" spans="1:5">
       <c r="A158" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="B158" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="C158" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="D158" t="s">
-        <v>455</v>
+        <v>437</v>
       </c>
       <c r="E158" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
     </row>
     <row r="159" spans="1:5">
       <c r="A159" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="B159" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C159" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="D159" t="s">
-        <v>416</v>
+        <v>425</v>
       </c>
       <c r="E159" t="s">
         <v>507</v>
@@ -4753,16 +4792,16 @@
     </row>
     <row r="160" spans="1:5">
       <c r="A160" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="B160" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C160" t="s">
-        <v>358</v>
+        <v>348</v>
       </c>
       <c r="D160" t="s">
-        <v>453</v>
+        <v>407</v>
       </c>
       <c r="E160" t="s">
         <v>508</v>
@@ -4770,2093 +4809,2654 @@
     </row>
     <row r="161" spans="1:5">
       <c r="A161" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="B161" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="C161" t="s">
-        <v>366</v>
+        <v>352</v>
       </c>
       <c r="D161" t="s">
-        <v>443</v>
+        <v>267</v>
       </c>
       <c r="E161" t="s">
-        <v>499</v>
+        <v>506</v>
       </c>
     </row>
     <row r="162" spans="1:5">
       <c r="A162" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="B162" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="C162" t="s">
-        <v>365</v>
+        <v>349</v>
       </c>
       <c r="D162" t="s">
-        <v>423</v>
+        <v>267</v>
       </c>
       <c r="E162" t="s">
-        <v>510</v>
+        <v>517</v>
       </c>
     </row>
     <row r="163" spans="1:5">
       <c r="A163" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="B163" t="s">
-        <v>216</v>
+        <v>180</v>
       </c>
       <c r="C163" t="s">
-        <v>367</v>
+        <v>353</v>
       </c>
       <c r="D163" t="s">
-        <v>266</v>
+        <v>431</v>
       </c>
       <c r="E163" t="s">
-        <v>504</v>
+        <v>537</v>
       </c>
     </row>
     <row r="164" spans="1:5">
       <c r="A164" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="B164" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="C164" t="s">
-        <v>368</v>
+        <v>342</v>
       </c>
       <c r="D164" t="s">
-        <v>457</v>
+        <v>267</v>
       </c>
       <c r="E164" t="s">
-        <v>512</v>
+        <v>501</v>
       </c>
     </row>
     <row r="165" spans="1:5">
       <c r="A165" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="B165" t="s">
-        <v>217</v>
+        <v>204</v>
       </c>
       <c r="C165" t="s">
-        <v>369</v>
+        <v>353</v>
       </c>
       <c r="D165" t="s">
-        <v>423</v>
+        <v>452</v>
       </c>
       <c r="E165" t="s">
-        <v>491</v>
+        <v>525</v>
       </c>
     </row>
     <row r="166" spans="1:5">
       <c r="A166" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="B166" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="C166" t="s">
-        <v>365</v>
+        <v>354</v>
       </c>
       <c r="D166" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="E166" t="s">
-        <v>494</v>
+        <v>484</v>
       </c>
     </row>
     <row r="167" spans="1:5">
       <c r="A167" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B167" t="s">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="C167" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D167" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="E167" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
     </row>
     <row r="168" spans="1:5">
       <c r="A168" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B168" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="C168" t="s">
-        <v>369</v>
+        <v>355</v>
       </c>
       <c r="D168" t="s">
-        <v>469</v>
+        <v>267</v>
       </c>
       <c r="E168" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="169" spans="1:5">
       <c r="A169" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="B169" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="C169" t="s">
-        <v>370</v>
+        <v>336</v>
       </c>
       <c r="D169" t="s">
-        <v>276</v>
+        <v>420</v>
       </c>
       <c r="E169" t="s">
-        <v>491</v>
+        <v>520</v>
       </c>
     </row>
     <row r="170" spans="1:5">
       <c r="A170" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="B170" t="s">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="C170" t="s">
-        <v>371</v>
+        <v>356</v>
       </c>
       <c r="D170" t="s">
-        <v>276</v>
+        <v>453</v>
       </c>
       <c r="E170" t="s">
-        <v>512</v>
+        <v>503</v>
       </c>
     </row>
     <row r="171" spans="1:5">
       <c r="A171" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="B171" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="C171" t="s">
-        <v>371</v>
+        <v>352</v>
       </c>
       <c r="D171" t="s">
-        <v>276</v>
+        <v>435</v>
       </c>
       <c r="E171" t="s">
-        <v>530</v>
+        <v>481</v>
       </c>
     </row>
     <row r="172" spans="1:5">
       <c r="A172" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="B172" t="s">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="C172" t="s">
-        <v>338</v>
+        <v>351</v>
       </c>
       <c r="D172" t="s">
-        <v>276</v>
+        <v>454</v>
       </c>
       <c r="E172" t="s">
-        <v>531</v>
+        <v>538</v>
       </c>
     </row>
     <row r="173" spans="1:5">
       <c r="A173" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="B173" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="C173" t="s">
-        <v>372</v>
+        <v>353</v>
       </c>
       <c r="D173" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="E173" t="s">
-        <v>491</v>
+        <v>539</v>
       </c>
     </row>
     <row r="174" spans="1:5">
       <c r="A174" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="B174" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="C174" t="s">
-        <v>316</v>
+        <v>356</v>
       </c>
       <c r="D174" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="E174" t="s">
-        <v>510</v>
+        <v>540</v>
       </c>
     </row>
     <row r="175" spans="1:5">
       <c r="A175" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="B175" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="C175" t="s">
-        <v>366</v>
+        <v>336</v>
       </c>
       <c r="D175" t="s">
-        <v>276</v>
+        <v>445</v>
       </c>
       <c r="E175" t="s">
-        <v>499</v>
+        <v>539</v>
       </c>
     </row>
     <row r="176" spans="1:5">
       <c r="A176" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="B176" t="s">
-        <v>225</v>
+        <v>195</v>
       </c>
       <c r="C176" t="s">
-        <v>367</v>
+        <v>346</v>
       </c>
       <c r="D176" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="E176" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
     </row>
     <row r="177" spans="1:5">
       <c r="A177" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="B177" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="C177" t="s">
-        <v>373</v>
+        <v>356</v>
       </c>
       <c r="D177" t="s">
-        <v>276</v>
+        <v>404</v>
       </c>
       <c r="E177" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
     </row>
     <row r="178" spans="1:5">
       <c r="A178" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="B178" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="C178" t="s">
-        <v>319</v>
+        <v>356</v>
       </c>
       <c r="D178" t="s">
-        <v>440</v>
+        <v>405</v>
       </c>
       <c r="E178" t="s">
-        <v>510</v>
+        <v>500</v>
       </c>
     </row>
     <row r="179" spans="1:5">
       <c r="A179" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="B179" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="C179" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="D179" t="s">
-        <v>470</v>
+        <v>455</v>
       </c>
       <c r="E179" t="s">
-        <v>499</v>
+        <v>481</v>
       </c>
     </row>
     <row r="180" spans="1:5">
       <c r="A180" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="B180" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="C180" t="s">
-        <v>374</v>
+        <v>358</v>
       </c>
       <c r="D180" t="s">
-        <v>428</v>
+        <v>267</v>
       </c>
       <c r="E180" t="s">
-        <v>508</v>
+        <v>520</v>
       </c>
     </row>
     <row r="181" spans="1:5">
       <c r="A181" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="B181" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="C181" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="D181" t="s">
-        <v>471</v>
+        <v>456</v>
       </c>
       <c r="E181" t="s">
-        <v>496</v>
+        <v>541</v>
       </c>
     </row>
     <row r="182" spans="1:5">
       <c r="A182" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="B182" t="s">
-        <v>229</v>
+        <v>207</v>
       </c>
       <c r="C182" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D182" t="s">
-        <v>430</v>
+        <v>267</v>
       </c>
       <c r="E182" t="s">
-        <v>504</v>
+        <v>514</v>
       </c>
     </row>
     <row r="183" spans="1:5">
       <c r="A183" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="B183" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
       <c r="C183" t="s">
-        <v>375</v>
+        <v>359</v>
       </c>
       <c r="D183" t="s">
-        <v>159</v>
+        <v>415</v>
       </c>
       <c r="E183" t="s">
-        <v>501</v>
+        <v>515</v>
       </c>
     </row>
     <row r="184" spans="1:5">
       <c r="A184" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="B184" t="s">
-        <v>231</v>
+        <v>218</v>
       </c>
       <c r="C184" t="s">
-        <v>376</v>
+        <v>360</v>
       </c>
       <c r="D184" t="s">
-        <v>276</v>
+        <v>442</v>
       </c>
       <c r="E184" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
     </row>
     <row r="185" spans="1:5">
       <c r="A185" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="B185" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="C185" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D185" t="s">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="E185" t="s">
-        <v>515</v>
+        <v>485</v>
       </c>
     </row>
     <row r="186" spans="1:5">
       <c r="A186" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="B186" t="s">
-        <v>232</v>
+        <v>209</v>
       </c>
       <c r="C186" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D186" t="s">
-        <v>419</v>
+        <v>436</v>
       </c>
       <c r="E186" t="s">
-        <v>496</v>
+        <v>542</v>
       </c>
     </row>
     <row r="187" spans="1:5">
       <c r="A187" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="B187" t="s">
-        <v>233</v>
+        <v>209</v>
       </c>
       <c r="C187" t="s">
-        <v>377</v>
+        <v>360</v>
       </c>
       <c r="D187" t="s">
-        <v>470</v>
+        <v>457</v>
       </c>
       <c r="E187" t="s">
-        <v>499</v>
+        <v>506</v>
       </c>
     </row>
     <row r="188" spans="1:5">
       <c r="A188" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="B188" t="s">
-        <v>196</v>
+        <v>219</v>
       </c>
       <c r="C188" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="D188" t="s">
-        <v>444</v>
+        <v>267</v>
       </c>
       <c r="E188" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
     </row>
     <row r="189" spans="1:5">
       <c r="A189" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="B189" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="C189" t="s">
-        <v>378</v>
+        <v>352</v>
       </c>
       <c r="D189" t="s">
-        <v>432</v>
+        <v>267</v>
       </c>
       <c r="E189" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="190" spans="1:5">
       <c r="A190" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="B190" t="s">
-        <v>234</v>
+        <v>220</v>
       </c>
       <c r="C190" t="s">
-        <v>379</v>
+        <v>362</v>
       </c>
       <c r="D190" t="s">
-        <v>472</v>
+        <v>267</v>
       </c>
       <c r="E190" t="s">
-        <v>486</v>
+        <v>507</v>
       </c>
     </row>
     <row r="191" spans="1:5">
       <c r="A191" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="B191" t="s">
-        <v>235</v>
+        <v>188</v>
       </c>
       <c r="C191" t="s">
-        <v>356</v>
+        <v>340</v>
       </c>
       <c r="D191" t="s">
-        <v>424</v>
+        <v>267</v>
       </c>
       <c r="E191" t="s">
-        <v>532</v>
+        <v>508</v>
       </c>
     </row>
     <row r="192" spans="1:5">
       <c r="A192" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="B192" t="s">
-        <v>236</v>
+        <v>220</v>
       </c>
       <c r="C192" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="D192" t="s">
-        <v>149</v>
+        <v>267</v>
       </c>
       <c r="E192" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="193" spans="1:5">
       <c r="A193" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="B193" t="s">
-        <v>237</v>
+        <v>221</v>
       </c>
       <c r="C193" t="s">
-        <v>380</v>
+        <v>363</v>
       </c>
       <c r="D193" t="s">
-        <v>473</v>
+        <v>267</v>
       </c>
       <c r="E193" t="s">
-        <v>486</v>
+        <v>506</v>
       </c>
     </row>
     <row r="194" spans="1:5">
       <c r="A194" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="B194" t="s">
-        <v>238</v>
+        <v>178</v>
       </c>
       <c r="C194" t="s">
-        <v>365</v>
+        <v>334</v>
       </c>
       <c r="D194" t="s">
-        <v>472</v>
+        <v>267</v>
       </c>
       <c r="E194" t="s">
-        <v>533</v>
+        <v>495</v>
       </c>
     </row>
     <row r="195" spans="1:5">
       <c r="A195" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="B195" t="s">
-        <v>238</v>
+        <v>222</v>
       </c>
       <c r="C195" t="s">
-        <v>377</v>
+        <v>305</v>
       </c>
       <c r="D195" t="s">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="E195" t="s">
-        <v>483</v>
+        <v>503</v>
       </c>
     </row>
     <row r="196" spans="1:5">
       <c r="A196" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="B196" t="s">
-        <v>239</v>
+        <v>223</v>
       </c>
       <c r="C196" t="s">
-        <v>381</v>
+        <v>363</v>
       </c>
       <c r="D196" t="s">
-        <v>276</v>
+        <v>162</v>
       </c>
       <c r="E196" t="s">
-        <v>505</v>
+        <v>481</v>
       </c>
     </row>
     <row r="197" spans="1:5">
       <c r="A197" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="B197" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="C197" t="s">
-        <v>365</v>
+        <v>336</v>
       </c>
       <c r="D197" t="s">
-        <v>276</v>
+        <v>408</v>
       </c>
       <c r="E197" t="s">
-        <v>534</v>
+        <v>520</v>
       </c>
     </row>
     <row r="198" spans="1:5">
       <c r="A198" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="B198" t="s">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="C198" t="s">
-        <v>369</v>
+        <v>303</v>
       </c>
       <c r="D198" t="s">
-        <v>472</v>
+        <v>267</v>
       </c>
       <c r="E198" t="s">
-        <v>535</v>
+        <v>514</v>
       </c>
     </row>
     <row r="199" spans="1:5">
       <c r="A199" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="B199" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="C199" t="s">
-        <v>382</v>
+        <v>310</v>
       </c>
       <c r="D199" t="s">
-        <v>276</v>
+        <v>458</v>
       </c>
       <c r="E199" t="s">
-        <v>486</v>
+        <v>543</v>
       </c>
     </row>
     <row r="200" spans="1:5">
       <c r="A200" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="B200" t="s">
-        <v>242</v>
+        <v>204</v>
       </c>
       <c r="C200" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="D200" t="s">
-        <v>276</v>
+        <v>459</v>
       </c>
       <c r="E200" t="s">
-        <v>536</v>
+        <v>501</v>
       </c>
     </row>
     <row r="201" spans="1:5">
       <c r="A201" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="B201" t="s">
-        <v>243</v>
+        <v>223</v>
       </c>
       <c r="C201" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="D201" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="E201" t="s">
-        <v>483</v>
+        <v>520</v>
       </c>
     </row>
     <row r="202" spans="1:5">
       <c r="A202" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="B202" t="s">
-        <v>244</v>
+        <v>227</v>
       </c>
       <c r="C202" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
       <c r="D202" t="s">
-        <v>458</v>
+        <v>412</v>
       </c>
       <c r="E202" t="s">
-        <v>501</v>
+        <v>481</v>
       </c>
     </row>
     <row r="203" spans="1:5">
       <c r="A203" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="B203" t="s">
-        <v>245</v>
+        <v>228</v>
       </c>
       <c r="C203" t="s">
-        <v>353</v>
+        <v>366</v>
       </c>
       <c r="D203" t="s">
-        <v>432</v>
+        <v>266</v>
       </c>
       <c r="E203" t="s">
-        <v>494</v>
+        <v>484</v>
       </c>
     </row>
     <row r="204" spans="1:5">
       <c r="A204" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="B204" t="s">
-        <v>203</v>
+        <v>228</v>
       </c>
       <c r="C204" t="s">
-        <v>357</v>
+        <v>367</v>
       </c>
       <c r="D204" t="s">
-        <v>474</v>
+        <v>433</v>
       </c>
       <c r="E204" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="205" spans="1:5">
       <c r="A205" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="B205" t="s">
-        <v>246</v>
+        <v>229</v>
       </c>
       <c r="C205" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="D205" t="s">
-        <v>419</v>
+        <v>267</v>
       </c>
       <c r="E205" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
     </row>
     <row r="206" spans="1:5">
       <c r="A206" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="B206" t="s">
-        <v>199</v>
+        <v>230</v>
       </c>
       <c r="C206" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="D206" t="s">
-        <v>453</v>
+        <v>460</v>
       </c>
       <c r="E206" t="s">
-        <v>499</v>
+        <v>484</v>
       </c>
     </row>
     <row r="207" spans="1:5">
       <c r="A207" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="B207" t="s">
-        <v>247</v>
+        <v>193</v>
       </c>
       <c r="C207" t="s">
-        <v>357</v>
+        <v>346</v>
       </c>
       <c r="D207" t="s">
-        <v>475</v>
+        <v>251</v>
       </c>
       <c r="E207" t="s">
-        <v>494</v>
+        <v>512</v>
       </c>
     </row>
     <row r="208" spans="1:5">
       <c r="A208" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="B208" t="s">
-        <v>248</v>
+        <v>194</v>
       </c>
       <c r="C208" t="s">
-        <v>384</v>
+        <v>346</v>
       </c>
       <c r="D208" t="s">
-        <v>440</v>
+        <v>425</v>
       </c>
       <c r="E208" t="s">
-        <v>512</v>
+        <v>533</v>
       </c>
     </row>
     <row r="209" spans="1:5">
       <c r="A209" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="B209" t="s">
-        <v>248</v>
+        <v>217</v>
       </c>
       <c r="C209" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="D209" t="s">
-        <v>266</v>
+        <v>461</v>
       </c>
       <c r="E209" t="s">
-        <v>537</v>
+        <v>501</v>
       </c>
     </row>
     <row r="210" spans="1:5">
       <c r="A210" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="B210" t="s">
-        <v>248</v>
+        <v>231</v>
       </c>
       <c r="C210" t="s">
-        <v>385</v>
+        <v>368</v>
       </c>
       <c r="D210" t="s">
-        <v>426</v>
+        <v>267</v>
       </c>
       <c r="E210" t="s">
-        <v>501</v>
+        <v>514</v>
       </c>
     </row>
     <row r="211" spans="1:5">
       <c r="A211" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="B211" t="s">
-        <v>212</v>
+        <v>193</v>
       </c>
       <c r="C211" t="s">
-        <v>357</v>
+        <v>346</v>
       </c>
       <c r="D211" t="s">
-        <v>468</v>
+        <v>251</v>
       </c>
       <c r="E211" t="s">
-        <v>538</v>
+        <v>520</v>
       </c>
     </row>
     <row r="212" spans="1:5">
       <c r="A212" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="B212" t="s">
-        <v>212</v>
+        <v>193</v>
       </c>
       <c r="C212" t="s">
-        <v>353</v>
+        <v>364</v>
       </c>
       <c r="D212" t="s">
-        <v>150</v>
+        <v>420</v>
       </c>
       <c r="E212" t="s">
-        <v>505</v>
+        <v>481</v>
       </c>
     </row>
     <row r="213" spans="1:5">
       <c r="A213" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="B213" t="s">
-        <v>212</v>
+        <v>232</v>
       </c>
       <c r="C213" t="s">
-        <v>381</v>
+        <v>343</v>
       </c>
       <c r="D213" t="s">
-        <v>476</v>
+        <v>462</v>
       </c>
       <c r="E213" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
     </row>
     <row r="214" spans="1:5">
       <c r="A214" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="B214" t="s">
-        <v>249</v>
+        <v>230</v>
       </c>
       <c r="C214" t="s">
-        <v>383</v>
+        <v>346</v>
       </c>
       <c r="D214" t="s">
-        <v>454</v>
+        <v>432</v>
       </c>
       <c r="E214" t="s">
-        <v>539</v>
+        <v>494</v>
       </c>
     </row>
     <row r="215" spans="1:5">
       <c r="A215" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="B215" t="s">
-        <v>250</v>
+        <v>231</v>
       </c>
       <c r="C215" t="s">
-        <v>384</v>
+        <v>368</v>
       </c>
       <c r="D215" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="E215" t="s">
-        <v>512</v>
+        <v>544</v>
       </c>
     </row>
     <row r="216" spans="1:5">
       <c r="A216" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="B216" t="s">
-        <v>220</v>
+        <v>233</v>
       </c>
       <c r="C216" t="s">
-        <v>370</v>
+        <v>341</v>
       </c>
       <c r="D216" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="E216" t="s">
-        <v>491</v>
+        <v>545</v>
       </c>
     </row>
     <row r="217" spans="1:5">
       <c r="A217" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="B217" t="s">
-        <v>199</v>
+        <v>234</v>
       </c>
       <c r="C217" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D217" t="s">
-        <v>416</v>
+        <v>252</v>
       </c>
       <c r="E217" t="s">
-        <v>494</v>
+        <v>546</v>
       </c>
     </row>
     <row r="218" spans="1:5">
       <c r="A218" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="B218" t="s">
-        <v>251</v>
+        <v>234</v>
       </c>
       <c r="C218" t="s">
-        <v>357</v>
+        <v>369</v>
       </c>
       <c r="D218" t="s">
-        <v>477</v>
+        <v>450</v>
       </c>
       <c r="E218" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
     </row>
     <row r="219" spans="1:5">
       <c r="A219" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="B219" t="s">
+        <v>235</v>
+      </c>
+      <c r="C219" t="s">
+        <v>360</v>
+      </c>
+      <c r="D219" t="s">
         <v>252</v>
       </c>
-      <c r="C219" t="s">
-        <v>386</v>
-      </c>
-      <c r="D219" t="s">
-        <v>276</v>
-      </c>
       <c r="E219" t="s">
-        <v>496</v>
+        <v>547</v>
       </c>
     </row>
     <row r="220" spans="1:5">
       <c r="A220" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="B220" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C220" t="s">
-        <v>381</v>
+        <v>356</v>
       </c>
       <c r="D220" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="E220" t="s">
-        <v>508</v>
+        <v>548</v>
       </c>
     </row>
     <row r="221" spans="1:5">
       <c r="A221" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="B221" t="s">
-        <v>215</v>
+        <v>237</v>
       </c>
       <c r="C221" t="s">
-        <v>365</v>
+        <v>336</v>
       </c>
       <c r="D221" t="s">
-        <v>423</v>
+        <v>267</v>
       </c>
       <c r="E221" t="s">
-        <v>507</v>
+        <v>544</v>
       </c>
     </row>
     <row r="222" spans="1:5">
       <c r="A222" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="B222" t="s">
-        <v>253</v>
+        <v>199</v>
       </c>
       <c r="C222" t="s">
-        <v>319</v>
+        <v>342</v>
       </c>
       <c r="D222" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="E222" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="223" spans="1:5">
       <c r="A223" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="B223" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="C223" t="s">
-        <v>357</v>
+        <v>370</v>
       </c>
       <c r="D223" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="E223" t="s">
-        <v>507</v>
+        <v>484</v>
       </c>
     </row>
     <row r="224" spans="1:5">
       <c r="A224" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="B224" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="C224" t="s">
-        <v>321</v>
+        <v>353</v>
       </c>
       <c r="D224" t="s">
-        <v>453</v>
+        <v>423</v>
       </c>
       <c r="E224" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
     </row>
     <row r="225" spans="1:5">
       <c r="A225" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="B225" t="s">
-        <v>242</v>
+        <v>201</v>
       </c>
       <c r="C225" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D225" t="s">
-        <v>276</v>
+        <v>463</v>
       </c>
       <c r="E225" t="s">
-        <v>512</v>
+        <v>503</v>
       </c>
     </row>
     <row r="226" spans="1:5">
       <c r="A226" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="B226" t="s">
-        <v>148</v>
+        <v>201</v>
       </c>
       <c r="C226" t="s">
-        <v>301</v>
+        <v>353</v>
       </c>
       <c r="D226" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="E226" t="s">
-        <v>508</v>
+        <v>520</v>
       </c>
     </row>
     <row r="227" spans="1:5">
       <c r="A227" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="B227" t="s">
-        <v>254</v>
+        <v>240</v>
       </c>
       <c r="C227" t="s">
-        <v>228</v>
+        <v>360</v>
       </c>
       <c r="D227" t="s">
-        <v>276</v>
+        <v>458</v>
       </c>
       <c r="E227" t="s">
-        <v>505</v>
+        <v>481</v>
       </c>
     </row>
     <row r="228" spans="1:5">
       <c r="A228" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="B228" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="C228" t="s">
-        <v>221</v>
+        <v>336</v>
       </c>
       <c r="D228" t="s">
-        <v>471</v>
+        <v>427</v>
       </c>
       <c r="E228" t="s">
-        <v>524</v>
+        <v>505</v>
       </c>
     </row>
     <row r="229" spans="1:5">
       <c r="A229" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="B229" t="s">
-        <v>256</v>
+        <v>242</v>
       </c>
       <c r="C229" t="s">
-        <v>387</v>
+        <v>356</v>
       </c>
       <c r="D229" t="s">
-        <v>463</v>
+        <v>421</v>
       </c>
       <c r="E229" t="s">
-        <v>505</v>
+        <v>529</v>
       </c>
     </row>
     <row r="230" spans="1:5">
       <c r="A230" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="B230" t="s">
-        <v>257</v>
+        <v>243</v>
       </c>
       <c r="C230" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="D230" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="E230" t="s">
-        <v>540</v>
+        <v>506</v>
       </c>
     </row>
     <row r="231" spans="1:5">
       <c r="A231" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="B231" t="s">
-        <v>235</v>
+        <v>210</v>
       </c>
       <c r="C231" t="s">
-        <v>377</v>
+        <v>353</v>
       </c>
       <c r="D231" t="s">
-        <v>477</v>
+        <v>404</v>
       </c>
       <c r="E231" t="s">
-        <v>505</v>
+        <v>492</v>
       </c>
     </row>
     <row r="232" spans="1:5">
       <c r="A232" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="B232" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="C232" t="s">
-        <v>389</v>
+        <v>353</v>
       </c>
       <c r="D232" t="s">
-        <v>478</v>
+        <v>441</v>
       </c>
       <c r="E232" t="s">
-        <v>499</v>
+        <v>522</v>
       </c>
     </row>
     <row r="233" spans="1:5">
       <c r="A233" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="B233" t="s">
-        <v>239</v>
+        <v>227</v>
       </c>
       <c r="C233" t="s">
-        <v>381</v>
+        <v>371</v>
       </c>
       <c r="D233" t="s">
-        <v>276</v>
+        <v>458</v>
       </c>
       <c r="E233" t="s">
-        <v>541</v>
+        <v>549</v>
       </c>
     </row>
     <row r="234" spans="1:5">
       <c r="A234" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="B234" t="s">
-        <v>243</v>
+        <v>227</v>
       </c>
       <c r="C234" t="s">
-        <v>358</v>
+        <v>372</v>
       </c>
       <c r="D234" t="s">
-        <v>276</v>
+        <v>464</v>
       </c>
       <c r="E234" t="s">
-        <v>483</v>
+        <v>508</v>
       </c>
     </row>
     <row r="235" spans="1:5">
       <c r="A235" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="B235" t="s">
-        <v>239</v>
+        <v>227</v>
       </c>
       <c r="C235" t="s">
-        <v>381</v>
+        <v>351</v>
       </c>
       <c r="D235" t="s">
-        <v>276</v>
+        <v>415</v>
       </c>
       <c r="E235" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
     </row>
     <row r="236" spans="1:5">
       <c r="A236" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="B236" t="s">
-        <v>148</v>
+        <v>233</v>
       </c>
       <c r="C236" t="s">
-        <v>305</v>
+        <v>341</v>
       </c>
       <c r="D236" t="s">
-        <v>429</v>
+        <v>267</v>
       </c>
       <c r="E236" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
     </row>
     <row r="237" spans="1:5">
       <c r="A237" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="B237" t="s">
-        <v>258</v>
+        <v>212</v>
       </c>
       <c r="C237" t="s">
-        <v>208</v>
+        <v>355</v>
       </c>
       <c r="D237" t="s">
-        <v>479</v>
+        <v>465</v>
       </c>
       <c r="E237" t="s">
-        <v>488</v>
+        <v>497</v>
       </c>
     </row>
     <row r="238" spans="1:5">
       <c r="A238" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="B238" t="s">
-        <v>167</v>
+        <v>212</v>
       </c>
       <c r="C238" t="s">
-        <v>242</v>
+        <v>358</v>
       </c>
       <c r="D238" t="s">
-        <v>276</v>
+        <v>466</v>
       </c>
       <c r="E238" t="s">
-        <v>496</v>
+        <v>489</v>
       </c>
     </row>
     <row r="239" spans="1:5">
       <c r="A239" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="B239" t="s">
-        <v>259</v>
+        <v>212</v>
       </c>
       <c r="C239" t="s">
-        <v>387</v>
+        <v>356</v>
       </c>
       <c r="D239" t="s">
-        <v>480</v>
+        <v>446</v>
       </c>
       <c r="E239" t="s">
-        <v>486</v>
+        <v>550</v>
       </c>
     </row>
     <row r="240" spans="1:5">
       <c r="A240" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="B240" t="s">
-        <v>260</v>
+        <v>213</v>
       </c>
       <c r="C240" t="s">
-        <v>390</v>
+        <v>373</v>
       </c>
       <c r="D240" t="s">
-        <v>481</v>
+        <v>443</v>
       </c>
       <c r="E240" t="s">
-        <v>504</v>
+        <v>485</v>
       </c>
     </row>
     <row r="241" spans="1:5">
       <c r="A241" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="B241" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
       <c r="C241" t="s">
-        <v>391</v>
+        <v>372</v>
       </c>
       <c r="D241" t="s">
-        <v>445</v>
+        <v>267</v>
       </c>
       <c r="E241" t="s">
-        <v>498</v>
+        <v>508</v>
       </c>
     </row>
     <row r="242" spans="1:5">
       <c r="A242" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="B242" t="s">
-        <v>262</v>
+        <v>245</v>
       </c>
       <c r="C242" t="s">
-        <v>392</v>
+        <v>371</v>
       </c>
       <c r="D242" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="E242" t="s">
-        <v>491</v>
+        <v>507</v>
       </c>
     </row>
     <row r="243" spans="1:5">
       <c r="A243" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="B243" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="C243" t="s">
-        <v>302</v>
+        <v>350</v>
       </c>
       <c r="D243" t="s">
-        <v>417</v>
+        <v>267</v>
       </c>
       <c r="E243" t="s">
-        <v>488</v>
+        <v>506</v>
       </c>
     </row>
     <row r="244" spans="1:5">
       <c r="A244" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="B244" t="s">
-        <v>263</v>
+        <v>214</v>
       </c>
       <c r="C244" t="s">
-        <v>393</v>
+        <v>356</v>
       </c>
       <c r="D244" t="s">
-        <v>275</v>
+        <v>405</v>
       </c>
       <c r="E244" t="s">
-        <v>486</v>
+        <v>551</v>
       </c>
     </row>
     <row r="245" spans="1:5">
       <c r="A245" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="B245" t="s">
-        <v>264</v>
+        <v>214</v>
       </c>
       <c r="C245" t="s">
-        <v>394</v>
+        <v>336</v>
       </c>
       <c r="D245" t="s">
-        <v>461</v>
+        <v>404</v>
       </c>
       <c r="E245" t="s">
-        <v>496</v>
+        <v>505</v>
       </c>
     </row>
     <row r="246" spans="1:5">
       <c r="A246" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="B246" t="s">
-        <v>265</v>
+        <v>247</v>
       </c>
       <c r="C246" t="s">
-        <v>395</v>
+        <v>336</v>
       </c>
       <c r="D246" t="s">
-        <v>474</v>
+        <v>405</v>
       </c>
       <c r="E246" t="s">
-        <v>504</v>
+        <v>539</v>
       </c>
     </row>
     <row r="247" spans="1:5">
       <c r="A247" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="B247" t="s">
-        <v>184</v>
+        <v>247</v>
       </c>
       <c r="C247" t="s">
-        <v>314</v>
+        <v>356</v>
       </c>
       <c r="D247" t="s">
-        <v>431</v>
+        <v>464</v>
       </c>
       <c r="E247" t="s">
-        <v>498</v>
+        <v>538</v>
       </c>
     </row>
     <row r="248" spans="1:5">
       <c r="A248" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="B248" t="s">
-        <v>266</v>
+        <v>236</v>
       </c>
       <c r="C248" t="s">
-        <v>248</v>
+        <v>356</v>
       </c>
       <c r="D248" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="E248" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="249" spans="1:5">
       <c r="A249" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="B249" t="s">
-        <v>264</v>
+        <v>211</v>
       </c>
       <c r="C249" t="s">
-        <v>313</v>
+        <v>350</v>
       </c>
       <c r="D249" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="E249" t="s">
-        <v>488</v>
+        <v>501</v>
       </c>
     </row>
     <row r="250" spans="1:5">
       <c r="A250" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="B250" t="s">
-        <v>267</v>
+        <v>217</v>
       </c>
       <c r="C250" t="s">
-        <v>359</v>
+        <v>336</v>
       </c>
       <c r="D250" t="s">
-        <v>150</v>
+        <v>412</v>
       </c>
       <c r="E250" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
     </row>
     <row r="251" spans="1:5">
       <c r="A251" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="B251" t="s">
-        <v>268</v>
+        <v>217</v>
       </c>
       <c r="C251" t="s">
-        <v>396</v>
+        <v>355</v>
       </c>
       <c r="D251" t="s">
-        <v>441</v>
+        <v>456</v>
       </c>
       <c r="E251" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
     </row>
     <row r="252" spans="1:5">
       <c r="A252" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="B252" t="s">
-        <v>269</v>
+        <v>236</v>
       </c>
       <c r="C252" t="s">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="D252" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="E252" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="253" spans="1:5">
       <c r="A253" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="B253" t="s">
-        <v>270</v>
+        <v>237</v>
       </c>
       <c r="C253" t="s">
-        <v>397</v>
+        <v>336</v>
       </c>
       <c r="D253" t="s">
-        <v>434</v>
+        <v>267</v>
       </c>
       <c r="E253" t="s">
-        <v>486</v>
+        <v>499</v>
       </c>
     </row>
     <row r="254" spans="1:5">
       <c r="A254" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="B254" t="s">
-        <v>171</v>
+        <v>236</v>
       </c>
       <c r="C254" t="s">
-        <v>373</v>
+        <v>356</v>
       </c>
       <c r="D254" t="s">
-        <v>465</v>
+        <v>267</v>
       </c>
       <c r="E254" t="s">
-        <v>488</v>
+        <v>515</v>
       </c>
     </row>
     <row r="255" spans="1:5">
       <c r="A255" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="B255" t="s">
-        <v>227</v>
+        <v>248</v>
       </c>
       <c r="C255" t="s">
-        <v>398</v>
+        <v>363</v>
       </c>
       <c r="D255" t="s">
-        <v>259</v>
+        <v>462</v>
       </c>
       <c r="E255" t="s">
-        <v>496</v>
+        <v>506</v>
       </c>
     </row>
     <row r="256" spans="1:5">
       <c r="A256" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="B256" t="s">
-        <v>271</v>
+        <v>139</v>
       </c>
       <c r="C256" t="s">
-        <v>399</v>
+        <v>284</v>
       </c>
       <c r="D256" t="s">
-        <v>423</v>
+        <v>465</v>
       </c>
       <c r="E256" t="s">
-        <v>498</v>
+        <v>489</v>
       </c>
     </row>
     <row r="257" spans="1:5">
       <c r="A257" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="B257" t="s">
-        <v>272</v>
+        <v>144</v>
       </c>
       <c r="C257" t="s">
-        <v>400</v>
+        <v>284</v>
       </c>
       <c r="D257" t="s">
-        <v>439</v>
+        <v>468</v>
       </c>
       <c r="E257" t="s">
-        <v>504</v>
+        <v>552</v>
       </c>
     </row>
     <row r="258" spans="1:5">
       <c r="A258" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="B258" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="C258" t="s">
-        <v>365</v>
+        <v>353</v>
       </c>
       <c r="D258" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="E258" t="s">
-        <v>486</v>
+        <v>553</v>
       </c>
     </row>
     <row r="259" spans="1:5">
       <c r="A259" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="B259" t="s">
-        <v>273</v>
+        <v>247</v>
       </c>
       <c r="C259" t="s">
-        <v>401</v>
+        <v>373</v>
       </c>
       <c r="D259" t="s">
-        <v>435</v>
+        <v>469</v>
       </c>
       <c r="E259" t="s">
-        <v>496</v>
+        <v>509</v>
       </c>
     </row>
     <row r="260" spans="1:5">
       <c r="A260" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="B260" t="s">
-        <v>274</v>
+        <v>216</v>
       </c>
       <c r="C260" t="s">
-        <v>402</v>
+        <v>358</v>
       </c>
       <c r="D260" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="E260" t="s">
-        <v>504</v>
+        <v>554</v>
       </c>
     </row>
     <row r="261" spans="1:5">
       <c r="A261" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="B261" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="C261" t="s">
-        <v>386</v>
+        <v>356</v>
       </c>
       <c r="D261" t="s">
-        <v>482</v>
+        <v>461</v>
       </c>
       <c r="E261" t="s">
-        <v>496</v>
+        <v>555</v>
       </c>
     </row>
     <row r="262" spans="1:5">
       <c r="A262" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="B262" t="s">
-        <v>274</v>
+        <v>217</v>
       </c>
       <c r="C262" t="s">
-        <v>402</v>
+        <v>336</v>
       </c>
       <c r="D262" t="s">
-        <v>276</v>
+        <v>412</v>
       </c>
       <c r="E262" t="s">
-        <v>504</v>
+        <v>556</v>
       </c>
     </row>
     <row r="263" spans="1:5">
       <c r="A263" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="B263" t="s">
-        <v>275</v>
+        <v>216</v>
       </c>
       <c r="C263" t="s">
-        <v>243</v>
+        <v>358</v>
       </c>
       <c r="D263" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="E263" t="s">
-        <v>543</v>
+        <v>514</v>
       </c>
     </row>
     <row r="264" spans="1:5">
       <c r="A264" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="B264" t="s">
-        <v>275</v>
+        <v>236</v>
       </c>
       <c r="C264" t="s">
-        <v>243</v>
+        <v>356</v>
       </c>
       <c r="D264" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="E264" t="s">
-        <v>544</v>
+        <v>557</v>
       </c>
     </row>
     <row r="265" spans="1:5">
       <c r="A265" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="B265" t="s">
-        <v>276</v>
+        <v>249</v>
       </c>
       <c r="C265" t="s">
-        <v>250</v>
+        <v>374</v>
       </c>
       <c r="D265" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="E265" t="s">
-        <v>545</v>
+        <v>508</v>
       </c>
     </row>
     <row r="266" spans="1:5">
       <c r="A266" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="B266" t="s">
-        <v>275</v>
+        <v>170</v>
       </c>
       <c r="C266" t="s">
-        <v>243</v>
+        <v>375</v>
       </c>
       <c r="D266" t="s">
-        <v>276</v>
+        <v>456</v>
       </c>
       <c r="E266" t="s">
-        <v>546</v>
+        <v>506</v>
       </c>
     </row>
     <row r="267" spans="1:5">
       <c r="A267" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="B267" t="s">
-        <v>276</v>
+        <v>250</v>
       </c>
       <c r="C267" t="s">
-        <v>403</v>
+        <v>376</v>
       </c>
       <c r="D267" t="s">
-        <v>276</v>
+        <v>449</v>
       </c>
       <c r="E267" t="s">
-        <v>547</v>
+        <v>487</v>
       </c>
     </row>
     <row r="268" spans="1:5">
       <c r="A268" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="B268" t="s">
-        <v>275</v>
+        <v>251</v>
       </c>
       <c r="C268" t="s">
-        <v>243</v>
+        <v>377</v>
       </c>
       <c r="D268" t="s">
-        <v>276</v>
+        <v>440</v>
       </c>
       <c r="E268" t="s">
-        <v>548</v>
+        <v>492</v>
       </c>
     </row>
     <row r="269" spans="1:5">
       <c r="A269" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="B269" t="s">
-        <v>277</v>
+        <v>252</v>
       </c>
       <c r="C269" t="s">
-        <v>250</v>
+        <v>378</v>
       </c>
       <c r="D269" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="E269" t="s">
-        <v>540</v>
+        <v>481</v>
       </c>
     </row>
     <row r="270" spans="1:5">
       <c r="A270" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="B270" t="s">
-        <v>275</v>
+        <v>253</v>
       </c>
       <c r="C270" t="s">
-        <v>243</v>
+        <v>379</v>
       </c>
       <c r="D270" t="s">
-        <v>276</v>
+        <v>456</v>
       </c>
       <c r="E270" t="s">
-        <v>549</v>
+        <v>501</v>
       </c>
     </row>
     <row r="271" spans="1:5">
       <c r="A271" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="B271" t="s">
-        <v>275</v>
+        <v>254</v>
       </c>
       <c r="C271" t="s">
-        <v>243</v>
+        <v>335</v>
       </c>
       <c r="D271" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="E271" t="s">
-        <v>550</v>
+        <v>505</v>
       </c>
     </row>
     <row r="272" spans="1:5">
       <c r="A272" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="B272" t="s">
-        <v>278</v>
+        <v>255</v>
       </c>
       <c r="C272" t="s">
-        <v>280</v>
+        <v>380</v>
       </c>
       <c r="D272" t="s">
-        <v>276</v>
+        <v>401</v>
       </c>
       <c r="E272" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
     </row>
     <row r="273" spans="1:5">
       <c r="A273" t="s">
-        <v>128</v>
+        <v>113</v>
       </c>
       <c r="B273" t="s">
-        <v>275</v>
+        <v>206</v>
       </c>
       <c r="C273" t="s">
-        <v>243</v>
+        <v>371</v>
       </c>
       <c r="D273" t="s">
-        <v>276</v>
+        <v>470</v>
       </c>
       <c r="E273" t="s">
-        <v>551</v>
+        <v>484</v>
       </c>
     </row>
     <row r="274" spans="1:5">
       <c r="A274" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="B274" t="s">
-        <v>275</v>
+        <v>256</v>
       </c>
       <c r="C274" t="s">
-        <v>243</v>
+        <v>381</v>
       </c>
       <c r="D274" t="s">
-        <v>276</v>
+        <v>401</v>
       </c>
       <c r="E274" t="s">
-        <v>552</v>
+        <v>508</v>
       </c>
     </row>
     <row r="275" spans="1:5">
       <c r="A275" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="B275" t="s">
-        <v>279</v>
+        <v>151</v>
       </c>
       <c r="C275" t="s">
-        <v>180</v>
+        <v>382</v>
       </c>
       <c r="D275" t="s">
-        <v>276</v>
+        <v>456</v>
       </c>
       <c r="E275" t="s">
-        <v>553</v>
+        <v>506</v>
       </c>
     </row>
     <row r="276" spans="1:5">
       <c r="A276" t="s">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="B276" t="s">
-        <v>176</v>
+        <v>257</v>
       </c>
       <c r="C276" t="s">
-        <v>404</v>
+        <v>383</v>
       </c>
       <c r="D276" t="s">
-        <v>276</v>
+        <v>446</v>
       </c>
       <c r="E276" t="s">
-        <v>554</v>
+        <v>492</v>
       </c>
     </row>
     <row r="277" spans="1:5">
       <c r="A277" t="s">
-        <v>132</v>
+        <v>114</v>
       </c>
       <c r="B277" t="s">
-        <v>280</v>
+        <v>167</v>
       </c>
       <c r="C277" t="s">
-        <v>405</v>
+        <v>384</v>
       </c>
       <c r="D277" t="s">
-        <v>276</v>
+        <v>449</v>
       </c>
       <c r="E277" t="s">
-        <v>553</v>
+        <v>487</v>
       </c>
     </row>
     <row r="278" spans="1:5">
       <c r="A278" t="s">
-        <v>133</v>
+        <v>114</v>
       </c>
       <c r="B278" t="s">
-        <v>275</v>
+        <v>178</v>
       </c>
       <c r="C278" t="s">
-        <v>243</v>
+        <v>334</v>
       </c>
       <c r="D278" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="E278" t="s">
-        <v>555</v>
+        <v>501</v>
       </c>
     </row>
     <row r="279" spans="1:5">
       <c r="A279" t="s">
-        <v>134</v>
+        <v>114</v>
       </c>
       <c r="B279" t="s">
-        <v>278</v>
+        <v>255</v>
       </c>
       <c r="C279" t="s">
-        <v>406</v>
+        <v>289</v>
       </c>
       <c r="D279" t="s">
-        <v>276</v>
+        <v>471</v>
       </c>
       <c r="E279" t="s">
-        <v>556</v>
+        <v>481</v>
       </c>
     </row>
     <row r="280" spans="1:5">
       <c r="A280" t="s">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="B280" t="s">
-        <v>275</v>
+        <v>193</v>
       </c>
       <c r="C280" t="s">
-        <v>243</v>
+        <v>361</v>
       </c>
       <c r="D280" t="s">
-        <v>276</v>
+        <v>400</v>
       </c>
       <c r="E280" t="s">
-        <v>556</v>
+        <v>505</v>
       </c>
     </row>
     <row r="281" spans="1:5">
       <c r="A281" t="s">
-        <v>136</v>
+        <v>114</v>
       </c>
       <c r="B281" t="s">
-        <v>276</v>
+        <v>258</v>
       </c>
       <c r="C281" t="s">
-        <v>403</v>
+        <v>369</v>
       </c>
       <c r="D281" t="s">
-        <v>276</v>
+        <v>468</v>
       </c>
       <c r="E281" t="s">
-        <v>540</v>
+        <v>488</v>
       </c>
     </row>
     <row r="282" spans="1:5">
       <c r="A282" t="s">
-        <v>136</v>
+        <v>115</v>
       </c>
       <c r="B282" t="s">
-        <v>281</v>
+        <v>170</v>
       </c>
       <c r="C282" t="s">
-        <v>407</v>
+        <v>193</v>
       </c>
       <c r="D282" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="E282" t="s">
-        <v>524</v>
+        <v>508</v>
       </c>
     </row>
     <row r="283" spans="1:5">
       <c r="A283" t="s">
-        <v>137</v>
+        <v>115</v>
       </c>
       <c r="B283" t="s">
-        <v>275</v>
+        <v>259</v>
       </c>
       <c r="C283" t="s">
-        <v>243</v>
+        <v>385</v>
       </c>
       <c r="D283" t="s">
-        <v>276</v>
+        <v>155</v>
       </c>
       <c r="E283" t="s">
-        <v>557</v>
+        <v>506</v>
+      </c>
+    </row>
+    <row r="284" spans="1:5">
+      <c r="A284" t="s">
+        <v>115</v>
+      </c>
+      <c r="B284" t="s">
+        <v>260</v>
+      </c>
+      <c r="C284" t="s">
+        <v>386</v>
+      </c>
+      <c r="D284" t="s">
+        <v>472</v>
+      </c>
+      <c r="E284" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="285" spans="1:5">
+      <c r="A285" t="s">
+        <v>115</v>
+      </c>
+      <c r="B285" t="s">
+        <v>205</v>
+      </c>
+      <c r="C285" t="s">
+        <v>354</v>
+      </c>
+      <c r="D285" t="s">
+        <v>267</v>
+      </c>
+      <c r="E285" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="286" spans="1:5">
+      <c r="A286" t="s">
+        <v>115</v>
+      </c>
+      <c r="B286" t="s">
+        <v>230</v>
+      </c>
+      <c r="C286" t="s">
+        <v>387</v>
+      </c>
+      <c r="D286" t="s">
+        <v>473</v>
+      </c>
+      <c r="E286" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="287" spans="1:5">
+      <c r="A287" t="s">
+        <v>115</v>
+      </c>
+      <c r="B287" t="s">
+        <v>261</v>
+      </c>
+      <c r="C287" t="s">
+        <v>345</v>
+      </c>
+      <c r="D287" t="s">
+        <v>250</v>
+      </c>
+      <c r="E287" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="288" spans="1:5">
+      <c r="A288" t="s">
+        <v>116</v>
+      </c>
+      <c r="B288" t="s">
+        <v>262</v>
+      </c>
+      <c r="C288" t="s">
+        <v>388</v>
+      </c>
+      <c r="D288" t="s">
+        <v>443</v>
+      </c>
+      <c r="E288" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="289" spans="1:5">
+      <c r="A289" t="s">
+        <v>116</v>
+      </c>
+      <c r="B289" t="s">
+        <v>159</v>
+      </c>
+      <c r="C289" t="s">
+        <v>389</v>
+      </c>
+      <c r="D289" t="s">
+        <v>449</v>
+      </c>
+      <c r="E289" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="290" spans="1:5">
+      <c r="A290" t="s">
+        <v>116</v>
+      </c>
+      <c r="B290" t="s">
+        <v>181</v>
+      </c>
+      <c r="C290" t="s">
+        <v>312</v>
+      </c>
+      <c r="D290" t="s">
+        <v>267</v>
+      </c>
+      <c r="E290" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="291" spans="1:5">
+      <c r="A291" t="s">
+        <v>116</v>
+      </c>
+      <c r="B291" t="s">
+        <v>263</v>
+      </c>
+      <c r="C291" t="s">
+        <v>352</v>
+      </c>
+      <c r="D291" t="s">
+        <v>474</v>
+      </c>
+      <c r="E291" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="292" spans="1:5">
+      <c r="A292" t="s">
+        <v>116</v>
+      </c>
+      <c r="B292" t="s">
+        <v>214</v>
+      </c>
+      <c r="C292" t="s">
+        <v>390</v>
+      </c>
+      <c r="D292" t="s">
+        <v>446</v>
+      </c>
+      <c r="E292" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="293" spans="1:5">
+      <c r="A293" t="s">
+        <v>117</v>
+      </c>
+      <c r="B293" t="s">
+        <v>264</v>
+      </c>
+      <c r="C293" t="s">
+        <v>391</v>
+      </c>
+      <c r="D293" t="s">
+        <v>267</v>
+      </c>
+      <c r="E293" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="294" spans="1:5">
+      <c r="A294" t="s">
+        <v>117</v>
+      </c>
+      <c r="B294" t="s">
+        <v>265</v>
+      </c>
+      <c r="C294" t="s">
+        <v>363</v>
+      </c>
+      <c r="D294" t="s">
+        <v>422</v>
+      </c>
+      <c r="E294" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="295" spans="1:5">
+      <c r="A295" t="s">
+        <v>117</v>
+      </c>
+      <c r="B295" t="s">
+        <v>220</v>
+      </c>
+      <c r="C295" t="s">
+        <v>390</v>
+      </c>
+      <c r="D295" t="s">
+        <v>415</v>
+      </c>
+      <c r="E295" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="296" spans="1:5">
+      <c r="A296" t="s">
+        <v>118</v>
+      </c>
+      <c r="B296" t="s">
+        <v>266</v>
+      </c>
+      <c r="C296" t="s">
+        <v>237</v>
+      </c>
+      <c r="D296" t="s">
+        <v>267</v>
+      </c>
+      <c r="E296" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="297" spans="1:5">
+      <c r="A297" t="s">
+        <v>119</v>
+      </c>
+      <c r="B297" t="s">
+        <v>267</v>
+      </c>
+      <c r="C297" t="s">
+        <v>392</v>
+      </c>
+      <c r="D297" t="s">
+        <v>267</v>
+      </c>
+      <c r="E297" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="298" spans="1:5">
+      <c r="A298" t="s">
+        <v>120</v>
+      </c>
+      <c r="B298" t="s">
+        <v>266</v>
+      </c>
+      <c r="C298" t="s">
+        <v>237</v>
+      </c>
+      <c r="D298" t="s">
+        <v>267</v>
+      </c>
+      <c r="E298" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="299" spans="1:5">
+      <c r="A299" t="s">
+        <v>121</v>
+      </c>
+      <c r="B299" t="s">
+        <v>267</v>
+      </c>
+      <c r="C299" t="s">
+        <v>245</v>
+      </c>
+      <c r="D299" t="s">
+        <v>267</v>
+      </c>
+      <c r="E299" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="300" spans="1:5">
+      <c r="A300" t="s">
+        <v>121</v>
+      </c>
+      <c r="B300" t="s">
+        <v>268</v>
+      </c>
+      <c r="C300" t="s">
+        <v>393</v>
+      </c>
+      <c r="D300" t="s">
+        <v>173</v>
+      </c>
+      <c r="E300" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="301" spans="1:5">
+      <c r="A301" t="s">
+        <v>122</v>
+      </c>
+      <c r="B301" t="s">
+        <v>266</v>
+      </c>
+      <c r="C301" t="s">
+        <v>237</v>
+      </c>
+      <c r="D301" t="s">
+        <v>267</v>
+      </c>
+      <c r="E301" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="302" spans="1:5">
+      <c r="A302" t="s">
+        <v>123</v>
+      </c>
+      <c r="B302" t="s">
+        <v>266</v>
+      </c>
+      <c r="C302" t="s">
+        <v>237</v>
+      </c>
+      <c r="D302" t="s">
+        <v>267</v>
+      </c>
+      <c r="E302" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="303" spans="1:5">
+      <c r="A303" t="s">
+        <v>124</v>
+      </c>
+      <c r="B303" t="s">
+        <v>267</v>
+      </c>
+      <c r="C303" t="s">
+        <v>392</v>
+      </c>
+      <c r="D303" t="s">
+        <v>267</v>
+      </c>
+      <c r="E303" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="304" spans="1:5">
+      <c r="A304" t="s">
+        <v>124</v>
+      </c>
+      <c r="B304" t="s">
+        <v>266</v>
+      </c>
+      <c r="C304" t="s">
+        <v>237</v>
+      </c>
+      <c r="D304" t="s">
+        <v>267</v>
+      </c>
+      <c r="E304" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="305" spans="1:5">
+      <c r="A305" t="s">
+        <v>125</v>
+      </c>
+      <c r="B305" t="s">
+        <v>266</v>
+      </c>
+      <c r="C305" t="s">
+        <v>237</v>
+      </c>
+      <c r="D305" t="s">
+        <v>428</v>
+      </c>
+      <c r="E305" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="306" spans="1:5">
+      <c r="A306" t="s">
+        <v>126</v>
+      </c>
+      <c r="B306" t="s">
+        <v>269</v>
+      </c>
+      <c r="C306" t="s">
+        <v>271</v>
+      </c>
+      <c r="D306" t="s">
+        <v>267</v>
+      </c>
+      <c r="E306" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="307" spans="1:5">
+      <c r="A307" t="s">
+        <v>127</v>
+      </c>
+      <c r="B307" t="s">
+        <v>266</v>
+      </c>
+      <c r="C307" t="s">
+        <v>237</v>
+      </c>
+      <c r="D307" t="s">
+        <v>267</v>
+      </c>
+      <c r="E307" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="308" spans="1:5">
+      <c r="A308" t="s">
+        <v>128</v>
+      </c>
+      <c r="B308" t="s">
+        <v>266</v>
+      </c>
+      <c r="C308" t="s">
+        <v>237</v>
+      </c>
+      <c r="D308" t="s">
+        <v>267</v>
+      </c>
+      <c r="E308" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="309" spans="1:5">
+      <c r="A309" t="s">
+        <v>129</v>
+      </c>
+      <c r="B309" t="s">
+        <v>270</v>
+      </c>
+      <c r="C309" t="s">
+        <v>178</v>
+      </c>
+      <c r="D309" t="s">
+        <v>267</v>
+      </c>
+      <c r="E309" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="310" spans="1:5">
+      <c r="A310" t="s">
+        <v>130</v>
+      </c>
+      <c r="B310" t="s">
+        <v>173</v>
+      </c>
+      <c r="C310" t="s">
+        <v>311</v>
+      </c>
+      <c r="D310" t="s">
+        <v>267</v>
+      </c>
+      <c r="E310" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="311" spans="1:5">
+      <c r="A311" t="s">
+        <v>131</v>
+      </c>
+      <c r="B311" t="s">
+        <v>271</v>
+      </c>
+      <c r="C311" t="s">
+        <v>394</v>
+      </c>
+      <c r="D311" t="s">
+        <v>267</v>
+      </c>
+      <c r="E311" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="312" spans="1:5">
+      <c r="A312" t="s">
+        <v>132</v>
+      </c>
+      <c r="B312" t="s">
+        <v>266</v>
+      </c>
+      <c r="C312" t="s">
+        <v>237</v>
+      </c>
+      <c r="D312" t="s">
+        <v>428</v>
+      </c>
+      <c r="E312" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="313" spans="1:5">
+      <c r="A313" t="s">
+        <v>133</v>
+      </c>
+      <c r="B313" t="s">
+        <v>269</v>
+      </c>
+      <c r="C313" t="s">
+        <v>395</v>
+      </c>
+      <c r="D313" t="s">
+        <v>267</v>
+      </c>
+      <c r="E313" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="314" spans="1:5">
+      <c r="A314" t="s">
+        <v>134</v>
+      </c>
+      <c r="B314" t="s">
+        <v>267</v>
+      </c>
+      <c r="C314" t="s">
+        <v>392</v>
+      </c>
+      <c r="D314" t="s">
+        <v>267</v>
+      </c>
+      <c r="E314" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="315" spans="1:5">
+      <c r="A315" t="s">
+        <v>134</v>
+      </c>
+      <c r="B315" t="s">
+        <v>272</v>
+      </c>
+      <c r="C315" t="s">
+        <v>396</v>
+      </c>
+      <c r="D315" t="s">
+        <v>267</v>
+      </c>
+      <c r="E315" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="316" spans="1:5">
+      <c r="A316" t="s">
+        <v>135</v>
+      </c>
+      <c r="B316" t="s">
+        <v>266</v>
+      </c>
+      <c r="C316" t="s">
+        <v>237</v>
+      </c>
+      <c r="D316" t="s">
+        <v>267</v>
+      </c>
+      <c r="E316" t="s">
+        <v>570</v>
       </c>
     </row>
   </sheetData>

--- a/data/TTC/班別時間對照表/TTC_TD_當月班別時間對照表.xlsx
+++ b/data/TTC/班別時間對照表/TTC_TD_當月班別時間對照表.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1580" uniqueCount="571">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1570" uniqueCount="558">
   <si>
     <t>班別代號</t>
   </si>
@@ -376,18 +376,6 @@
     <t>DSUI</t>
   </si>
   <si>
-    <t>DTT</t>
-  </si>
-  <si>
-    <t>DTT1</t>
-  </si>
-  <si>
-    <t>FAC</t>
-  </si>
-  <si>
-    <t>LUTS</t>
-  </si>
-  <si>
     <t>M</t>
   </si>
   <si>
@@ -400,9 +388,6 @@
     <t>OGT3</t>
   </si>
   <si>
-    <t>PAY</t>
-  </si>
-  <si>
     <t>STD1</t>
   </si>
   <si>
@@ -415,15 +400,9 @@
     <t>T</t>
   </si>
   <si>
-    <t>TOWN</t>
-  </si>
-  <si>
     <t>TTC1</t>
   </si>
   <si>
-    <t>WRSL</t>
-  </si>
-  <si>
     <t>3:59</t>
   </si>
   <si>
@@ -538,12 +517,18 @@
     <t>10:00</t>
   </si>
   <si>
+    <t>10:25</t>
+  </si>
+  <si>
     <t>10:35</t>
   </si>
   <si>
     <t>10:13</t>
   </si>
   <si>
+    <t>11:33</t>
+  </si>
+  <si>
     <t>4:52</t>
   </si>
   <si>
@@ -574,6 +559,9 @@
     <t>13:16</t>
   </si>
   <si>
+    <t>13:21</t>
+  </si>
+  <si>
     <t>13:15</t>
   </si>
   <si>
@@ -799,6 +787,9 @@
     <t>11:07</t>
   </si>
   <si>
+    <t>11:51</t>
+  </si>
+  <si>
     <t>15:53</t>
   </si>
   <si>
@@ -820,9 +811,6 @@
     <t>8:00</t>
   </si>
   <si>
-    <t>21:30</t>
-  </si>
-  <si>
     <t>7:30</t>
   </si>
   <si>
@@ -1006,6 +994,9 @@
     <t>19:18</t>
   </si>
   <si>
+    <t>19:33</t>
+  </si>
+  <si>
     <t>19:53</t>
   </si>
   <si>
@@ -1033,6 +1024,9 @@
     <t>22:22</t>
   </si>
   <si>
+    <t>22:56</t>
+  </si>
+  <si>
     <t>21:15</t>
   </si>
   <si>
@@ -1045,9 +1039,6 @@
     <t>23:03</t>
   </si>
   <si>
-    <t>22:56</t>
-  </si>
-  <si>
     <t>23:46</t>
   </si>
   <si>
@@ -1177,6 +1168,9 @@
     <t>19:08</t>
   </si>
   <si>
+    <t>19:51</t>
+  </si>
+  <si>
     <t>24:28</t>
   </si>
   <si>
@@ -1195,15 +1189,9 @@
     <t>16:00</t>
   </si>
   <si>
-    <t>31:30</t>
-  </si>
-  <si>
     <t>23:30</t>
   </si>
   <si>
-    <t>16:30</t>
-  </si>
-  <si>
     <t>21:00</t>
   </si>
   <si>
@@ -1363,6 +1351,9 @@
     <t>9:04</t>
   </si>
   <si>
+    <t>9:35</t>
+  </si>
+  <si>
     <t>8:10</t>
   </si>
   <si>
@@ -1402,6 +1393,9 @@
     <t>8:21</t>
   </si>
   <si>
+    <t>9:11</t>
+  </si>
+  <si>
     <t>8:28</t>
   </si>
   <si>
@@ -1444,28 +1438,28 @@
     <t>10/27(TUE), 10/28(WED)</t>
   </si>
   <si>
-    <t>10/13(TUE), 10/14(WED), 10/20(TUE), 10/21(WED), 10/6(TUE), 10/7(WED)</t>
-  </si>
-  <si>
-    <t>10/13(TUE), 10/14(WED), 10/20(TUE), 10/21(WED), 10/27(TUE), 10/28(WED), 10/6(TUE), 10/7(WED)</t>
-  </si>
-  <si>
-    <t>10/15(THU), 10/16(FRI), 10/22(THU), 10/29(THU), 10/30(FRI), 10/9(FRI)</t>
-  </si>
-  <si>
-    <t>10/23(FRI), 10/8(THU)</t>
-  </si>
-  <si>
-    <t>10/12(MON), 10/19(MON), 10/5(MON)</t>
+    <t>10/6(TUE), 10/7(WED), 10/13(TUE), 10/14(WED), 10/20(TUE), 10/21(WED)</t>
+  </si>
+  <si>
+    <t>10/6(TUE), 10/7(WED), 10/13(TUE), 10/14(WED), 10/20(TUE), 10/21(WED), 10/27(TUE), 10/28(WED)</t>
+  </si>
+  <si>
+    <t>10/9(FRI), 10/15(THU), 10/16(FRI), 10/22(THU), 10/29(THU), 10/30(FRI)</t>
+  </si>
+  <si>
+    <t>10/8(THU), 10/23(FRI)</t>
+  </si>
+  <si>
+    <t>10/5(MON), 10/12(MON), 10/19(MON)</t>
   </si>
   <si>
     <t>10/26(MON)</t>
   </si>
   <si>
-    <t>10/11(SUN), 10/12(MON), 10/18(SUN), 10/19(MON), 10/25(SUN), 10/4(SUN), 10/5(MON)</t>
-  </si>
-  <si>
-    <t>10/16(FRI), 10/30(FRI), 10/9(FRI)</t>
+    <t>10/4(SUN), 10/5(MON), 10/11(SUN), 10/12(MON), 10/18(SUN), 10/19(MON), 10/25(SUN)</t>
+  </si>
+  <si>
+    <t>10/9(FRI), 10/16(FRI), 10/30(FRI)</t>
   </si>
   <si>
     <t>10/23(FRI)</t>
@@ -1486,10 +1480,10 @@
     <t>10/14(WED)</t>
   </si>
   <si>
-    <t>10/13(TUE), 10/20(TUE), 10/21(WED), 10/28(WED), 10/6(TUE), 10/7(WED)</t>
-  </si>
-  <si>
-    <t>10/10(SAT), 10/11(SUN), 10/15(THU), 10/17(SAT), 10/18(SUN), 10/22(THU), 10/25(SUN), 10/29(THU), 10/31(SAT), 10/4(SUN), 10/8(THU)</t>
+    <t>10/6(TUE), 10/7(WED), 10/13(TUE), 10/20(TUE), 10/21(WED), 10/28(WED)</t>
+  </si>
+  <si>
+    <t>10/4(SUN), 10/8(THU), 10/10(SAT), 10/11(SUN), 10/15(THU), 10/17(SAT), 10/18(SUN), 10/22(THU), 10/25(SUN), 10/29(THU), 10/31(SAT)</t>
   </si>
   <si>
     <t>10/9(FRI)</t>
@@ -1498,10 +1492,10 @@
     <t>10/16(FRI), 10/23(FRI), 10/30(FRI)</t>
   </si>
   <si>
-    <t>10/13(TUE), 10/14(WED), 10/20(TUE), 10/21(WED), 10/28(WED), 10/6(TUE), 10/7(WED)</t>
-  </si>
-  <si>
-    <t>10/11(SUN), 10/18(SUN), 10/25(SUN), 10/4(SUN)</t>
+    <t>10/6(TUE), 10/7(WED), 10/13(TUE), 10/14(WED), 10/20(TUE), 10/21(WED), 10/28(WED)</t>
+  </si>
+  <si>
+    <t>10/4(SUN), 10/11(SUN), 10/18(SUN), 10/25(SUN)</t>
   </si>
   <si>
     <t>10/6(TUE)</t>
@@ -1510,7 +1504,7 @@
     <t>10/13(TUE), 10/20(TUE), 10/28(WED)</t>
   </si>
   <si>
-    <t>10/14(WED), 10/21(WED), 10/27(TUE), 10/7(WED)</t>
+    <t>10/7(WED), 10/14(WED), 10/21(WED), 10/27(TUE)</t>
   </si>
   <si>
     <t>10/15(THU)</t>
@@ -1522,10 +1516,10 @@
     <t>10/8(THU)</t>
   </si>
   <si>
-    <t>10/15(THU), 10/22(THU), 10/29(THU), 10/8(THU)</t>
-  </si>
-  <si>
-    <t>10/19(MON), 10/5(MON)</t>
+    <t>10/8(THU), 10/15(THU), 10/22(THU), 10/29(THU)</t>
+  </si>
+  <si>
+    <t>10/5(MON), 10/19(MON)</t>
   </si>
   <si>
     <t>10/17(SAT), 10/31(SAT)</t>
@@ -1537,7 +1531,7 @@
     <t>10/11(SUN)</t>
   </si>
   <si>
-    <t>10/18(SUN), 10/4(SUN)</t>
+    <t>10/4(SUN), 10/18(SUN)</t>
   </si>
   <si>
     <t>10/25(SUN)</t>
@@ -1546,9 +1540,6 @@
     <t>10/16(FRI), 10/30(FRI)</t>
   </si>
   <si>
-    <t>10/15(THU), 10/29(THU), 10/8(THU)</t>
-  </si>
-  <si>
     <t>10/22(THU)</t>
   </si>
   <si>
@@ -1561,19 +1552,19 @@
     <t>10/5(MON)</t>
   </si>
   <si>
-    <t>10/18(SUN), 10/25(SUN), 10/4(SUN)</t>
-  </si>
-  <si>
-    <t>10/11(SUN), 10/13(TUE), 10/15(THU), 10/18(SUN), 10/20(TUE), 10/21(WED), 10/27(TUE), 10/29(THU), 10/4(SUN)</t>
+    <t>10/4(SUN), 10/18(SUN), 10/25(SUN)</t>
+  </si>
+  <si>
+    <t>10/4(SUN), 10/11(SUN), 10/13(TUE), 10/15(THU), 10/18(SUN), 10/20(TUE), 10/21(WED), 10/27(TUE), 10/29(THU)</t>
   </si>
   <si>
     <t>10/28(WED)</t>
   </si>
   <si>
-    <t>10/22(THU), 10/6(TUE), 10/7(WED)</t>
-  </si>
-  <si>
-    <t>10/12(MON), 10/15(THU), 10/16(FRI), 10/19(MON), 10/22(THU), 10/23(FRI), 10/29(THU), 10/30(FRI), 10/5(MON), 10/9(FRI)</t>
+    <t>10/6(TUE), 10/7(WED), 10/22(THU)</t>
+  </si>
+  <si>
+    <t>10/5(MON), 10/9(FRI), 10/12(MON), 10/15(THU), 10/16(FRI), 10/19(MON), 10/22(THU), 10/23(FRI), 10/29(THU), 10/30(FRI)</t>
   </si>
   <si>
     <t>10/12(MON)</t>
@@ -1588,16 +1579,13 @@
     <t>10/10(SAT), 10/24(SAT)</t>
   </si>
   <si>
-    <t>10/13(TUE), 10/14(WED), 10/18(SUN), 10/20(TUE), 10/21(WED), 10/27(TUE), 10/28(WED), 10/4(SUN), 10/6(TUE), 10/7(WED)</t>
+    <t>10/4(SUN), 10/6(TUE), 10/7(WED), 10/13(TUE), 10/14(WED), 10/18(SUN), 10/20(TUE), 10/21(WED), 10/27(TUE), 10/28(WED)</t>
   </si>
   <si>
     <t>10/15(THU), 10/22(THU), 10/29(THU)</t>
   </si>
   <si>
-    <t>10/31(SAT)</t>
-  </si>
-  <si>
-    <t>10/13(TUE), 10/20(TUE), 10/7(WED)</t>
+    <t>10/7(WED), 10/13(TUE), 10/14(WED), 10/20(TUE)</t>
   </si>
   <si>
     <t>10/21(WED)</t>
@@ -1609,25 +1597,19 @@
     <t>10/15(THU), 10/16(FRI), 10/22(THU), 10/23(FRI), 10/29(THU), 10/30(FRI)</t>
   </si>
   <si>
-    <t>10/18(SUN)</t>
-  </si>
-  <si>
-    <t>10/14(WED), 10/20(TUE), 10/21(WED), 10/6(TUE), 10/7(WED)</t>
-  </si>
-  <si>
     <t>10/15(THU), 10/22(THU)</t>
   </si>
   <si>
-    <t>10/21(WED), 10/6(TUE), 10/7(WED)</t>
+    <t>10/6(TUE), 10/7(WED), 10/21(WED)</t>
   </si>
   <si>
     <t>10/13(TUE), 10/14(WED), 10/20(TUE)</t>
   </si>
   <si>
-    <t>10/11(SUN), 10/18(SUN), 10/4(SUN)</t>
-  </si>
-  <si>
-    <t>10/13(TUE), 10/14(WED), 10/20(TUE), 10/21(WED), 10/27(TUE), 10/6(TUE), 10/7(WED)</t>
+    <t>10/4(SUN), 10/11(SUN), 10/18(SUN)</t>
+  </si>
+  <si>
+    <t>10/6(TUE), 10/7(WED), 10/13(TUE), 10/14(WED), 10/20(TUE), 10/21(WED), 10/27(TUE)</t>
   </si>
   <si>
     <t>10/23(FRI), 10/30(FRI)</t>
@@ -1636,15 +1618,12 @@
     <t>10/16(FRI)</t>
   </si>
   <si>
-    <t>10/23(FRI), 10/30(FRI), 10/9(FRI)</t>
+    <t>10/9(FRI), 10/23(FRI), 10/30(FRI)</t>
   </si>
   <si>
     <t>10/19(MON)</t>
   </si>
   <si>
-    <t>10/25(SUN), 10/4(SUN)</t>
-  </si>
-  <si>
     <t>10/15(THU), 10/19(MON), 10/22(THU), 10/29(THU)</t>
   </si>
   <si>
@@ -1654,31 +1633,28 @@
     <t>10/14(WED), 10/20(TUE)</t>
   </si>
   <si>
-    <t>10/21(WED), 10/27(TUE), 10/6(TUE), 10/7(WED)</t>
-  </si>
-  <si>
-    <t>10/14(WED), 10/21(WED), 10/6(TUE), 10/7(WED)</t>
+    <t>10/6(TUE), 10/7(WED), 10/21(WED), 10/27(TUE)</t>
+  </si>
+  <si>
+    <t>10/6(TUE), 10/7(WED), 10/14(WED), 10/21(WED)</t>
   </si>
   <si>
     <t>10/20(TUE), 10/27(TUE), 10/28(WED)</t>
   </si>
   <si>
-    <t>10/18(SUN), 10/23(FRI), 10/4(SUN)</t>
-  </si>
-  <si>
-    <t>10/21(WED), 10/27(TUE), 10/7(WED)</t>
-  </si>
-  <si>
-    <t>10/17(SAT), 10/24(SAT)</t>
-  </si>
-  <si>
-    <t>10/21(WED), 10/7(WED)</t>
-  </si>
-  <si>
-    <t>10/28(WED), 10/5(MON)</t>
-  </si>
-  <si>
-    <t>10/15(THU), 10/21(WED), 10/22(THU), 10/6(TUE)</t>
+    <t>10/4(SUN), 10/18(SUN), 10/23(FRI)</t>
+  </si>
+  <si>
+    <t>10/7(WED), 10/21(WED), 10/27(TUE)</t>
+  </si>
+  <si>
+    <t>10/7(WED), 10/21(WED)</t>
+  </si>
+  <si>
+    <t>10/5(MON), 10/28(WED)</t>
+  </si>
+  <si>
+    <t>10/6(TUE), 10/15(THU), 10/21(WED), 10/22(THU)</t>
   </si>
   <si>
     <t>10/20(TUE)</t>
@@ -1687,28 +1663,19 @@
     <t>10/13(TUE), 10/14(WED)</t>
   </si>
   <si>
-    <t>10/28(WED), 10/6(TUE)</t>
-  </si>
-  <si>
-    <t>10/13(TUE), 10/15(THU), 10/19(MON), 10/20(TUE), 10/6(TUE), 10/7(WED)</t>
+    <t>10/6(TUE), 10/28(WED)</t>
+  </si>
+  <si>
+    <t>10/6(TUE), 10/7(WED), 10/13(TUE), 10/15(THU), 10/19(MON), 10/20(TUE)</t>
   </si>
   <si>
     <t>10/14(WED), 10/15(THU), 10/16(FRI)</t>
   </si>
   <si>
-    <t>10/15(THU), 10/19(MON), 10/27(TUE), 10/28(WED), 10/5(MON)</t>
-  </si>
-  <si>
-    <t>10/15(THU), 10/27(TUE), 10/29(THU)</t>
-  </si>
-  <si>
-    <t>10/19(MON), 10/29(THU)</t>
-  </si>
-  <si>
     <t>10/21(WED), 10/22(THU), 10/29(THU), 10/30(FRI)</t>
   </si>
   <si>
-    <t>10/12(MON), 10/13(TUE), 10/14(WED), 10/15(THU), 10/16(FRI), 10/17(SAT), 10/19(MON), 10/20(TUE), 10/21(WED), 10/22(THU), 10/23(FRI), 10/26(MON), 10/27(TUE), 10/28(WED), 10/29(THU), 10/30(FRI), 10/5(MON), 10/6(TUE), 10/7(WED), 10/8(THU), 10/9(FRI)</t>
+    <t>10/5(MON), 10/6(TUE), 10/7(WED), 10/8(THU), 10/9(FRI), 10/12(MON), 10/13(TUE), 10/14(WED), 10/15(THU), 10/16(FRI), 10/17(SAT), 10/19(MON), 10/20(TUE), 10/21(WED), 10/22(THU), 10/23(FRI), 10/26(MON), 10/27(TUE), 10/28(WED), 10/29(THU), 10/30(FRI)</t>
   </si>
   <si>
     <t>10/16(FRI), 10/19(MON), 10/23(FRI), 10/27(TUE)</t>
@@ -1717,16 +1684,10 @@
     <t>10/13(TUE), 10/15(THU)</t>
   </si>
   <si>
-    <t>10/11(SUN), 10/12(MON), 10/13(TUE), 10/14(WED), 10/15(THU), 10/16(FRI), 10/18(SUN), 10/19(MON), 10/20(TUE), 10/21(WED), 10/22(THU), 10/23(FRI), 10/24(SAT), 10/26(MON), 10/28(WED), 10/29(THU), 10/30(FRI), 10/4(SUN), 10/5(MON), 10/6(TUE), 10/8(THU), 10/9(FRI)</t>
-  </si>
-  <si>
-    <t>10/10(SAT), 10/11(SUN), 10/12(MON), 10/13(TUE), 10/14(WED), 10/15(THU), 10/16(FRI), 10/17(SAT), 10/18(SUN), 10/19(MON), 10/20(TUE), 10/21(WED), 10/22(THU), 10/23(FRI), 10/24(SAT), 10/25(SUN), 10/26(MON), 10/27(TUE), 10/28(WED), 10/29(THU), 10/30(FRI), 10/31(SAT), 10/4(SUN), 10/5(MON), 10/6(TUE), 10/7(WED), 10/8(THU), 10/9(FRI)</t>
-  </si>
-  <si>
-    <t>10/13(TUE), 10/20(TUE)</t>
-  </si>
-  <si>
-    <t>10/13(TUE), 10/22(THU), 10/30(FRI), 10/6(TUE)</t>
+    <t>10/4(SUN), 10/5(MON), 10/6(TUE), 10/7(WED), 10/8(THU), 10/9(FRI), 10/10(SAT), 10/11(SUN), 10/12(MON), 10/13(TUE), 10/14(WED), 10/15(THU), 10/16(FRI), 10/17(SAT), 10/18(SUN), 10/19(MON), 10/20(TUE), 10/21(WED), 10/22(THU), 10/23(FRI), 10/24(SAT), 10/25(SUN), 10/26(MON), 10/27(TUE), 10/28(WED), 10/29(THU), 10/30(FRI), 10/31(SAT)</t>
+  </si>
+  <si>
+    <t>10/7(WED), 10/9(FRI)</t>
   </si>
 </sst>
 </file>
@@ -2084,7 +2045,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E316"/>
+  <dimension ref="A1:E314"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -2109,16 +2070,16 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="C2" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="D2" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="E2" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -2126,16 +2087,16 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="C3" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="D3" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="E3" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -2143,16 +2104,16 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="C4" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E4" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -2160,16 +2121,16 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="C5" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="D5" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="E5" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -2177,16 +2138,16 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="C6" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="D6" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="E6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -2194,16 +2155,16 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="C7" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="D7" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="E7" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -2211,16 +2172,16 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="C8" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="D8" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="E8" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -2228,16 +2189,16 @@
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="C9" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="D9" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="E9" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -2245,16 +2206,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="C10" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="D10" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="E10" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -2262,16 +2223,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="C11" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="D11" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="E11" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -2279,16 +2240,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="C12" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="D12" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E12" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -2296,16 +2257,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="C13" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="D13" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E13" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -2313,16 +2274,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="C14" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="D14" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="E14" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -2330,16 +2291,16 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="C15" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="D15" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="E15" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -2347,16 +2308,16 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="C16" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="D16" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E16" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -2364,16 +2325,16 @@
         <v>13</v>
       </c>
       <c r="B17" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="C17" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="D17" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="E17" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -2381,16 +2342,16 @@
         <v>13</v>
       </c>
       <c r="B18" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="C18" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="D18" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="E18" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -2398,16 +2359,16 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="C19" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="D19" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="E19" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -2415,16 +2376,16 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="C20" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="D20" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="E20" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -2432,16 +2393,16 @@
         <v>15</v>
       </c>
       <c r="B21" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="C21" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="D21" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="E21" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -2449,16 +2410,16 @@
         <v>15</v>
       </c>
       <c r="B22" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="C22" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="D22" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E22" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -2466,16 +2427,16 @@
         <v>16</v>
       </c>
       <c r="B23" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="C23" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="D23" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="E23" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -2483,16 +2444,16 @@
         <v>16</v>
       </c>
       <c r="B24" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="C24" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="D24" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="E24" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2500,16 +2461,16 @@
         <v>17</v>
       </c>
       <c r="B25" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="C25" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="D25" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="E25" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2517,16 +2478,16 @@
         <v>17</v>
       </c>
       <c r="B26" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="C26" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="D26" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="E26" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2534,16 +2495,16 @@
         <v>18</v>
       </c>
       <c r="B27" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="C27" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="D27" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="E27" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2551,16 +2512,16 @@
         <v>19</v>
       </c>
       <c r="B28" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="C28" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="D28" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E28" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2568,16 +2529,16 @@
         <v>20</v>
       </c>
       <c r="B29" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="C29" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="D29" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="E29" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2585,16 +2546,16 @@
         <v>20</v>
       </c>
       <c r="B30" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="C30" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="D30" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="E30" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2602,16 +2563,16 @@
         <v>21</v>
       </c>
       <c r="B31" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="C31" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="D31" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E31" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2619,16 +2580,16 @@
         <v>21</v>
       </c>
       <c r="B32" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="C32" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="D32" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="E32" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2636,16 +2597,16 @@
         <v>21</v>
       </c>
       <c r="B33" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="C33" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D33" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E33" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2653,16 +2614,16 @@
         <v>22</v>
       </c>
       <c r="B34" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="C34" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="D34" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E34" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2670,16 +2631,16 @@
         <v>22</v>
       </c>
       <c r="B35" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="C35" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="D35" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="E35" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2687,16 +2648,16 @@
         <v>22</v>
       </c>
       <c r="B36" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="C36" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="D36" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="E36" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2704,16 +2665,16 @@
         <v>23</v>
       </c>
       <c r="B37" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="C37" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="D37" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="E37" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2721,16 +2682,16 @@
         <v>24</v>
       </c>
       <c r="B38" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="C38" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="D38" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="E38" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2738,16 +2699,16 @@
         <v>24</v>
       </c>
       <c r="B39" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="C39" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="D39" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="E39" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2755,16 +2716,16 @@
         <v>25</v>
       </c>
       <c r="B40" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="C40" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="D40" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="E40" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2772,16 +2733,16 @@
         <v>25</v>
       </c>
       <c r="B41" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="C41" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="D41" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E41" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2789,16 +2750,16 @@
         <v>26</v>
       </c>
       <c r="B42" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="C42" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="D42" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="E42" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2806,16 +2767,16 @@
         <v>26</v>
       </c>
       <c r="B43" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="C43" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="D43" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="E43" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2823,16 +2784,16 @@
         <v>27</v>
       </c>
       <c r="B44" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="C44" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="D44" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="E44" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2840,16 +2801,16 @@
         <v>27</v>
       </c>
       <c r="B45" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="C45" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="D45" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="E45" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2857,16 +2818,16 @@
         <v>28</v>
       </c>
       <c r="B46" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="C46" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="D46" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="E46" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -2874,16 +2835,16 @@
         <v>28</v>
       </c>
       <c r="B47" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="C47" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="D47" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="E47" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -2891,16 +2852,16 @@
         <v>28</v>
       </c>
       <c r="B48" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="C48" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="D48" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="E48" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -2908,16 +2869,16 @@
         <v>29</v>
       </c>
       <c r="B49" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="C49" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="D49" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E49" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -2925,16 +2886,16 @@
         <v>30</v>
       </c>
       <c r="B50" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="C50" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="D50" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="E50" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -2942,16 +2903,16 @@
         <v>30</v>
       </c>
       <c r="B51" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="C51" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="D51" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E51" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -2959,16 +2920,16 @@
         <v>30</v>
       </c>
       <c r="B52" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="C52" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="D52" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="E52" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -2976,16 +2937,16 @@
         <v>31</v>
       </c>
       <c r="B53" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="C53" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="D53" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="E53" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -2993,16 +2954,16 @@
         <v>31</v>
       </c>
       <c r="B54" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="C54" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="D54" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="E54" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -3010,16 +2971,16 @@
         <v>31</v>
       </c>
       <c r="B55" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="C55" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="D55" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="E55" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -3027,16 +2988,16 @@
         <v>32</v>
       </c>
       <c r="B56" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="C56" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="D56" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E56" t="s">
-        <v>510</v>
+        <v>500</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -3044,16 +3005,16 @@
         <v>33</v>
       </c>
       <c r="B57" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="C57" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="D57" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="E57" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -3061,16 +3022,16 @@
         <v>33</v>
       </c>
       <c r="B58" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="C58" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="D58" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="E58" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -3078,16 +3039,16 @@
         <v>34</v>
       </c>
       <c r="B59" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="C59" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="D59" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="E59" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -3095,16 +3056,16 @@
         <v>34</v>
       </c>
       <c r="B60" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="C60" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="D60" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="E60" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -3112,16 +3073,16 @@
         <v>34</v>
       </c>
       <c r="B61" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="C61" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="D61" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E61" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -3129,16 +3090,16 @@
         <v>34</v>
       </c>
       <c r="B62" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="C62" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="D62" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="E62" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -3146,16 +3107,16 @@
         <v>35</v>
       </c>
       <c r="B63" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="C63" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="D63" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E63" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -3163,16 +3124,16 @@
         <v>35</v>
       </c>
       <c r="B64" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="C64" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="D64" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="E64" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -3180,16 +3141,16 @@
         <v>35</v>
       </c>
       <c r="B65" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="C65" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="D65" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="E65" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -3197,16 +3158,16 @@
         <v>36</v>
       </c>
       <c r="B66" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="C66" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="D66" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="E66" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -3214,16 +3175,16 @@
         <v>36</v>
       </c>
       <c r="B67" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="C67" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="D67" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="E67" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -3231,16 +3192,16 @@
         <v>37</v>
       </c>
       <c r="B68" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="C68" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="D68" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="E68" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -3248,16 +3209,16 @@
         <v>37</v>
       </c>
       <c r="B69" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="C69" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="D69" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="E69" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -3265,16 +3226,16 @@
         <v>37</v>
       </c>
       <c r="B70" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="C70" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="D70" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="E70" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -3282,16 +3243,16 @@
         <v>37</v>
       </c>
       <c r="B71" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="C71" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="D71" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="E71" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -3299,16 +3260,16 @@
         <v>37</v>
       </c>
       <c r="B72" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="C72" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="D72" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="E72" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -3316,16 +3277,16 @@
         <v>37</v>
       </c>
       <c r="B73" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="C73" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="D73" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E73" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -3333,16 +3294,16 @@
         <v>38</v>
       </c>
       <c r="B74" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="C74" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="D74" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="E74" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -3350,16 +3311,16 @@
         <v>38</v>
       </c>
       <c r="B75" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="C75" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="D75" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="E75" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -3367,16 +3328,16 @@
         <v>38</v>
       </c>
       <c r="B76" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="C76" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="D76" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E76" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -3384,16 +3345,16 @@
         <v>39</v>
       </c>
       <c r="B77" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="C77" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="D77" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E77" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -3401,16 +3362,16 @@
         <v>40</v>
       </c>
       <c r="B78" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="C78" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="D78" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E78" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="79" spans="1:5">
@@ -3418,16 +3379,16 @@
         <v>40</v>
       </c>
       <c r="B79" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="C79" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="D79" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="E79" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
     </row>
     <row r="80" spans="1:5">
@@ -3435,16 +3396,16 @@
         <v>40</v>
       </c>
       <c r="B80" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="C80" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="D80" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E80" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="81" spans="1:5">
@@ -3452,16 +3413,16 @@
         <v>41</v>
       </c>
       <c r="B81" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="C81" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="D81" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E81" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -3469,16 +3430,16 @@
         <v>42</v>
       </c>
       <c r="B82" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="C82" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="D82" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E82" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -3486,16 +3447,16 @@
         <v>42</v>
       </c>
       <c r="B83" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="C83" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="D83" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E83" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
     <row r="84" spans="1:5">
@@ -3503,16 +3464,16 @@
         <v>43</v>
       </c>
       <c r="B84" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="C84" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="D84" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="E84" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
     </row>
     <row r="85" spans="1:5">
@@ -3520,16 +3481,16 @@
         <v>43</v>
       </c>
       <c r="B85" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="C85" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="D85" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="E85" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
     </row>
     <row r="86" spans="1:5">
@@ -3537,16 +3498,16 @@
         <v>43</v>
       </c>
       <c r="B86" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="C86" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="D86" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E86" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -3554,16 +3515,16 @@
         <v>44</v>
       </c>
       <c r="B87" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="C87" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="D87" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E87" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -3571,16 +3532,16 @@
         <v>44</v>
       </c>
       <c r="B88" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="C88" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="D88" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E88" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
     </row>
     <row r="89" spans="1:5">
@@ -3588,16 +3549,16 @@
         <v>44</v>
       </c>
       <c r="B89" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="C89" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="D89" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="E89" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
     </row>
     <row r="90" spans="1:5">
@@ -3605,16 +3566,16 @@
         <v>45</v>
       </c>
       <c r="B90" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="C90" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="D90" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="E90" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
     </row>
     <row r="91" spans="1:5">
@@ -3622,16 +3583,16 @@
         <v>45</v>
       </c>
       <c r="B91" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="C91" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="D91" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="E91" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -3639,16 +3600,16 @@
         <v>46</v>
       </c>
       <c r="B92" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="C92" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="D92" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="E92" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
     </row>
     <row r="93" spans="1:5">
@@ -3656,16 +3617,16 @@
         <v>46</v>
       </c>
       <c r="B93" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="C93" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="D93" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="E93" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
     </row>
     <row r="94" spans="1:5">
@@ -3673,16 +3634,16 @@
         <v>46</v>
       </c>
       <c r="B94" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="C94" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="D94" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="E94" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
     </row>
     <row r="95" spans="1:5">
@@ -3690,16 +3651,16 @@
         <v>47</v>
       </c>
       <c r="B95" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="C95" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="D95" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="E95" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
     </row>
     <row r="96" spans="1:5">
@@ -3707,16 +3668,16 @@
         <v>47</v>
       </c>
       <c r="B96" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="C96" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="D96" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="E96" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
     </row>
     <row r="97" spans="1:5">
@@ -3724,16 +3685,16 @@
         <v>48</v>
       </c>
       <c r="B97" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="C97" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="D97" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E97" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
     </row>
     <row r="98" spans="1:5">
@@ -3741,16 +3702,16 @@
         <v>48</v>
       </c>
       <c r="B98" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="C98" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="D98" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="E98" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
     </row>
     <row r="99" spans="1:5">
@@ -3758,16 +3719,16 @@
         <v>49</v>
       </c>
       <c r="B99" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="C99" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="D99" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E99" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="100" spans="1:5">
@@ -3775,16 +3736,16 @@
         <v>49</v>
       </c>
       <c r="B100" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="C100" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="D100" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="E100" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
     </row>
     <row r="101" spans="1:5">
@@ -3792,16 +3753,16 @@
         <v>49</v>
       </c>
       <c r="B101" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="C101" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="D101" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="E101" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
     </row>
     <row r="102" spans="1:5">
@@ -3809,16 +3770,16 @@
         <v>50</v>
       </c>
       <c r="B102" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="C102" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="D102" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E102" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
     </row>
     <row r="103" spans="1:5">
@@ -3826,16 +3787,16 @@
         <v>50</v>
       </c>
       <c r="B103" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="C103" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="D103" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="E103" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
     </row>
     <row r="104" spans="1:5">
@@ -3843,16 +3804,16 @@
         <v>50</v>
       </c>
       <c r="B104" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="C104" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="D104" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="E104" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="105" spans="1:5">
@@ -3860,16 +3821,16 @@
         <v>51</v>
       </c>
       <c r="B105" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="C105" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="D105" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="E105" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
     </row>
     <row r="106" spans="1:5">
@@ -3877,16 +3838,16 @@
         <v>51</v>
       </c>
       <c r="B106" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="C106" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="D106" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="E106" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
     </row>
     <row r="107" spans="1:5">
@@ -3894,16 +3855,16 @@
         <v>52</v>
       </c>
       <c r="B107" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="C107" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="D107" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E107" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="108" spans="1:5">
@@ -3911,16 +3872,16 @@
         <v>53</v>
       </c>
       <c r="B108" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="C108" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="D108" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E108" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
     </row>
     <row r="109" spans="1:5">
@@ -3928,16 +3889,16 @@
         <v>53</v>
       </c>
       <c r="B109" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="C109" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="D109" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="E109" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
     </row>
     <row r="110" spans="1:5">
@@ -3945,16 +3906,16 @@
         <v>54</v>
       </c>
       <c r="B110" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="C110" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="D110" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E110" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
     </row>
     <row r="111" spans="1:5">
@@ -3962,16 +3923,16 @@
         <v>54</v>
       </c>
       <c r="B111" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="C111" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="D111" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E111" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
     </row>
     <row r="112" spans="1:5">
@@ -3979,16 +3940,16 @@
         <v>55</v>
       </c>
       <c r="B112" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="C112" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="D112" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="E112" t="s">
-        <v>526</v>
+        <v>502</v>
       </c>
     </row>
     <row r="113" spans="1:5">
@@ -3996,16 +3957,16 @@
         <v>55</v>
       </c>
       <c r="B113" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="C113" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="D113" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="E113" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="114" spans="1:5">
@@ -4013,16 +3974,16 @@
         <v>55</v>
       </c>
       <c r="B114" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="C114" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="D114" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E114" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
     </row>
     <row r="115" spans="1:5">
@@ -4030,33 +3991,33 @@
         <v>56</v>
       </c>
       <c r="B115" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="C115" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="D115" t="s">
-        <v>443</v>
+        <v>425</v>
       </c>
       <c r="E115" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B116" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="C116" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="D116" t="s">
-        <v>423</v>
+        <v>439</v>
       </c>
       <c r="E116" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
     </row>
     <row r="117" spans="1:5">
@@ -4064,16 +4025,16 @@
         <v>57</v>
       </c>
       <c r="B117" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="C117" t="s">
-        <v>302</v>
+        <v>325</v>
       </c>
       <c r="D117" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E117" t="s">
-        <v>527</v>
+        <v>494</v>
       </c>
     </row>
     <row r="118" spans="1:5">
@@ -4081,84 +4042,84 @@
         <v>57</v>
       </c>
       <c r="B118" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="C118" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="D118" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E118" t="s">
-        <v>528</v>
+        <v>514</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B119" t="s">
-        <v>136</v>
+        <v>152</v>
       </c>
       <c r="C119" t="s">
-        <v>164</v>
+        <v>298</v>
       </c>
       <c r="D119" t="s">
-        <v>267</v>
+        <v>414</v>
       </c>
       <c r="E119" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B120" t="s">
-        <v>136</v>
+        <v>152</v>
       </c>
       <c r="C120" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="D120" t="s">
-        <v>408</v>
+        <v>264</v>
       </c>
       <c r="E120" t="s">
-        <v>505</v>
+        <v>524</v>
       </c>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B121" t="s">
-        <v>171</v>
+        <v>129</v>
       </c>
       <c r="C121" t="s">
-        <v>284</v>
+        <v>157</v>
       </c>
       <c r="D121" t="s">
-        <v>436</v>
+        <v>264</v>
       </c>
       <c r="E121" t="s">
-        <v>492</v>
+        <v>525</v>
       </c>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B122" t="s">
-        <v>172</v>
+        <v>129</v>
       </c>
       <c r="C122" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="D122" t="s">
-        <v>428</v>
+        <v>404</v>
       </c>
       <c r="E122" t="s">
-        <v>530</v>
+        <v>503</v>
       </c>
     </row>
     <row r="123" spans="1:5">
@@ -4166,84 +4127,84 @@
         <v>59</v>
       </c>
       <c r="B123" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="C123" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="D123" t="s">
-        <v>267</v>
+        <v>432</v>
       </c>
       <c r="E123" t="s">
-        <v>501</v>
+        <v>490</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B124" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="C124" t="s">
-        <v>332</v>
+        <v>320</v>
       </c>
       <c r="D124" t="s">
-        <v>267</v>
+        <v>424</v>
       </c>
       <c r="E124" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B125" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="C125" t="s">
-        <v>290</v>
+        <v>278</v>
       </c>
       <c r="D125" t="s">
-        <v>445</v>
+        <v>264</v>
       </c>
       <c r="E125" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B126" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="C126" t="s">
-        <v>291</v>
+        <v>329</v>
       </c>
       <c r="D126" t="s">
-        <v>446</v>
+        <v>264</v>
       </c>
       <c r="E126" t="s">
-        <v>505</v>
+        <v>525</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B127" t="s">
-        <v>150</v>
+        <v>171</v>
       </c>
       <c r="C127" t="s">
-        <v>326</v>
+        <v>286</v>
       </c>
       <c r="D127" t="s">
-        <v>267</v>
+        <v>441</v>
       </c>
       <c r="E127" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="128" spans="1:5">
@@ -4251,50 +4212,50 @@
         <v>61</v>
       </c>
       <c r="B128" t="s">
-        <v>141</v>
+        <v>172</v>
       </c>
       <c r="C128" t="s">
-        <v>333</v>
+        <v>287</v>
       </c>
       <c r="D128" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="E128" t="s">
-        <v>487</v>
+        <v>503</v>
       </c>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B129" t="s">
-        <v>178</v>
+        <v>143</v>
       </c>
       <c r="C129" t="s">
-        <v>334</v>
+        <v>322</v>
       </c>
       <c r="D129" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E129" t="s">
-        <v>487</v>
+        <v>502</v>
       </c>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B130" t="s">
-        <v>179</v>
+        <v>134</v>
       </c>
       <c r="C130" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="D130" t="s">
         <v>443</v>
       </c>
       <c r="E130" t="s">
-        <v>504</v>
+        <v>485</v>
       </c>
     </row>
     <row r="131" spans="1:5">
@@ -4302,50 +4263,50 @@
         <v>62</v>
       </c>
       <c r="B131" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="C131" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="D131" t="s">
-        <v>414</v>
+        <v>264</v>
       </c>
       <c r="E131" t="s">
-        <v>505</v>
+        <v>485</v>
       </c>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B132" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="C132" t="s">
-        <v>289</v>
+        <v>332</v>
       </c>
       <c r="D132" t="s">
-        <v>415</v>
+        <v>439</v>
       </c>
       <c r="E132" t="s">
-        <v>531</v>
+        <v>502</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B133" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="C133" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="D133" t="s">
-        <v>448</v>
+        <v>410</v>
       </c>
       <c r="E133" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
     </row>
     <row r="134" spans="1:5">
@@ -4353,50 +4314,50 @@
         <v>63</v>
       </c>
       <c r="B134" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="C134" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="D134" t="s">
-        <v>267</v>
+        <v>411</v>
       </c>
       <c r="E134" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B135" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="C135" t="s">
-        <v>301</v>
+        <v>334</v>
       </c>
       <c r="D135" t="s">
-        <v>267</v>
+        <v>444</v>
       </c>
       <c r="E135" t="s">
-        <v>517</v>
+        <v>506</v>
       </c>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B136" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="C136" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
       <c r="D136" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E136" t="s">
-        <v>532</v>
+        <v>504</v>
       </c>
     </row>
     <row r="137" spans="1:5">
@@ -4404,764 +4365,764 @@
         <v>64</v>
       </c>
       <c r="B137" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="C137" t="s">
-        <v>338</v>
+        <v>297</v>
       </c>
       <c r="D137" t="s">
-        <v>411</v>
+        <v>264</v>
       </c>
       <c r="E137" t="s">
-        <v>488</v>
+        <v>514</v>
       </c>
     </row>
     <row r="138" spans="1:5">
       <c r="A138" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B138" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C138" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="D138" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E138" t="s">
-        <v>501</v>
+        <v>474</v>
       </c>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B139" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C139" t="s">
-        <v>310</v>
+        <v>335</v>
       </c>
       <c r="D139" t="s">
-        <v>267</v>
+        <v>407</v>
       </c>
       <c r="E139" t="s">
-        <v>533</v>
+        <v>486</v>
       </c>
     </row>
     <row r="140" spans="1:5">
       <c r="A140" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B140" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="C140" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="D140" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E140" t="s">
-        <v>509</v>
+        <v>499</v>
       </c>
     </row>
     <row r="141" spans="1:5">
       <c r="A141" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B141" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="C141" t="s">
-        <v>339</v>
+        <v>306</v>
       </c>
       <c r="D141" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E141" t="s">
-        <v>492</v>
+        <v>527</v>
       </c>
     </row>
     <row r="142" spans="1:5">
       <c r="A142" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B142" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="C142" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D142" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="E142" t="s">
-        <v>484</v>
+        <v>509</v>
       </c>
     </row>
     <row r="143" spans="1:5">
       <c r="A143" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B143" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="C143" t="s">
-        <v>340</v>
+        <v>285</v>
       </c>
       <c r="D143" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E143" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="144" spans="1:5">
       <c r="A144" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B144" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="C144" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="D144" t="s">
-        <v>436</v>
+        <v>264</v>
       </c>
       <c r="E144" t="s">
-        <v>520</v>
+        <v>490</v>
       </c>
     </row>
     <row r="145" spans="1:5">
       <c r="A145" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B145" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="C145" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="D145" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="E145" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="146" spans="1:5">
       <c r="A146" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B146" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="C146" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="D146" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E146" t="s">
-        <v>533</v>
+        <v>501</v>
       </c>
     </row>
     <row r="147" spans="1:5">
       <c r="A147" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B147" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="C147" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="D147" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="E147" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
     </row>
     <row r="148" spans="1:5">
       <c r="A148" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B148" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="C148" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="D148" t="s">
-        <v>267</v>
+        <v>447</v>
       </c>
       <c r="E148" t="s">
-        <v>501</v>
+        <v>479</v>
       </c>
     </row>
     <row r="149" spans="1:5">
       <c r="A149" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B149" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C149" t="s">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="D149" t="s">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="E149" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
     </row>
     <row r="150" spans="1:5">
       <c r="A150" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B150" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="C150" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="D150" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="E150" t="s">
-        <v>535</v>
+        <v>509</v>
       </c>
     </row>
     <row r="151" spans="1:5">
       <c r="A151" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B151" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="C151" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="D151" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E151" t="s">
-        <v>475</v>
+        <v>499</v>
       </c>
     </row>
     <row r="152" spans="1:5">
       <c r="A152" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B152" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="C152" t="s">
-        <v>310</v>
+        <v>343</v>
       </c>
       <c r="D152" t="s">
-        <v>449</v>
+        <v>247</v>
       </c>
       <c r="E152" t="s">
-        <v>492</v>
+        <v>528</v>
       </c>
     </row>
     <row r="153" spans="1:5">
       <c r="A153" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B153" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="C153" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D153" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="E153" t="s">
-        <v>484</v>
+        <v>529</v>
       </c>
     </row>
     <row r="154" spans="1:5">
       <c r="A154" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B154" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="C154" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="D154" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E154" t="s">
-        <v>509</v>
+        <v>473</v>
       </c>
     </row>
     <row r="155" spans="1:5">
       <c r="A155" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B155" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="C155" t="s">
-        <v>342</v>
+        <v>306</v>
       </c>
       <c r="D155" t="s">
-        <v>267</v>
+        <v>446</v>
       </c>
       <c r="E155" t="s">
-        <v>536</v>
+        <v>490</v>
       </c>
     </row>
     <row r="156" spans="1:5">
       <c r="A156" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B156" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="C156" t="s">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="D156" t="s">
-        <v>438</v>
+        <v>412</v>
       </c>
       <c r="E156" t="s">
-        <v>508</v>
+        <v>482</v>
       </c>
     </row>
     <row r="157" spans="1:5">
       <c r="A157" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B157" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="C157" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="D157" t="s">
-        <v>451</v>
+        <v>264</v>
       </c>
       <c r="E157" t="s">
-        <v>500</v>
+        <v>507</v>
       </c>
     </row>
     <row r="158" spans="1:5">
       <c r="A158" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B158" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="C158" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="D158" t="s">
-        <v>437</v>
+        <v>264</v>
       </c>
       <c r="E158" t="s">
-        <v>501</v>
+        <v>530</v>
       </c>
     </row>
     <row r="159" spans="1:5">
       <c r="A159" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B159" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="C159" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="D159" t="s">
-        <v>425</v>
+        <v>434</v>
       </c>
       <c r="E159" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="160" spans="1:5">
       <c r="A160" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B160" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C160" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="D160" t="s">
-        <v>407</v>
+        <v>448</v>
       </c>
       <c r="E160" t="s">
-        <v>508</v>
+        <v>522</v>
       </c>
     </row>
     <row r="161" spans="1:5">
       <c r="A161" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B161" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="C161" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="D161" t="s">
-        <v>267</v>
+        <v>433</v>
       </c>
       <c r="E161" t="s">
-        <v>506</v>
+        <v>499</v>
       </c>
     </row>
     <row r="162" spans="1:5">
       <c r="A162" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B162" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="C162" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D162" t="s">
-        <v>267</v>
+        <v>421</v>
       </c>
       <c r="E162" t="s">
-        <v>517</v>
+        <v>505</v>
       </c>
     </row>
     <row r="163" spans="1:5">
       <c r="A163" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B163" t="s">
-        <v>180</v>
+        <v>197</v>
       </c>
       <c r="C163" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="D163" t="s">
-        <v>431</v>
+        <v>403</v>
       </c>
       <c r="E163" t="s">
-        <v>537</v>
+        <v>506</v>
       </c>
     </row>
     <row r="164" spans="1:5">
       <c r="A164" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B164" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C164" t="s">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="D164" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E164" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
     </row>
     <row r="165" spans="1:5">
       <c r="A165" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B165" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="C165" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="D165" t="s">
-        <v>452</v>
+        <v>264</v>
       </c>
       <c r="E165" t="s">
-        <v>525</v>
+        <v>514</v>
       </c>
     </row>
     <row r="166" spans="1:5">
       <c r="A166" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B166" t="s">
-        <v>205</v>
+        <v>175</v>
       </c>
       <c r="C166" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="D166" t="s">
-        <v>267</v>
+        <v>427</v>
       </c>
       <c r="E166" t="s">
-        <v>484</v>
+        <v>531</v>
       </c>
     </row>
     <row r="167" spans="1:5">
       <c r="A167" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B167" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="C167" t="s">
-        <v>355</v>
+        <v>340</v>
       </c>
       <c r="D167" t="s">
-        <v>438</v>
+        <v>264</v>
       </c>
       <c r="E167" t="s">
-        <v>509</v>
+        <v>499</v>
       </c>
     </row>
     <row r="168" spans="1:5">
       <c r="A168" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B168" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="C168" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="D168" t="s">
-        <v>267</v>
+        <v>449</v>
       </c>
       <c r="E168" t="s">
-        <v>492</v>
+        <v>522</v>
       </c>
     </row>
     <row r="169" spans="1:5">
       <c r="A169" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B169" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="C169" t="s">
-        <v>336</v>
+        <v>351</v>
       </c>
       <c r="D169" t="s">
-        <v>420</v>
+        <v>264</v>
       </c>
       <c r="E169" t="s">
-        <v>520</v>
+        <v>482</v>
       </c>
     </row>
     <row r="170" spans="1:5">
       <c r="A170" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B170" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="C170" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="D170" t="s">
-        <v>453</v>
+        <v>434</v>
       </c>
       <c r="E170" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="171" spans="1:5">
       <c r="A171" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B171" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="C171" t="s">
         <v>352</v>
       </c>
       <c r="D171" t="s">
-        <v>435</v>
+        <v>264</v>
       </c>
       <c r="E171" t="s">
-        <v>481</v>
+        <v>490</v>
       </c>
     </row>
     <row r="172" spans="1:5">
       <c r="A172" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B172" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="C172" t="s">
-        <v>351</v>
+        <v>333</v>
       </c>
       <c r="D172" t="s">
-        <v>454</v>
+        <v>416</v>
       </c>
       <c r="E172" t="s">
-        <v>538</v>
+        <v>517</v>
       </c>
     </row>
     <row r="173" spans="1:5">
       <c r="A173" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B173" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="C173" t="s">
         <v>353</v>
       </c>
       <c r="D173" t="s">
-        <v>267</v>
+        <v>450</v>
       </c>
       <c r="E173" t="s">
-        <v>539</v>
+        <v>501</v>
       </c>
     </row>
     <row r="174" spans="1:5">
       <c r="A174" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B174" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="C174" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="D174" t="s">
-        <v>446</v>
+        <v>431</v>
       </c>
       <c r="E174" t="s">
-        <v>540</v>
+        <v>479</v>
       </c>
     </row>
     <row r="175" spans="1:5">
       <c r="A175" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B175" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="C175" t="s">
-        <v>336</v>
+        <v>348</v>
       </c>
       <c r="D175" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="E175" t="s">
-        <v>539</v>
+        <v>532</v>
       </c>
     </row>
     <row r="176" spans="1:5">
       <c r="A176" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B176" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="C176" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="D176" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E176" t="s">
-        <v>499</v>
+        <v>533</v>
       </c>
     </row>
     <row r="177" spans="1:5">
       <c r="A177" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B177" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="C177" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="D177" t="s">
-        <v>404</v>
+        <v>442</v>
       </c>
       <c r="E177" t="s">
-        <v>501</v>
+        <v>534</v>
       </c>
     </row>
     <row r="178" spans="1:5">
       <c r="A178" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B178" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="C178" t="s">
-        <v>356</v>
+        <v>333</v>
       </c>
       <c r="D178" t="s">
-        <v>405</v>
+        <v>441</v>
       </c>
       <c r="E178" t="s">
-        <v>500</v>
+        <v>533</v>
       </c>
     </row>
     <row r="179" spans="1:5">
       <c r="A179" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B179" t="s">
-        <v>215</v>
+        <v>191</v>
       </c>
       <c r="C179" t="s">
-        <v>357</v>
+        <v>343</v>
       </c>
       <c r="D179" t="s">
-        <v>455</v>
+        <v>264</v>
       </c>
       <c r="E179" t="s">
-        <v>481</v>
+        <v>497</v>
       </c>
     </row>
     <row r="180" spans="1:5">
       <c r="A180" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B180" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="C180" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="D180" t="s">
-        <v>267</v>
+        <v>400</v>
       </c>
       <c r="E180" t="s">
-        <v>520</v>
+        <v>499</v>
       </c>
     </row>
     <row r="181" spans="1:5">
       <c r="A181" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B181" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="C181" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="D181" t="s">
-        <v>456</v>
+        <v>401</v>
       </c>
       <c r="E181" t="s">
-        <v>541</v>
+        <v>498</v>
       </c>
     </row>
     <row r="182" spans="1:5">
@@ -5169,322 +5130,322 @@
         <v>81</v>
       </c>
       <c r="B182" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="C182" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D182" t="s">
-        <v>267</v>
+        <v>452</v>
       </c>
       <c r="E182" t="s">
-        <v>514</v>
+        <v>479</v>
       </c>
     </row>
     <row r="183" spans="1:5">
       <c r="A183" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B183" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="C183" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="D183" t="s">
-        <v>415</v>
+        <v>264</v>
       </c>
       <c r="E183" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="184" spans="1:5">
       <c r="A184" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B184" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="C184" t="s">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="D184" t="s">
-        <v>442</v>
+        <v>453</v>
       </c>
       <c r="E184" t="s">
-        <v>506</v>
+        <v>535</v>
       </c>
     </row>
     <row r="185" spans="1:5">
       <c r="A185" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B185" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="C185" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="D185" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E185" t="s">
-        <v>485</v>
+        <v>511</v>
       </c>
     </row>
     <row r="186" spans="1:5">
       <c r="A186" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B186" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="C186" t="s">
         <v>356</v>
       </c>
       <c r="D186" t="s">
-        <v>436</v>
+        <v>411</v>
       </c>
       <c r="E186" t="s">
-        <v>542</v>
+        <v>512</v>
       </c>
     </row>
     <row r="187" spans="1:5">
       <c r="A187" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B187" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="C187" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="D187" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
       <c r="E187" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
     </row>
     <row r="188" spans="1:5">
       <c r="A188" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B188" t="s">
-        <v>219</v>
+        <v>203</v>
       </c>
       <c r="C188" t="s">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="D188" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E188" t="s">
-        <v>508</v>
+        <v>483</v>
       </c>
     </row>
     <row r="189" spans="1:5">
       <c r="A189" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B189" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="C189" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D189" t="s">
-        <v>267</v>
+        <v>432</v>
       </c>
       <c r="E189" t="s">
-        <v>506</v>
+        <v>512</v>
       </c>
     </row>
     <row r="190" spans="1:5">
       <c r="A190" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B190" t="s">
-        <v>220</v>
+        <v>205</v>
       </c>
       <c r="C190" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="D190" t="s">
-        <v>267</v>
+        <v>454</v>
       </c>
       <c r="E190" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
     </row>
     <row r="191" spans="1:5">
       <c r="A191" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B191" t="s">
-        <v>188</v>
+        <v>215</v>
       </c>
       <c r="C191" t="s">
-        <v>340</v>
+        <v>358</v>
       </c>
       <c r="D191" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E191" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
     </row>
     <row r="192" spans="1:5">
       <c r="A192" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B192" t="s">
-        <v>220</v>
+        <v>198</v>
       </c>
       <c r="C192" t="s">
-        <v>362</v>
+        <v>349</v>
       </c>
       <c r="D192" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E192" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
     </row>
     <row r="193" spans="1:5">
       <c r="A193" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B193" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="C193" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="D193" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E193" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="194" spans="1:5">
       <c r="A194" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B194" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="C194" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="D194" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E194" t="s">
-        <v>495</v>
+        <v>506</v>
       </c>
     </row>
     <row r="195" spans="1:5">
       <c r="A195" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B195" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="C195" t="s">
-        <v>305</v>
+        <v>359</v>
       </c>
       <c r="D195" t="s">
-        <v>450</v>
+        <v>264</v>
       </c>
       <c r="E195" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="196" spans="1:5">
       <c r="A196" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B196" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="C196" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="D196" t="s">
-        <v>162</v>
+        <v>264</v>
       </c>
       <c r="E196" t="s">
-        <v>481</v>
+        <v>504</v>
       </c>
     </row>
     <row r="197" spans="1:5">
       <c r="A197" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B197" t="s">
-        <v>224</v>
+        <v>173</v>
       </c>
       <c r="C197" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="D197" t="s">
-        <v>408</v>
+        <v>264</v>
       </c>
       <c r="E197" t="s">
-        <v>520</v>
+        <v>493</v>
       </c>
     </row>
     <row r="198" spans="1:5">
       <c r="A198" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B198" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="C198" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="D198" t="s">
-        <v>267</v>
+        <v>447</v>
       </c>
       <c r="E198" t="s">
-        <v>514</v>
+        <v>501</v>
       </c>
     </row>
     <row r="199" spans="1:5">
       <c r="A199" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B199" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C199" t="s">
-        <v>310</v>
+        <v>360</v>
       </c>
       <c r="D199" t="s">
-        <v>458</v>
+        <v>155</v>
       </c>
       <c r="E199" t="s">
-        <v>543</v>
+        <v>479</v>
       </c>
     </row>
     <row r="200" spans="1:5">
       <c r="A200" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B200" t="s">
-        <v>204</v>
+        <v>220</v>
       </c>
       <c r="C200" t="s">
-        <v>351</v>
+        <v>333</v>
       </c>
       <c r="D200" t="s">
-        <v>459</v>
+        <v>404</v>
       </c>
       <c r="E200" t="s">
-        <v>501</v>
+        <v>517</v>
       </c>
     </row>
     <row r="201" spans="1:5">
@@ -5492,16 +5453,16 @@
         <v>89</v>
       </c>
       <c r="B201" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C201" t="s">
-        <v>364</v>
+        <v>299</v>
       </c>
       <c r="D201" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E201" t="s">
-        <v>520</v>
+        <v>511</v>
       </c>
     </row>
     <row r="202" spans="1:5">
@@ -5509,543 +5470,543 @@
         <v>89</v>
       </c>
       <c r="B202" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="C202" t="s">
-        <v>365</v>
+        <v>306</v>
       </c>
       <c r="D202" t="s">
-        <v>412</v>
+        <v>455</v>
       </c>
       <c r="E202" t="s">
-        <v>481</v>
+        <v>536</v>
       </c>
     </row>
     <row r="203" spans="1:5">
       <c r="A203" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B203" t="s">
-        <v>228</v>
+        <v>200</v>
       </c>
       <c r="C203" t="s">
-        <v>366</v>
+        <v>348</v>
       </c>
       <c r="D203" t="s">
-        <v>266</v>
+        <v>456</v>
       </c>
       <c r="E203" t="s">
-        <v>484</v>
+        <v>499</v>
       </c>
     </row>
     <row r="204" spans="1:5">
       <c r="A204" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B204" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="C204" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="D204" t="s">
-        <v>433</v>
+        <v>264</v>
       </c>
       <c r="E204" t="s">
-        <v>509</v>
+        <v>517</v>
       </c>
     </row>
     <row r="205" spans="1:5">
       <c r="A205" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B205" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="C205" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="D205" t="s">
-        <v>267</v>
+        <v>408</v>
       </c>
       <c r="E205" t="s">
-        <v>509</v>
+        <v>479</v>
       </c>
     </row>
     <row r="206" spans="1:5">
       <c r="A206" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B206" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="C206" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="D206" t="s">
-        <v>460</v>
+        <v>263</v>
       </c>
       <c r="E206" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
     </row>
     <row r="207" spans="1:5">
       <c r="A207" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B207" t="s">
-        <v>193</v>
+        <v>224</v>
       </c>
       <c r="C207" t="s">
-        <v>346</v>
+        <v>364</v>
       </c>
       <c r="D207" t="s">
-        <v>251</v>
+        <v>429</v>
       </c>
       <c r="E207" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
     </row>
     <row r="208" spans="1:5">
       <c r="A208" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B208" t="s">
-        <v>194</v>
+        <v>225</v>
       </c>
       <c r="C208" t="s">
-        <v>346</v>
+        <v>364</v>
       </c>
       <c r="D208" t="s">
-        <v>425</v>
+        <v>264</v>
       </c>
       <c r="E208" t="s">
-        <v>533</v>
+        <v>507</v>
       </c>
     </row>
     <row r="209" spans="1:5">
       <c r="A209" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B209" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="C209" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="D209" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="E209" t="s">
-        <v>501</v>
+        <v>482</v>
       </c>
     </row>
     <row r="210" spans="1:5">
       <c r="A210" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B210" t="s">
-        <v>231</v>
+        <v>189</v>
       </c>
       <c r="C210" t="s">
-        <v>368</v>
+        <v>343</v>
       </c>
       <c r="D210" t="s">
-        <v>267</v>
+        <v>247</v>
       </c>
       <c r="E210" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
     </row>
     <row r="211" spans="1:5">
       <c r="A211" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B211" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C211" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="D211" t="s">
-        <v>251</v>
+        <v>421</v>
       </c>
       <c r="E211" t="s">
-        <v>520</v>
+        <v>527</v>
       </c>
     </row>
     <row r="212" spans="1:5">
       <c r="A212" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B212" t="s">
-        <v>193</v>
+        <v>213</v>
       </c>
       <c r="C212" t="s">
-        <v>364</v>
+        <v>353</v>
       </c>
       <c r="D212" t="s">
-        <v>420</v>
+        <v>458</v>
       </c>
       <c r="E212" t="s">
-        <v>481</v>
+        <v>499</v>
       </c>
     </row>
     <row r="213" spans="1:5">
       <c r="A213" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B213" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="C213" t="s">
-        <v>343</v>
+        <v>365</v>
       </c>
       <c r="D213" t="s">
-        <v>462</v>
+        <v>264</v>
       </c>
       <c r="E213" t="s">
-        <v>488</v>
+        <v>511</v>
       </c>
     </row>
     <row r="214" spans="1:5">
       <c r="A214" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B214" t="s">
-        <v>230</v>
+        <v>189</v>
       </c>
       <c r="C214" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="D214" t="s">
-        <v>432</v>
+        <v>247</v>
       </c>
       <c r="E214" t="s">
-        <v>494</v>
+        <v>517</v>
       </c>
     </row>
     <row r="215" spans="1:5">
       <c r="A215" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B215" t="s">
-        <v>231</v>
+        <v>189</v>
       </c>
       <c r="C215" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="D215" t="s">
-        <v>267</v>
+        <v>416</v>
       </c>
       <c r="E215" t="s">
-        <v>544</v>
+        <v>479</v>
       </c>
     </row>
     <row r="216" spans="1:5">
       <c r="A216" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B216" t="s">
-        <v>233</v>
+        <v>190</v>
       </c>
       <c r="C216" t="s">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="D216" t="s">
-        <v>267</v>
+        <v>459</v>
       </c>
       <c r="E216" t="s">
-        <v>545</v>
+        <v>535</v>
       </c>
     </row>
     <row r="217" spans="1:5">
       <c r="A217" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B217" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="C217" t="s">
-        <v>355</v>
+        <v>336</v>
       </c>
       <c r="D217" t="s">
-        <v>252</v>
+        <v>460</v>
       </c>
       <c r="E217" t="s">
-        <v>546</v>
+        <v>486</v>
       </c>
     </row>
     <row r="218" spans="1:5">
       <c r="A218" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B218" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="C218" t="s">
-        <v>369</v>
+        <v>343</v>
       </c>
       <c r="D218" t="s">
-        <v>450</v>
+        <v>428</v>
       </c>
       <c r="E218" t="s">
-        <v>517</v>
+        <v>492</v>
       </c>
     </row>
     <row r="219" spans="1:5">
       <c r="A219" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B219" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="C219" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="D219" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="E219" t="s">
-        <v>547</v>
+        <v>537</v>
       </c>
     </row>
     <row r="220" spans="1:5">
       <c r="A220" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B220" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="C220" t="s">
-        <v>356</v>
+        <v>339</v>
       </c>
       <c r="D220" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E220" t="s">
-        <v>548</v>
+        <v>538</v>
       </c>
     </row>
     <row r="221" spans="1:5">
       <c r="A221" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B221" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="C221" t="s">
-        <v>336</v>
+        <v>352</v>
       </c>
       <c r="D221" t="s">
-        <v>267</v>
+        <v>248</v>
       </c>
       <c r="E221" t="s">
-        <v>544</v>
+        <v>539</v>
       </c>
     </row>
     <row r="222" spans="1:5">
       <c r="A222" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B222" t="s">
-        <v>199</v>
+        <v>230</v>
       </c>
       <c r="C222" t="s">
-        <v>342</v>
+        <v>366</v>
       </c>
       <c r="D222" t="s">
-        <v>267</v>
+        <v>447</v>
       </c>
       <c r="E222" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
     </row>
     <row r="223" spans="1:5">
       <c r="A223" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B223" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="C223" t="s">
-        <v>370</v>
+        <v>357</v>
       </c>
       <c r="D223" t="s">
-        <v>267</v>
+        <v>248</v>
       </c>
       <c r="E223" t="s">
-        <v>484</v>
+        <v>540</v>
       </c>
     </row>
     <row r="224" spans="1:5">
       <c r="A224" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B224" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="C224" t="s">
         <v>353</v>
       </c>
       <c r="D224" t="s">
-        <v>423</v>
+        <v>264</v>
       </c>
       <c r="E224" t="s">
-        <v>485</v>
+        <v>541</v>
       </c>
     </row>
     <row r="225" spans="1:5">
       <c r="A225" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B225" t="s">
-        <v>201</v>
+        <v>233</v>
       </c>
       <c r="C225" t="s">
-        <v>356</v>
+        <v>333</v>
       </c>
       <c r="D225" t="s">
-        <v>463</v>
+        <v>264</v>
       </c>
       <c r="E225" t="s">
-        <v>503</v>
+        <v>537</v>
       </c>
     </row>
     <row r="226" spans="1:5">
       <c r="A226" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B226" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="C226" t="s">
-        <v>353</v>
+        <v>340</v>
       </c>
       <c r="D226" t="s">
-        <v>445</v>
+        <v>264</v>
       </c>
       <c r="E226" t="s">
-        <v>520</v>
+        <v>507</v>
       </c>
     </row>
     <row r="227" spans="1:5">
       <c r="A227" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B227" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="C227" t="s">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="D227" t="s">
-        <v>458</v>
+        <v>264</v>
       </c>
       <c r="E227" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="228" spans="1:5">
       <c r="A228" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B228" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="C228" t="s">
-        <v>336</v>
+        <v>350</v>
       </c>
       <c r="D228" t="s">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="E228" t="s">
-        <v>505</v>
+        <v>483</v>
       </c>
     </row>
     <row r="229" spans="1:5">
       <c r="A229" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B229" t="s">
-        <v>242</v>
+        <v>197</v>
       </c>
       <c r="C229" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="D229" t="s">
-        <v>421</v>
+        <v>461</v>
       </c>
       <c r="E229" t="s">
-        <v>529</v>
+        <v>501</v>
       </c>
     </row>
     <row r="230" spans="1:5">
       <c r="A230" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B230" t="s">
-        <v>243</v>
+        <v>197</v>
       </c>
       <c r="C230" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="D230" t="s">
-        <v>267</v>
+        <v>441</v>
       </c>
       <c r="E230" t="s">
-        <v>506</v>
+        <v>517</v>
       </c>
     </row>
     <row r="231" spans="1:5">
       <c r="A231" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B231" t="s">
-        <v>210</v>
+        <v>236</v>
       </c>
       <c r="C231" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="D231" t="s">
-        <v>404</v>
+        <v>455</v>
       </c>
       <c r="E231" t="s">
-        <v>492</v>
+        <v>479</v>
       </c>
     </row>
     <row r="232" spans="1:5">
       <c r="A232" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B232" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="C232" t="s">
-        <v>353</v>
+        <v>333</v>
       </c>
       <c r="D232" t="s">
-        <v>441</v>
+        <v>423</v>
       </c>
       <c r="E232" t="s">
-        <v>522</v>
+        <v>503</v>
       </c>
     </row>
     <row r="233" spans="1:5">
       <c r="A233" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B233" t="s">
-        <v>227</v>
+        <v>238</v>
       </c>
       <c r="C233" t="s">
-        <v>371</v>
+        <v>353</v>
       </c>
       <c r="D233" t="s">
-        <v>458</v>
+        <v>417</v>
       </c>
       <c r="E233" t="s">
-        <v>549</v>
+        <v>525</v>
       </c>
     </row>
     <row r="234" spans="1:5">
@@ -6053,16 +6014,16 @@
         <v>101</v>
       </c>
       <c r="B234" t="s">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="C234" t="s">
-        <v>372</v>
+        <v>354</v>
       </c>
       <c r="D234" t="s">
-        <v>464</v>
+        <v>264</v>
       </c>
       <c r="E234" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
     </row>
     <row r="235" spans="1:5">
@@ -6070,319 +6031,319 @@
         <v>101</v>
       </c>
       <c r="B235" t="s">
-        <v>227</v>
+        <v>206</v>
       </c>
       <c r="C235" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D235" t="s">
-        <v>415</v>
+        <v>400</v>
       </c>
       <c r="E235" t="s">
-        <v>539</v>
+        <v>490</v>
       </c>
     </row>
     <row r="236" spans="1:5">
       <c r="A236" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B236" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="C236" t="s">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="D236" t="s">
-        <v>267</v>
+        <v>437</v>
       </c>
       <c r="E236" t="s">
-        <v>496</v>
+        <v>519</v>
       </c>
     </row>
     <row r="237" spans="1:5">
       <c r="A237" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B237" t="s">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="C237" t="s">
-        <v>355</v>
+        <v>368</v>
       </c>
       <c r="D237" t="s">
-        <v>465</v>
+        <v>455</v>
       </c>
       <c r="E237" t="s">
-        <v>497</v>
+        <v>542</v>
       </c>
     </row>
     <row r="238" spans="1:5">
       <c r="A238" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B238" t="s">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="C238" t="s">
-        <v>358</v>
+        <v>369</v>
       </c>
       <c r="D238" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="E238" t="s">
-        <v>489</v>
+        <v>506</v>
       </c>
     </row>
     <row r="239" spans="1:5">
       <c r="A239" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B239" t="s">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="C239" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="D239" t="s">
-        <v>446</v>
+        <v>411</v>
       </c>
       <c r="E239" t="s">
-        <v>550</v>
+        <v>533</v>
       </c>
     </row>
     <row r="240" spans="1:5">
       <c r="A240" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B240" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="C240" t="s">
-        <v>373</v>
+        <v>339</v>
       </c>
       <c r="D240" t="s">
-        <v>443</v>
+        <v>264</v>
       </c>
       <c r="E240" t="s">
-        <v>485</v>
+        <v>494</v>
       </c>
     </row>
     <row r="241" spans="1:5">
       <c r="A241" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B241" t="s">
-        <v>244</v>
+        <v>208</v>
       </c>
       <c r="C241" t="s">
-        <v>372</v>
+        <v>352</v>
       </c>
       <c r="D241" t="s">
-        <v>267</v>
+        <v>463</v>
       </c>
       <c r="E241" t="s">
-        <v>508</v>
+        <v>495</v>
       </c>
     </row>
     <row r="242" spans="1:5">
       <c r="A242" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B242" t="s">
-        <v>245</v>
+        <v>208</v>
       </c>
       <c r="C242" t="s">
-        <v>371</v>
+        <v>355</v>
       </c>
       <c r="D242" t="s">
-        <v>267</v>
+        <v>464</v>
       </c>
       <c r="E242" t="s">
-        <v>507</v>
+        <v>487</v>
       </c>
     </row>
     <row r="243" spans="1:5">
       <c r="A243" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B243" t="s">
-        <v>246</v>
+        <v>208</v>
       </c>
       <c r="C243" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="D243" t="s">
-        <v>267</v>
+        <v>442</v>
       </c>
       <c r="E243" t="s">
-        <v>506</v>
+        <v>543</v>
       </c>
     </row>
     <row r="244" spans="1:5">
       <c r="A244" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B244" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="C244" t="s">
-        <v>356</v>
+        <v>370</v>
       </c>
       <c r="D244" t="s">
-        <v>405</v>
+        <v>439</v>
       </c>
       <c r="E244" t="s">
-        <v>551</v>
+        <v>483</v>
       </c>
     </row>
     <row r="245" spans="1:5">
       <c r="A245" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B245" t="s">
-        <v>214</v>
+        <v>240</v>
       </c>
       <c r="C245" t="s">
-        <v>336</v>
+        <v>369</v>
       </c>
       <c r="D245" t="s">
-        <v>404</v>
+        <v>264</v>
       </c>
       <c r="E245" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="246" spans="1:5">
       <c r="A246" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B246" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="C246" t="s">
-        <v>336</v>
+        <v>368</v>
       </c>
       <c r="D246" t="s">
-        <v>405</v>
+        <v>264</v>
       </c>
       <c r="E246" t="s">
-        <v>539</v>
+        <v>505</v>
       </c>
     </row>
     <row r="247" spans="1:5">
       <c r="A247" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B247" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="C247" t="s">
-        <v>356</v>
+        <v>347</v>
       </c>
       <c r="D247" t="s">
-        <v>464</v>
+        <v>264</v>
       </c>
       <c r="E247" t="s">
-        <v>538</v>
+        <v>504</v>
       </c>
     </row>
     <row r="248" spans="1:5">
       <c r="A248" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B248" t="s">
-        <v>236</v>
+        <v>210</v>
       </c>
       <c r="C248" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="D248" t="s">
-        <v>267</v>
+        <v>401</v>
       </c>
       <c r="E248" t="s">
-        <v>492</v>
+        <v>525</v>
       </c>
     </row>
     <row r="249" spans="1:5">
       <c r="A249" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B249" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C249" t="s">
-        <v>350</v>
+        <v>333</v>
       </c>
       <c r="D249" t="s">
-        <v>467</v>
+        <v>400</v>
       </c>
       <c r="E249" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="250" spans="1:5">
       <c r="A250" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B250" t="s">
-        <v>217</v>
+        <v>243</v>
       </c>
       <c r="C250" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="D250" t="s">
-        <v>412</v>
+        <v>401</v>
       </c>
       <c r="E250" t="s">
-        <v>499</v>
+        <v>533</v>
       </c>
     </row>
     <row r="251" spans="1:5">
       <c r="A251" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B251" t="s">
-        <v>217</v>
+        <v>243</v>
       </c>
       <c r="C251" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="D251" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="E251" t="s">
-        <v>500</v>
+        <v>532</v>
       </c>
     </row>
     <row r="252" spans="1:5">
       <c r="A252" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B252" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="C252" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="D252" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E252" t="s">
-        <v>500</v>
+        <v>490</v>
       </c>
     </row>
     <row r="253" spans="1:5">
       <c r="A253" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B253" t="s">
-        <v>237</v>
+        <v>207</v>
       </c>
       <c r="C253" t="s">
-        <v>336</v>
+        <v>347</v>
       </c>
       <c r="D253" t="s">
-        <v>267</v>
+        <v>465</v>
       </c>
       <c r="E253" t="s">
         <v>499</v>
@@ -6390,274 +6351,274 @@
     </row>
     <row r="254" spans="1:5">
       <c r="A254" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B254" t="s">
-        <v>236</v>
+        <v>213</v>
       </c>
       <c r="C254" t="s">
-        <v>356</v>
+        <v>333</v>
       </c>
       <c r="D254" t="s">
-        <v>267</v>
+        <v>408</v>
       </c>
       <c r="E254" t="s">
-        <v>515</v>
+        <v>497</v>
       </c>
     </row>
     <row r="255" spans="1:5">
       <c r="A255" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B255" t="s">
-        <v>248</v>
+        <v>213</v>
       </c>
       <c r="C255" t="s">
-        <v>363</v>
+        <v>352</v>
       </c>
       <c r="D255" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="E255" t="s">
-        <v>506</v>
+        <v>498</v>
       </c>
     </row>
     <row r="256" spans="1:5">
       <c r="A256" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B256" t="s">
-        <v>139</v>
+        <v>176</v>
       </c>
       <c r="C256" t="s">
-        <v>284</v>
+        <v>308</v>
       </c>
       <c r="D256" t="s">
-        <v>465</v>
+        <v>264</v>
       </c>
       <c r="E256" t="s">
-        <v>489</v>
+        <v>499</v>
       </c>
     </row>
     <row r="257" spans="1:5">
       <c r="A257" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B257" t="s">
-        <v>144</v>
+        <v>232</v>
       </c>
       <c r="C257" t="s">
-        <v>284</v>
+        <v>353</v>
       </c>
       <c r="D257" t="s">
-        <v>468</v>
+        <v>264</v>
       </c>
       <c r="E257" t="s">
-        <v>552</v>
+        <v>498</v>
       </c>
     </row>
     <row r="258" spans="1:5">
       <c r="A258" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B258" t="s">
-        <v>211</v>
+        <v>233</v>
       </c>
       <c r="C258" t="s">
-        <v>353</v>
+        <v>333</v>
       </c>
       <c r="D258" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E258" t="s">
-        <v>553</v>
+        <v>497</v>
       </c>
     </row>
     <row r="259" spans="1:5">
       <c r="A259" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B259" t="s">
-        <v>247</v>
+        <v>232</v>
       </c>
       <c r="C259" t="s">
-        <v>373</v>
+        <v>353</v>
       </c>
       <c r="D259" t="s">
-        <v>469</v>
+        <v>264</v>
       </c>
       <c r="E259" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
     </row>
     <row r="260" spans="1:5">
       <c r="A260" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B260" t="s">
-        <v>216</v>
+        <v>244</v>
       </c>
       <c r="C260" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="D260" t="s">
-        <v>267</v>
+        <v>460</v>
       </c>
       <c r="E260" t="s">
-        <v>554</v>
+        <v>504</v>
       </c>
     </row>
     <row r="261" spans="1:5">
       <c r="A261" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B261" t="s">
-        <v>217</v>
+        <v>132</v>
       </c>
       <c r="C261" t="s">
-        <v>356</v>
+        <v>280</v>
       </c>
       <c r="D261" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="E261" t="s">
-        <v>555</v>
+        <v>487</v>
       </c>
     </row>
     <row r="262" spans="1:5">
       <c r="A262" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B262" t="s">
-        <v>217</v>
+        <v>137</v>
       </c>
       <c r="C262" t="s">
-        <v>336</v>
+        <v>280</v>
       </c>
       <c r="D262" t="s">
-        <v>412</v>
+        <v>466</v>
       </c>
       <c r="E262" t="s">
-        <v>556</v>
+        <v>544</v>
       </c>
     </row>
     <row r="263" spans="1:5">
       <c r="A263" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B263" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="C263" t="s">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="D263" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E263" t="s">
-        <v>514</v>
+        <v>545</v>
       </c>
     </row>
     <row r="264" spans="1:5">
       <c r="A264" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B264" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="C264" t="s">
-        <v>356</v>
+        <v>370</v>
       </c>
       <c r="D264" t="s">
-        <v>267</v>
+        <v>467</v>
       </c>
       <c r="E264" t="s">
-        <v>557</v>
+        <v>507</v>
       </c>
     </row>
     <row r="265" spans="1:5">
       <c r="A265" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B265" t="s">
-        <v>249</v>
+        <v>212</v>
       </c>
       <c r="C265" t="s">
-        <v>374</v>
+        <v>355</v>
       </c>
       <c r="D265" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E265" t="s">
-        <v>508</v>
+        <v>546</v>
       </c>
     </row>
     <row r="266" spans="1:5">
       <c r="A266" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B266" t="s">
-        <v>170</v>
+        <v>213</v>
       </c>
       <c r="C266" t="s">
-        <v>375</v>
+        <v>353</v>
       </c>
       <c r="D266" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="E266" t="s">
-        <v>506</v>
+        <v>547</v>
       </c>
     </row>
     <row r="267" spans="1:5">
       <c r="A267" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B267" t="s">
-        <v>250</v>
+        <v>213</v>
       </c>
       <c r="C267" t="s">
-        <v>376</v>
+        <v>333</v>
       </c>
       <c r="D267" t="s">
-        <v>449</v>
+        <v>408</v>
       </c>
       <c r="E267" t="s">
-        <v>487</v>
+        <v>548</v>
       </c>
     </row>
     <row r="268" spans="1:5">
       <c r="A268" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B268" t="s">
-        <v>251</v>
+        <v>212</v>
       </c>
       <c r="C268" t="s">
-        <v>377</v>
+        <v>355</v>
       </c>
       <c r="D268" t="s">
-        <v>440</v>
+        <v>264</v>
       </c>
       <c r="E268" t="s">
-        <v>492</v>
+        <v>511</v>
       </c>
     </row>
     <row r="269" spans="1:5">
       <c r="A269" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B269" t="s">
-        <v>252</v>
+        <v>232</v>
       </c>
       <c r="C269" t="s">
-        <v>378</v>
+        <v>353</v>
       </c>
       <c r="D269" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E269" t="s">
-        <v>481</v>
+        <v>549</v>
       </c>
     </row>
     <row r="270" spans="1:5">
@@ -6665,16 +6626,16 @@
         <v>113</v>
       </c>
       <c r="B270" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="C270" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="D270" t="s">
-        <v>456</v>
+        <v>264</v>
       </c>
       <c r="E270" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
     </row>
     <row r="271" spans="1:5">
@@ -6682,16 +6643,16 @@
         <v>113</v>
       </c>
       <c r="B271" t="s">
-        <v>254</v>
+        <v>163</v>
       </c>
       <c r="C271" t="s">
-        <v>335</v>
+        <v>372</v>
       </c>
       <c r="D271" t="s">
-        <v>267</v>
+        <v>453</v>
       </c>
       <c r="E271" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="272" spans="1:5">
@@ -6699,16 +6660,16 @@
         <v>113</v>
       </c>
       <c r="B272" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="C272" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="D272" t="s">
-        <v>401</v>
+        <v>446</v>
       </c>
       <c r="E272" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
     </row>
     <row r="273" spans="1:5">
@@ -6716,101 +6677,101 @@
         <v>113</v>
       </c>
       <c r="B273" t="s">
-        <v>206</v>
+        <v>247</v>
       </c>
       <c r="C273" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="D273" t="s">
-        <v>470</v>
+        <v>436</v>
       </c>
       <c r="E273" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="274" spans="1:5">
       <c r="A274" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B274" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="C274" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="D274" t="s">
-        <v>401</v>
+        <v>264</v>
       </c>
       <c r="E274" t="s">
-        <v>508</v>
+        <v>479</v>
       </c>
     </row>
     <row r="275" spans="1:5">
       <c r="A275" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B275" t="s">
-        <v>151</v>
+        <v>249</v>
       </c>
       <c r="C275" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="D275" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="E275" t="s">
-        <v>506</v>
+        <v>499</v>
       </c>
     </row>
     <row r="276" spans="1:5">
       <c r="A276" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B276" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="C276" t="s">
-        <v>383</v>
+        <v>332</v>
       </c>
       <c r="D276" t="s">
-        <v>446</v>
+        <v>264</v>
       </c>
       <c r="E276" t="s">
-        <v>492</v>
+        <v>503</v>
       </c>
     </row>
     <row r="277" spans="1:5">
       <c r="A277" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B277" t="s">
-        <v>167</v>
+        <v>251</v>
       </c>
       <c r="C277" t="s">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="D277" t="s">
-        <v>449</v>
+        <v>397</v>
       </c>
       <c r="E277" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="278" spans="1:5">
       <c r="A278" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B278" t="s">
-        <v>178</v>
+        <v>202</v>
       </c>
       <c r="C278" t="s">
-        <v>334</v>
+        <v>368</v>
       </c>
       <c r="D278" t="s">
-        <v>267</v>
+        <v>468</v>
       </c>
       <c r="E278" t="s">
-        <v>501</v>
+        <v>482</v>
       </c>
     </row>
     <row r="279" spans="1:5">
@@ -6818,16 +6779,16 @@
         <v>114</v>
       </c>
       <c r="B279" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="C279" t="s">
-        <v>289</v>
+        <v>378</v>
       </c>
       <c r="D279" t="s">
-        <v>471</v>
+        <v>397</v>
       </c>
       <c r="E279" t="s">
-        <v>481</v>
+        <v>506</v>
       </c>
     </row>
     <row r="280" spans="1:5">
@@ -6835,16 +6796,16 @@
         <v>114</v>
       </c>
       <c r="B280" t="s">
-        <v>193</v>
+        <v>144</v>
       </c>
       <c r="C280" t="s">
-        <v>361</v>
+        <v>379</v>
       </c>
       <c r="D280" t="s">
-        <v>400</v>
+        <v>453</v>
       </c>
       <c r="E280" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="281" spans="1:5">
@@ -6852,101 +6813,101 @@
         <v>114</v>
       </c>
       <c r="B281" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="C281" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="D281" t="s">
-        <v>468</v>
+        <v>442</v>
       </c>
       <c r="E281" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="282" spans="1:5">
       <c r="A282" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B282" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="C282" t="s">
-        <v>193</v>
+        <v>381</v>
       </c>
       <c r="D282" t="s">
-        <v>267</v>
+        <v>446</v>
       </c>
       <c r="E282" t="s">
-        <v>508</v>
+        <v>485</v>
       </c>
     </row>
     <row r="283" spans="1:5">
       <c r="A283" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B283" t="s">
-        <v>259</v>
+        <v>173</v>
       </c>
       <c r="C283" t="s">
-        <v>385</v>
+        <v>331</v>
       </c>
       <c r="D283" t="s">
-        <v>155</v>
+        <v>264</v>
       </c>
       <c r="E283" t="s">
-        <v>506</v>
+        <v>499</v>
       </c>
     </row>
     <row r="284" spans="1:5">
       <c r="A284" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B284" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="C284" t="s">
-        <v>386</v>
+        <v>285</v>
       </c>
       <c r="D284" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="E284" t="s">
-        <v>492</v>
+        <v>479</v>
       </c>
     </row>
     <row r="285" spans="1:5">
       <c r="A285" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B285" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="C285" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="D285" t="s">
-        <v>267</v>
+        <v>396</v>
       </c>
       <c r="E285" t="s">
-        <v>481</v>
+        <v>503</v>
       </c>
     </row>
     <row r="286" spans="1:5">
       <c r="A286" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B286" t="s">
-        <v>230</v>
+        <v>254</v>
       </c>
       <c r="C286" t="s">
-        <v>387</v>
+        <v>366</v>
       </c>
       <c r="D286" t="s">
-        <v>473</v>
+        <v>466</v>
       </c>
       <c r="E286" t="s">
-        <v>505</v>
+        <v>486</v>
       </c>
     </row>
     <row r="287" spans="1:5">
@@ -6954,509 +6915,475 @@
         <v>115</v>
       </c>
       <c r="B287" t="s">
-        <v>261</v>
+        <v>163</v>
       </c>
       <c r="C287" t="s">
-        <v>345</v>
+        <v>189</v>
       </c>
       <c r="D287" t="s">
-        <v>250</v>
+        <v>264</v>
       </c>
       <c r="E287" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
     </row>
     <row r="288" spans="1:5">
       <c r="A288" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B288" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="C288" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="D288" t="s">
-        <v>443</v>
+        <v>148</v>
       </c>
       <c r="E288" t="s">
-        <v>492</v>
+        <v>504</v>
       </c>
     </row>
     <row r="289" spans="1:5">
       <c r="A289" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B289" t="s">
-        <v>159</v>
+        <v>256</v>
       </c>
       <c r="C289" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="D289" t="s">
-        <v>449</v>
+        <v>470</v>
       </c>
       <c r="E289" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="290" spans="1:5">
       <c r="A290" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B290" t="s">
-        <v>181</v>
+        <v>257</v>
       </c>
       <c r="C290" t="s">
-        <v>312</v>
+        <v>384</v>
       </c>
       <c r="D290" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E290" t="s">
-        <v>506</v>
+        <v>485</v>
       </c>
     </row>
     <row r="291" spans="1:5">
       <c r="A291" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B291" t="s">
-        <v>263</v>
+        <v>201</v>
       </c>
       <c r="C291" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D291" t="s">
-        <v>474</v>
+        <v>264</v>
       </c>
       <c r="E291" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
     <row r="292" spans="1:5">
       <c r="A292" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B292" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="C292" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="D292" t="s">
-        <v>446</v>
+        <v>471</v>
       </c>
       <c r="E292" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="293" spans="1:5">
       <c r="A293" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B293" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="C293" t="s">
-        <v>391</v>
+        <v>342</v>
       </c>
       <c r="D293" t="s">
-        <v>267</v>
+        <v>246</v>
       </c>
       <c r="E293" t="s">
-        <v>487</v>
+        <v>499</v>
       </c>
     </row>
     <row r="294" spans="1:5">
       <c r="A294" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B294" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="C294" t="s">
-        <v>363</v>
+        <v>386</v>
       </c>
       <c r="D294" t="s">
-        <v>422</v>
+        <v>439</v>
       </c>
       <c r="E294" t="s">
-        <v>481</v>
+        <v>490</v>
       </c>
     </row>
     <row r="295" spans="1:5">
       <c r="A295" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B295" t="s">
-        <v>220</v>
+        <v>152</v>
       </c>
       <c r="C295" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="D295" t="s">
-        <v>415</v>
+        <v>446</v>
       </c>
       <c r="E295" t="s">
-        <v>505</v>
+        <v>485</v>
       </c>
     </row>
     <row r="296" spans="1:5">
       <c r="A296" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B296" t="s">
-        <v>266</v>
+        <v>176</v>
       </c>
       <c r="C296" t="s">
-        <v>237</v>
+        <v>308</v>
       </c>
       <c r="D296" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E296" t="s">
-        <v>558</v>
+        <v>504</v>
       </c>
     </row>
     <row r="297" spans="1:5">
       <c r="A297" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B297" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="C297" t="s">
-        <v>392</v>
+        <v>349</v>
       </c>
       <c r="D297" t="s">
-        <v>267</v>
+        <v>472</v>
       </c>
       <c r="E297" t="s">
-        <v>559</v>
+        <v>479</v>
       </c>
     </row>
     <row r="298" spans="1:5">
       <c r="A298" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B298" t="s">
-        <v>266</v>
+        <v>210</v>
       </c>
       <c r="C298" t="s">
-        <v>237</v>
+        <v>388</v>
       </c>
       <c r="D298" t="s">
-        <v>267</v>
+        <v>442</v>
       </c>
       <c r="E298" t="s">
-        <v>560</v>
+        <v>503</v>
       </c>
     </row>
     <row r="299" spans="1:5">
       <c r="A299" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B299" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="C299" t="s">
-        <v>245</v>
+        <v>389</v>
       </c>
       <c r="D299" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E299" t="s">
-        <v>561</v>
+        <v>485</v>
       </c>
     </row>
     <row r="300" spans="1:5">
       <c r="A300" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B300" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="C300" t="s">
-        <v>393</v>
+        <v>360</v>
       </c>
       <c r="D300" t="s">
-        <v>173</v>
+        <v>418</v>
       </c>
       <c r="E300" t="s">
-        <v>512</v>
+        <v>479</v>
       </c>
     </row>
     <row r="301" spans="1:5">
       <c r="A301" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="B301" t="s">
-        <v>266</v>
+        <v>216</v>
       </c>
       <c r="C301" t="s">
-        <v>237</v>
+        <v>388</v>
       </c>
       <c r="D301" t="s">
-        <v>267</v>
+        <v>411</v>
       </c>
       <c r="E301" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="302" spans="1:5">
       <c r="A302" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="B302" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="C302" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="D302" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E302" t="s">
-        <v>562</v>
+        <v>550</v>
       </c>
     </row>
     <row r="303" spans="1:5">
       <c r="A303" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="B303" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="C303" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="D303" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E303" t="s">
-        <v>528</v>
+        <v>551</v>
       </c>
     </row>
     <row r="304" spans="1:5">
       <c r="A304" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B304" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C304" t="s">
-        <v>237</v>
+        <v>390</v>
       </c>
       <c r="D304" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E304" t="s">
-        <v>563</v>
+        <v>524</v>
       </c>
     </row>
     <row r="305" spans="1:5">
       <c r="A305" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="B305" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="C305" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="D305" t="s">
-        <v>428</v>
+        <v>264</v>
       </c>
       <c r="E305" t="s">
-        <v>564</v>
+        <v>552</v>
       </c>
     </row>
     <row r="306" spans="1:5">
       <c r="A306" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="B306" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="C306" t="s">
-        <v>271</v>
+        <v>233</v>
       </c>
       <c r="D306" t="s">
-        <v>267</v>
+        <v>424</v>
       </c>
       <c r="E306" t="s">
-        <v>565</v>
+        <v>553</v>
       </c>
     </row>
     <row r="307" spans="1:5">
       <c r="A307" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="B307" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C307" t="s">
-        <v>237</v>
+        <v>267</v>
       </c>
       <c r="D307" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E307" t="s">
-        <v>566</v>
+        <v>554</v>
       </c>
     </row>
     <row r="308" spans="1:5">
       <c r="A308" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="B308" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="C308" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="D308" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E308" t="s">
-        <v>567</v>
+        <v>555</v>
       </c>
     </row>
     <row r="309" spans="1:5">
       <c r="A309" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="B309" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C309" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="D309" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E309" t="s">
-        <v>568</v>
+        <v>556</v>
       </c>
     </row>
     <row r="310" spans="1:5">
       <c r="A310" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="B310" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="C310" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="D310" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E310" t="s">
-        <v>492</v>
+        <v>557</v>
       </c>
     </row>
     <row r="311" spans="1:5">
       <c r="A311" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B311" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="C311" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="D311" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E311" t="s">
-        <v>568</v>
+        <v>556</v>
       </c>
     </row>
     <row r="312" spans="1:5">
       <c r="A312" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="B312" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="C312" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="D312" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="E312" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="313" spans="1:5">
       <c r="A313" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="B313" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="C313" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="D313" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E313" t="s">
-        <v>569</v>
+        <v>519</v>
       </c>
     </row>
     <row r="314" spans="1:5">
       <c r="A314" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="B314" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C314" t="s">
         <v>392</v>
       </c>
       <c r="D314" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E314" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="315" spans="1:5">
-      <c r="A315" t="s">
-        <v>134</v>
-      </c>
-      <c r="B315" t="s">
-        <v>272</v>
-      </c>
-      <c r="C315" t="s">
-        <v>396</v>
-      </c>
-      <c r="D315" t="s">
-        <v>267</v>
-      </c>
-      <c r="E315" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="316" spans="1:5">
-      <c r="A316" t="s">
-        <v>135</v>
-      </c>
-      <c r="B316" t="s">
-        <v>266</v>
-      </c>
-      <c r="C316" t="s">
-        <v>237</v>
-      </c>
-      <c r="D316" t="s">
-        <v>267</v>
-      </c>
-      <c r="E316" t="s">
-        <v>570</v>
+        <v>486</v>
       </c>
     </row>
   </sheetData>

--- a/data/TTC/班別時間對照表/TTC_TD_當月班別時間對照表.xlsx
+++ b/data/TTC/班別時間對照表/TTC_TD_當月班別時間對照表.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1570" uniqueCount="558">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1575" uniqueCount="561">
   <si>
     <t>班別代號</t>
   </si>
@@ -382,6 +382,9 @@
     <t>NGRSD</t>
   </si>
   <si>
+    <t>NGRSN</t>
+  </si>
+  <si>
     <t>OGC4</t>
   </si>
   <si>
@@ -403,67 +406,67 @@
     <t>TTC1</t>
   </si>
   <si>
-    <t>3:59</t>
-  </si>
-  <si>
-    <t>4:53</t>
-  </si>
-  <si>
-    <t>4:10</t>
-  </si>
-  <si>
-    <t>4:11</t>
-  </si>
-  <si>
-    <t>4:15</t>
-  </si>
-  <si>
-    <t>6:49</t>
-  </si>
-  <si>
-    <t>4:50</t>
-  </si>
-  <si>
-    <t>5:02</t>
-  </si>
-  <si>
-    <t>4:34</t>
-  </si>
-  <si>
-    <t>5:09</t>
-  </si>
-  <si>
-    <t>6:53</t>
+    <t>03:59</t>
+  </si>
+  <si>
+    <t>04:53</t>
+  </si>
+  <si>
+    <t>04:10</t>
+  </si>
+  <si>
+    <t>04:11</t>
+  </si>
+  <si>
+    <t>04:15</t>
+  </si>
+  <si>
+    <t>06:49</t>
+  </si>
+  <si>
+    <t>04:50</t>
+  </si>
+  <si>
+    <t>05:02</t>
+  </si>
+  <si>
+    <t>04:34</t>
+  </si>
+  <si>
+    <t>05:09</t>
+  </si>
+  <si>
+    <t>06:53</t>
   </si>
   <si>
     <t>11:06</t>
   </si>
   <si>
-    <t>5:22</t>
-  </si>
-  <si>
-    <t>6:03</t>
-  </si>
-  <si>
-    <t>6:09</t>
-  </si>
-  <si>
-    <t>7:59</t>
-  </si>
-  <si>
-    <t>4:31</t>
-  </si>
-  <si>
-    <t>6:35</t>
-  </si>
-  <si>
-    <t>7:08</t>
-  </si>
-  <si>
-    <t>8:45</t>
-  </si>
-  <si>
-    <t>8:59</t>
+    <t>05:22</t>
+  </si>
+  <si>
+    <t>06:03</t>
+  </si>
+  <si>
+    <t>06:09</t>
+  </si>
+  <si>
+    <t>07:59</t>
+  </si>
+  <si>
+    <t>04:31</t>
+  </si>
+  <si>
+    <t>06:35</t>
+  </si>
+  <si>
+    <t>07:08</t>
+  </si>
+  <si>
+    <t>08:45</t>
+  </si>
+  <si>
+    <t>08:59</t>
   </si>
   <si>
     <t>10:59</t>
@@ -481,19 +484,19 @@
     <t>11:48</t>
   </si>
   <si>
-    <t>9:33</t>
-  </si>
-  <si>
-    <t>9:36</t>
+    <t>09:33</t>
+  </si>
+  <si>
+    <t>09:36</t>
   </si>
   <si>
     <t>11:59</t>
   </si>
   <si>
-    <t>4:04</t>
-  </si>
-  <si>
-    <t>4:24</t>
+    <t>04:04</t>
+  </si>
+  <si>
+    <t>04:24</t>
   </si>
   <si>
     <t>10:53</t>
@@ -502,16 +505,16 @@
     <t>10:04</t>
   </si>
   <si>
-    <t>5:58</t>
-  </si>
-  <si>
-    <t>6:59</t>
-  </si>
-  <si>
-    <t>4:41</t>
-  </si>
-  <si>
-    <t>4:47</t>
+    <t>05:58</t>
+  </si>
+  <si>
+    <t>06:59</t>
+  </si>
+  <si>
+    <t>04:41</t>
+  </si>
+  <si>
+    <t>04:47</t>
   </si>
   <si>
     <t>10:00</t>
@@ -529,10 +532,10 @@
     <t>11:33</t>
   </si>
   <si>
-    <t>4:52</t>
-  </si>
-  <si>
-    <t>5:57</t>
+    <t>04:52</t>
+  </si>
+  <si>
+    <t>05:57</t>
   </si>
   <si>
     <t>12:00</t>
@@ -751,16 +754,16 @@
     <t>17:27</t>
   </si>
   <si>
-    <t>5:28</t>
-  </si>
-  <si>
-    <t>8:53</t>
-  </si>
-  <si>
-    <t>9:22</t>
-  </si>
-  <si>
-    <t>9:59</t>
+    <t>05:28</t>
+  </si>
+  <si>
+    <t>08:53</t>
+  </si>
+  <si>
+    <t>09:22</t>
+  </si>
+  <si>
+    <t>09:59</t>
   </si>
   <si>
     <t>11:25</t>
@@ -772,7 +775,7 @@
     <t>12:50</t>
   </si>
   <si>
-    <t>6:37</t>
+    <t>06:37</t>
   </si>
   <si>
     <t>10:07</t>
@@ -805,16 +808,19 @@
     <t>17:22</t>
   </si>
   <si>
-    <t>8:30</t>
-  </si>
-  <si>
-    <t>8:00</t>
-  </si>
-  <si>
-    <t>7:30</t>
-  </si>
-  <si>
-    <t>4:00</t>
+    <t>08:30</t>
+  </si>
+  <si>
+    <t>08:00</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>07:30</t>
+  </si>
+  <si>
+    <t>04:00</t>
   </si>
   <si>
     <t>15:30</t>
@@ -1195,271 +1201,271 @@
     <t>21:00</t>
   </si>
   <si>
-    <t>9:41</t>
-  </si>
-  <si>
-    <t>8:41</t>
-  </si>
-  <si>
-    <t>8:46</t>
-  </si>
-  <si>
-    <t>8:36</t>
-  </si>
-  <si>
-    <t>8:38</t>
-  </si>
-  <si>
-    <t>9:15</t>
-  </si>
-  <si>
-    <t>8:40</t>
-  </si>
-  <si>
-    <t>8:37</t>
-  </si>
-  <si>
-    <t>8:32</t>
-  </si>
-  <si>
-    <t>8:49</t>
-  </si>
-  <si>
-    <t>8:44</t>
-  </si>
-  <si>
-    <t>8:04</t>
-  </si>
-  <si>
-    <t>9:45</t>
-  </si>
-  <si>
-    <t>9:42</t>
-  </si>
-  <si>
-    <t>9:06</t>
-  </si>
-  <si>
-    <t>8:26</t>
-  </si>
-  <si>
-    <t>9:58</t>
-  </si>
-  <si>
-    <t>9:32</t>
-  </si>
-  <si>
-    <t>8:05</t>
-  </si>
-  <si>
-    <t>9:38</t>
-  </si>
-  <si>
-    <t>9:03</t>
-  </si>
-  <si>
-    <t>8:24</t>
-  </si>
-  <si>
-    <t>8:22</t>
-  </si>
-  <si>
-    <t>9:23</t>
-  </si>
-  <si>
-    <t>9:20</t>
-  </si>
-  <si>
-    <t>8:33</t>
-  </si>
-  <si>
-    <t>9:05</t>
-  </si>
-  <si>
-    <t>9:01</t>
-  </si>
-  <si>
-    <t>8:42</t>
-  </si>
-  <si>
-    <t>8:16</t>
-  </si>
-  <si>
-    <t>9:53</t>
-  </si>
-  <si>
-    <t>9:00</t>
-  </si>
-  <si>
-    <t>8:29</t>
-  </si>
-  <si>
-    <t>9:56</t>
-  </si>
-  <si>
-    <t>8:52</t>
-  </si>
-  <si>
-    <t>9:21</t>
-  </si>
-  <si>
-    <t>8:55</t>
-  </si>
-  <si>
-    <t>9:24</t>
-  </si>
-  <si>
-    <t>8:23</t>
-  </si>
-  <si>
-    <t>8:13</t>
-  </si>
-  <si>
-    <t>9:13</t>
-  </si>
-  <si>
-    <t>9:07</t>
-  </si>
-  <si>
-    <t>9:12</t>
-  </si>
-  <si>
-    <t>8:18</t>
-  </si>
-  <si>
-    <t>8:25</t>
-  </si>
-  <si>
-    <t>8:12</t>
-  </si>
-  <si>
-    <t>8:19</t>
-  </si>
-  <si>
-    <t>9:55</t>
-  </si>
-  <si>
-    <t>9:02</t>
-  </si>
-  <si>
-    <t>8:57</t>
-  </si>
-  <si>
-    <t>9:54</t>
-  </si>
-  <si>
-    <t>9:04</t>
-  </si>
-  <si>
-    <t>9:35</t>
-  </si>
-  <si>
-    <t>8:10</t>
-  </si>
-  <si>
-    <t>8:15</t>
-  </si>
-  <si>
-    <t>8:03</t>
-  </si>
-  <si>
-    <t>8:51</t>
-  </si>
-  <si>
-    <t>9:18</t>
-  </si>
-  <si>
-    <t>8:17</t>
-  </si>
-  <si>
-    <t>9:16</t>
-  </si>
-  <si>
-    <t>8:07</t>
-  </si>
-  <si>
-    <t>8:08</t>
-  </si>
-  <si>
-    <t>8:35</t>
-  </si>
-  <si>
-    <t>8:31</t>
-  </si>
-  <si>
-    <t>9:30</t>
-  </si>
-  <si>
-    <t>8:21</t>
-  </si>
-  <si>
-    <t>9:11</t>
-  </si>
-  <si>
-    <t>8:28</t>
-  </si>
-  <si>
-    <t>9:37</t>
-  </si>
-  <si>
-    <t>8:27</t>
-  </si>
-  <si>
-    <t>8:43</t>
-  </si>
-  <si>
-    <t>8:34</t>
-  </si>
-  <si>
-    <t>8:11</t>
-  </si>
-  <si>
-    <t>8:20</t>
-  </si>
-  <si>
-    <t>8:09</t>
-  </si>
-  <si>
-    <t>8:56</t>
-  </si>
-  <si>
-    <t>8:14</t>
-  </si>
-  <si>
-    <t>8:01</t>
-  </si>
-  <si>
-    <t>9:28</t>
-  </si>
-  <si>
-    <t>9:27</t>
+    <t>09:41</t>
+  </si>
+  <si>
+    <t>08:41</t>
+  </si>
+  <si>
+    <t>08:46</t>
+  </si>
+  <si>
+    <t>08:36</t>
+  </si>
+  <si>
+    <t>08:38</t>
+  </si>
+  <si>
+    <t>09:15</t>
+  </si>
+  <si>
+    <t>08:40</t>
+  </si>
+  <si>
+    <t>08:37</t>
+  </si>
+  <si>
+    <t>08:32</t>
+  </si>
+  <si>
+    <t>08:49</t>
+  </si>
+  <si>
+    <t>08:44</t>
+  </si>
+  <si>
+    <t>08:04</t>
+  </si>
+  <si>
+    <t>09:45</t>
+  </si>
+  <si>
+    <t>09:42</t>
+  </si>
+  <si>
+    <t>09:06</t>
+  </si>
+  <si>
+    <t>08:26</t>
+  </si>
+  <si>
+    <t>09:58</t>
+  </si>
+  <si>
+    <t>09:32</t>
+  </si>
+  <si>
+    <t>08:05</t>
+  </si>
+  <si>
+    <t>09:38</t>
+  </si>
+  <si>
+    <t>09:03</t>
+  </si>
+  <si>
+    <t>08:24</t>
+  </si>
+  <si>
+    <t>08:22</t>
+  </si>
+  <si>
+    <t>09:23</t>
+  </si>
+  <si>
+    <t>09:20</t>
+  </si>
+  <si>
+    <t>08:33</t>
+  </si>
+  <si>
+    <t>09:05</t>
+  </si>
+  <si>
+    <t>09:01</t>
+  </si>
+  <si>
+    <t>08:42</t>
+  </si>
+  <si>
+    <t>08:16</t>
+  </si>
+  <si>
+    <t>09:53</t>
+  </si>
+  <si>
+    <t>09:00</t>
+  </si>
+  <si>
+    <t>08:29</t>
+  </si>
+  <si>
+    <t>09:56</t>
+  </si>
+  <si>
+    <t>08:52</t>
+  </si>
+  <si>
+    <t>09:21</t>
+  </si>
+  <si>
+    <t>08:55</t>
+  </si>
+  <si>
+    <t>09:24</t>
+  </si>
+  <si>
+    <t>08:23</t>
+  </si>
+  <si>
+    <t>08:13</t>
+  </si>
+  <si>
+    <t>09:13</t>
+  </si>
+  <si>
+    <t>09:07</t>
+  </si>
+  <si>
+    <t>09:12</t>
+  </si>
+  <si>
+    <t>08:18</t>
+  </si>
+  <si>
+    <t>08:25</t>
+  </si>
+  <si>
+    <t>08:12</t>
+  </si>
+  <si>
+    <t>08:19</t>
+  </si>
+  <si>
+    <t>09:55</t>
+  </si>
+  <si>
+    <t>09:02</t>
+  </si>
+  <si>
+    <t>08:57</t>
+  </si>
+  <si>
+    <t>09:54</t>
+  </si>
+  <si>
+    <t>09:04</t>
+  </si>
+  <si>
+    <t>09:35</t>
+  </si>
+  <si>
+    <t>08:10</t>
+  </si>
+  <si>
+    <t>08:15</t>
+  </si>
+  <si>
+    <t>08:03</t>
+  </si>
+  <si>
+    <t>08:51</t>
+  </si>
+  <si>
+    <t>09:18</t>
+  </si>
+  <si>
+    <t>08:17</t>
+  </si>
+  <si>
+    <t>09:16</t>
+  </si>
+  <si>
+    <t>08:07</t>
+  </si>
+  <si>
+    <t>08:08</t>
+  </si>
+  <si>
+    <t>08:35</t>
+  </si>
+  <si>
+    <t>08:31</t>
+  </si>
+  <si>
+    <t>09:30</t>
+  </si>
+  <si>
+    <t>08:21</t>
+  </si>
+  <si>
+    <t>09:11</t>
+  </si>
+  <si>
+    <t>08:28</t>
+  </si>
+  <si>
+    <t>09:37</t>
+  </si>
+  <si>
+    <t>08:27</t>
+  </si>
+  <si>
+    <t>08:43</t>
+  </si>
+  <si>
+    <t>08:34</t>
+  </si>
+  <si>
+    <t>08:11</t>
+  </si>
+  <si>
+    <t>08:20</t>
+  </si>
+  <si>
+    <t>08:09</t>
+  </si>
+  <si>
+    <t>08:56</t>
+  </si>
+  <si>
+    <t>08:14</t>
+  </si>
+  <si>
+    <t>08:01</t>
+  </si>
+  <si>
+    <t>09:28</t>
+  </si>
+  <si>
+    <t>09:27</t>
   </si>
   <si>
     <t>10/27(TUE), 10/28(WED)</t>
   </si>
   <si>
-    <t>10/6(TUE), 10/7(WED), 10/13(TUE), 10/14(WED), 10/20(TUE), 10/21(WED)</t>
-  </si>
-  <si>
-    <t>10/6(TUE), 10/7(WED), 10/13(TUE), 10/14(WED), 10/20(TUE), 10/21(WED), 10/27(TUE), 10/28(WED)</t>
-  </si>
-  <si>
-    <t>10/9(FRI), 10/15(THU), 10/16(FRI), 10/22(THU), 10/29(THU), 10/30(FRI)</t>
-  </si>
-  <si>
-    <t>10/8(THU), 10/23(FRI)</t>
-  </si>
-  <si>
-    <t>10/5(MON), 10/12(MON), 10/19(MON)</t>
+    <t>10/06(TUE), 10/07(WED), 10/13(TUE), 10/14(WED), 10/20(TUE), 10/21(WED)</t>
+  </si>
+  <si>
+    <t>10/06(TUE), 10/07(WED), 10/13(TUE), 10/14(WED), 10/20(TUE), 10/21(WED), 10/27(TUE), 10/28(WED)</t>
+  </si>
+  <si>
+    <t>10/09(FRI), 10/15(THU), 10/16(FRI), 10/22(THU), 10/29(THU), 10/30(FRI)</t>
+  </si>
+  <si>
+    <t>10/08(THU), 10/23(FRI)</t>
+  </si>
+  <si>
+    <t>10/05(MON), 10/12(MON), 10/19(MON)</t>
   </si>
   <si>
     <t>10/26(MON)</t>
   </si>
   <si>
-    <t>10/4(SUN), 10/5(MON), 10/11(SUN), 10/12(MON), 10/18(SUN), 10/19(MON), 10/25(SUN)</t>
-  </si>
-  <si>
-    <t>10/9(FRI), 10/16(FRI), 10/30(FRI)</t>
+    <t>10/04(SUN), 10/05(MON), 10/11(SUN), 10/12(MON), 10/18(SUN), 10/19(MON), 10/25(SUN)</t>
+  </si>
+  <si>
+    <t>10/09(FRI), 10/16(FRI), 10/30(FRI)</t>
   </si>
   <si>
     <t>10/23(FRI)</t>
@@ -1480,31 +1486,31 @@
     <t>10/14(WED)</t>
   </si>
   <si>
-    <t>10/6(TUE), 10/7(WED), 10/13(TUE), 10/20(TUE), 10/21(WED), 10/28(WED)</t>
-  </si>
-  <si>
-    <t>10/4(SUN), 10/8(THU), 10/10(SAT), 10/11(SUN), 10/15(THU), 10/17(SAT), 10/18(SUN), 10/22(THU), 10/25(SUN), 10/29(THU), 10/31(SAT)</t>
-  </si>
-  <si>
-    <t>10/9(FRI)</t>
+    <t>10/06(TUE), 10/07(WED), 10/13(TUE), 10/20(TUE), 10/21(WED), 10/28(WED)</t>
+  </si>
+  <si>
+    <t>10/04(SUN), 10/08(THU), 10/10(SAT), 10/11(SUN), 10/15(THU), 10/17(SAT), 10/18(SUN), 10/22(THU), 10/25(SUN), 10/29(THU), 10/31(SAT)</t>
+  </si>
+  <si>
+    <t>10/09(FRI)</t>
   </si>
   <si>
     <t>10/16(FRI), 10/23(FRI), 10/30(FRI)</t>
   </si>
   <si>
-    <t>10/6(TUE), 10/7(WED), 10/13(TUE), 10/14(WED), 10/20(TUE), 10/21(WED), 10/28(WED)</t>
-  </si>
-  <si>
-    <t>10/4(SUN), 10/11(SUN), 10/18(SUN), 10/25(SUN)</t>
-  </si>
-  <si>
-    <t>10/6(TUE)</t>
+    <t>10/06(TUE), 10/07(WED), 10/13(TUE), 10/14(WED), 10/20(TUE), 10/21(WED), 10/28(WED)</t>
+  </si>
+  <si>
+    <t>10/04(SUN), 10/11(SUN), 10/18(SUN), 10/25(SUN)</t>
+  </si>
+  <si>
+    <t>10/06(TUE)</t>
   </si>
   <si>
     <t>10/13(TUE), 10/20(TUE), 10/28(WED)</t>
   </si>
   <si>
-    <t>10/7(WED), 10/14(WED), 10/21(WED), 10/27(TUE)</t>
+    <t>10/07(WED), 10/14(WED), 10/21(WED), 10/27(TUE)</t>
   </si>
   <si>
     <t>10/15(THU)</t>
@@ -1513,13 +1519,13 @@
     <t>10/22(THU), 10/29(THU)</t>
   </si>
   <si>
-    <t>10/8(THU)</t>
-  </si>
-  <si>
-    <t>10/8(THU), 10/15(THU), 10/22(THU), 10/29(THU)</t>
-  </si>
-  <si>
-    <t>10/5(MON), 10/19(MON)</t>
+    <t>10/08(THU)</t>
+  </si>
+  <si>
+    <t>10/08(THU), 10/15(THU), 10/22(THU), 10/29(THU)</t>
+  </si>
+  <si>
+    <t>10/05(MON), 10/19(MON)</t>
   </si>
   <si>
     <t>10/17(SAT), 10/31(SAT)</t>
@@ -1531,7 +1537,7 @@
     <t>10/11(SUN)</t>
   </si>
   <si>
-    <t>10/4(SUN), 10/18(SUN)</t>
+    <t>10/04(SUN), 10/18(SUN)</t>
   </si>
   <si>
     <t>10/25(SUN)</t>
@@ -1549,22 +1555,22 @@
     <t>10/12(MON), 10/19(MON)</t>
   </si>
   <si>
-    <t>10/5(MON)</t>
-  </si>
-  <si>
-    <t>10/4(SUN), 10/18(SUN), 10/25(SUN)</t>
-  </si>
-  <si>
-    <t>10/4(SUN), 10/11(SUN), 10/13(TUE), 10/15(THU), 10/18(SUN), 10/20(TUE), 10/21(WED), 10/27(TUE), 10/29(THU)</t>
+    <t>10/05(MON)</t>
+  </si>
+  <si>
+    <t>10/04(SUN), 10/18(SUN), 10/25(SUN)</t>
+  </si>
+  <si>
+    <t>10/04(SUN), 10/11(SUN), 10/13(TUE), 10/15(THU), 10/18(SUN), 10/20(TUE), 10/21(WED), 10/27(TUE), 10/29(THU)</t>
   </si>
   <si>
     <t>10/28(WED)</t>
   </si>
   <si>
-    <t>10/6(TUE), 10/7(WED), 10/22(THU)</t>
-  </si>
-  <si>
-    <t>10/5(MON), 10/9(FRI), 10/12(MON), 10/15(THU), 10/16(FRI), 10/19(MON), 10/22(THU), 10/23(FRI), 10/29(THU), 10/30(FRI)</t>
+    <t>10/06(TUE), 10/07(WED), 10/22(THU)</t>
+  </si>
+  <si>
+    <t>10/05(MON), 10/09(FRI), 10/12(MON), 10/15(THU), 10/16(FRI), 10/19(MON), 10/22(THU), 10/23(FRI), 10/29(THU), 10/30(FRI)</t>
   </si>
   <si>
     <t>10/12(MON)</t>
@@ -1579,13 +1585,13 @@
     <t>10/10(SAT), 10/24(SAT)</t>
   </si>
   <si>
-    <t>10/4(SUN), 10/6(TUE), 10/7(WED), 10/13(TUE), 10/14(WED), 10/18(SUN), 10/20(TUE), 10/21(WED), 10/27(TUE), 10/28(WED)</t>
+    <t>10/04(SUN), 10/06(TUE), 10/07(WED), 10/13(TUE), 10/14(WED), 10/18(SUN), 10/20(TUE), 10/21(WED), 10/27(TUE), 10/28(WED)</t>
   </si>
   <si>
     <t>10/15(THU), 10/22(THU), 10/29(THU)</t>
   </si>
   <si>
-    <t>10/7(WED), 10/13(TUE), 10/14(WED), 10/20(TUE)</t>
+    <t>10/07(WED), 10/13(TUE), 10/14(WED), 10/20(TUE)</t>
   </si>
   <si>
     <t>10/21(WED)</t>
@@ -1600,16 +1606,16 @@
     <t>10/15(THU), 10/22(THU)</t>
   </si>
   <si>
-    <t>10/6(TUE), 10/7(WED), 10/21(WED)</t>
+    <t>10/06(TUE), 10/07(WED), 10/21(WED)</t>
   </si>
   <si>
     <t>10/13(TUE), 10/14(WED), 10/20(TUE)</t>
   </si>
   <si>
-    <t>10/4(SUN), 10/11(SUN), 10/18(SUN)</t>
-  </si>
-  <si>
-    <t>10/6(TUE), 10/7(WED), 10/13(TUE), 10/14(WED), 10/20(TUE), 10/21(WED), 10/27(TUE)</t>
+    <t>10/04(SUN), 10/11(SUN), 10/18(SUN)</t>
+  </si>
+  <si>
+    <t>10/06(TUE), 10/07(WED), 10/13(TUE), 10/14(WED), 10/20(TUE), 10/21(WED), 10/27(TUE)</t>
   </si>
   <si>
     <t>10/23(FRI), 10/30(FRI)</t>
@@ -1618,7 +1624,7 @@
     <t>10/16(FRI)</t>
   </si>
   <si>
-    <t>10/9(FRI), 10/23(FRI), 10/30(FRI)</t>
+    <t>10/09(FRI), 10/23(FRI), 10/30(FRI)</t>
   </si>
   <si>
     <t>10/19(MON)</t>
@@ -1633,28 +1639,28 @@
     <t>10/14(WED), 10/20(TUE)</t>
   </si>
   <si>
-    <t>10/6(TUE), 10/7(WED), 10/21(WED), 10/27(TUE)</t>
-  </si>
-  <si>
-    <t>10/6(TUE), 10/7(WED), 10/14(WED), 10/21(WED)</t>
+    <t>10/06(TUE), 10/07(WED), 10/21(WED), 10/27(TUE)</t>
+  </si>
+  <si>
+    <t>10/06(TUE), 10/07(WED), 10/14(WED), 10/21(WED)</t>
   </si>
   <si>
     <t>10/20(TUE), 10/27(TUE), 10/28(WED)</t>
   </si>
   <si>
-    <t>10/4(SUN), 10/18(SUN), 10/23(FRI)</t>
-  </si>
-  <si>
-    <t>10/7(WED), 10/21(WED), 10/27(TUE)</t>
-  </si>
-  <si>
-    <t>10/7(WED), 10/21(WED)</t>
-  </si>
-  <si>
-    <t>10/5(MON), 10/28(WED)</t>
-  </si>
-  <si>
-    <t>10/6(TUE), 10/15(THU), 10/21(WED), 10/22(THU)</t>
+    <t>10/04(SUN), 10/18(SUN), 10/23(FRI)</t>
+  </si>
+  <si>
+    <t>10/07(WED), 10/21(WED), 10/27(TUE)</t>
+  </si>
+  <si>
+    <t>10/07(WED), 10/21(WED)</t>
+  </si>
+  <si>
+    <t>10/05(MON), 10/28(WED)</t>
+  </si>
+  <si>
+    <t>10/06(TUE), 10/15(THU), 10/21(WED), 10/22(THU)</t>
   </si>
   <si>
     <t>10/20(TUE)</t>
@@ -1663,10 +1669,10 @@
     <t>10/13(TUE), 10/14(WED)</t>
   </si>
   <si>
-    <t>10/6(TUE), 10/28(WED)</t>
-  </si>
-  <si>
-    <t>10/6(TUE), 10/7(WED), 10/13(TUE), 10/15(THU), 10/19(MON), 10/20(TUE)</t>
+    <t>10/06(TUE), 10/28(WED)</t>
+  </si>
+  <si>
+    <t>10/06(TUE), 10/07(WED), 10/13(TUE), 10/15(THU), 10/19(MON), 10/20(TUE)</t>
   </si>
   <si>
     <t>10/14(WED), 10/15(THU), 10/16(FRI)</t>
@@ -1675,7 +1681,10 @@
     <t>10/21(WED), 10/22(THU), 10/29(THU), 10/30(FRI)</t>
   </si>
   <si>
-    <t>10/5(MON), 10/6(TUE), 10/7(WED), 10/8(THU), 10/9(FRI), 10/12(MON), 10/13(TUE), 10/14(WED), 10/15(THU), 10/16(FRI), 10/17(SAT), 10/19(MON), 10/20(TUE), 10/21(WED), 10/22(THU), 10/23(FRI), 10/26(MON), 10/27(TUE), 10/28(WED), 10/29(THU), 10/30(FRI)</t>
+    <t>10/05(MON), 10/06(TUE), 10/07(WED), 10/08(THU), 10/09(FRI), 10/12(MON), 10/13(TUE), 10/14(WED), 10/15(THU), 10/16(FRI), 10/17(SAT), 10/19(MON), 10/20(TUE), 10/21(WED), 10/22(THU), 10/23(FRI), 10/26(MON), 10/27(TUE), 10/28(WED), 10/29(THU), 10/30(FRI)</t>
+  </si>
+  <si>
+    <t>10/05(MON), 10/06(TUE), 10/07(WED), 10/08(THU), 10/09(FRI)</t>
   </si>
   <si>
     <t>10/16(FRI), 10/19(MON), 10/23(FRI), 10/27(TUE)</t>
@@ -1684,10 +1693,10 @@
     <t>10/13(TUE), 10/15(THU)</t>
   </si>
   <si>
-    <t>10/4(SUN), 10/5(MON), 10/6(TUE), 10/7(WED), 10/8(THU), 10/9(FRI), 10/10(SAT), 10/11(SUN), 10/12(MON), 10/13(TUE), 10/14(WED), 10/15(THU), 10/16(FRI), 10/17(SAT), 10/18(SUN), 10/19(MON), 10/20(TUE), 10/21(WED), 10/22(THU), 10/23(FRI), 10/24(SAT), 10/25(SUN), 10/26(MON), 10/27(TUE), 10/28(WED), 10/29(THU), 10/30(FRI), 10/31(SAT)</t>
-  </si>
-  <si>
-    <t>10/7(WED), 10/9(FRI)</t>
+    <t>10/04(SUN), 10/05(MON), 10/06(TUE), 10/07(WED), 10/08(THU), 10/09(FRI), 10/10(SAT), 10/11(SUN), 10/12(MON), 10/13(TUE), 10/14(WED), 10/15(THU), 10/16(FRI), 10/17(SAT), 10/18(SUN), 10/19(MON), 10/20(TUE), 10/21(WED), 10/22(THU), 10/23(FRI), 10/24(SAT), 10/25(SUN), 10/26(MON), 10/27(TUE), 10/28(WED), 10/29(THU), 10/30(FRI), 10/31(SAT)</t>
+  </si>
+  <si>
+    <t>10/07(WED), 10/09(FRI)</t>
   </si>
 </sst>
 </file>
@@ -2045,7 +2054,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E314"/>
+  <dimension ref="A1:E315"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -2070,16 +2079,16 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="D2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E2" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -2087,16 +2096,16 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C3" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D3" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="E3" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -2104,16 +2113,16 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D4" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E4" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -2121,16 +2130,16 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C5" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="D5" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="E5" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -2138,16 +2147,16 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C6" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D6" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="E6" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -2155,16 +2164,16 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C7" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="D7" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="E7" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -2172,16 +2181,16 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C8" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="D8" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="E8" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -2189,16 +2198,16 @@
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C9" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="D9" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E9" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -2206,16 +2215,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C10" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="D10" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="E10" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -2223,16 +2232,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C11" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="D11" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="E11" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -2240,16 +2249,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C12" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D12" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E12" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -2257,16 +2266,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C13" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D13" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E13" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -2274,16 +2283,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C14" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="D14" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E14" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -2291,16 +2300,16 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C15" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="D15" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="E15" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -2308,16 +2317,16 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C16" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="D16" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E16" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -2325,16 +2334,16 @@
         <v>13</v>
       </c>
       <c r="B17" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C17" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="D17" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="E17" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -2342,16 +2351,16 @@
         <v>13</v>
       </c>
       <c r="B18" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C18" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="D18" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E18" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -2359,16 +2368,16 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C19" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D19" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="E19" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -2376,16 +2385,16 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C20" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D20" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E20" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -2393,16 +2402,16 @@
         <v>15</v>
       </c>
       <c r="B21" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C21" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D21" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E21" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -2410,16 +2419,16 @@
         <v>15</v>
       </c>
       <c r="B22" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C22" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="D22" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E22" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -2427,16 +2436,16 @@
         <v>16</v>
       </c>
       <c r="B23" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C23" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D23" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="E23" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -2444,16 +2453,16 @@
         <v>16</v>
       </c>
       <c r="B24" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C24" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D24" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="E24" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2461,16 +2470,16 @@
         <v>17</v>
       </c>
       <c r="B25" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C25" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D25" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="E25" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2478,16 +2487,16 @@
         <v>17</v>
       </c>
       <c r="B26" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C26" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D26" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="E26" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2495,16 +2504,16 @@
         <v>18</v>
       </c>
       <c r="B27" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C27" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D27" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="E27" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2512,16 +2521,16 @@
         <v>19</v>
       </c>
       <c r="B28" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C28" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D28" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E28" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2529,16 +2538,16 @@
         <v>20</v>
       </c>
       <c r="B29" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C29" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="D29" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="E29" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2546,16 +2555,16 @@
         <v>20</v>
       </c>
       <c r="B30" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C30" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D30" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="E30" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2563,16 +2572,16 @@
         <v>21</v>
       </c>
       <c r="B31" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C31" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D31" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E31" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2580,16 +2589,16 @@
         <v>21</v>
       </c>
       <c r="B32" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C32" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D32" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E32" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2597,16 +2606,16 @@
         <v>21</v>
       </c>
       <c r="B33" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C33" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="D33" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E33" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2614,16 +2623,16 @@
         <v>22</v>
       </c>
       <c r="B34" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C34" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D34" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E34" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2631,16 +2640,16 @@
         <v>22</v>
       </c>
       <c r="B35" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C35" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="D35" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="E35" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2648,16 +2657,16 @@
         <v>22</v>
       </c>
       <c r="B36" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C36" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="D36" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="E36" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2665,16 +2674,16 @@
         <v>23</v>
       </c>
       <c r="B37" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C37" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="D37" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E37" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2682,16 +2691,16 @@
         <v>24</v>
       </c>
       <c r="B38" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C38" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="D38" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="E38" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2699,16 +2708,16 @@
         <v>24</v>
       </c>
       <c r="B39" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C39" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D39" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="E39" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2716,16 +2725,16 @@
         <v>25</v>
       </c>
       <c r="B40" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C40" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="D40" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="E40" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2733,16 +2742,16 @@
         <v>25</v>
       </c>
       <c r="B41" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C41" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="D41" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E41" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2750,16 +2759,16 @@
         <v>26</v>
       </c>
       <c r="B42" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C42" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D42" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E42" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2767,16 +2776,16 @@
         <v>26</v>
       </c>
       <c r="B43" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C43" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="D43" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E43" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2784,16 +2793,16 @@
         <v>27</v>
       </c>
       <c r="B44" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C44" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="D44" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="E44" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2801,16 +2810,16 @@
         <v>27</v>
       </c>
       <c r="B45" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C45" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D45" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="E45" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2818,16 +2827,16 @@
         <v>28</v>
       </c>
       <c r="B46" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C46" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D46" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="E46" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -2835,16 +2844,16 @@
         <v>28</v>
       </c>
       <c r="B47" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C47" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="D47" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E47" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -2852,16 +2861,16 @@
         <v>28</v>
       </c>
       <c r="B48" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C48" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D48" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="E48" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -2869,16 +2878,16 @@
         <v>29</v>
       </c>
       <c r="B49" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C49" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D49" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E49" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -2886,16 +2895,16 @@
         <v>30</v>
       </c>
       <c r="B50" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C50" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="D50" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="E50" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -2903,16 +2912,16 @@
         <v>30</v>
       </c>
       <c r="B51" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C51" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="D51" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E51" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -2920,16 +2929,16 @@
         <v>30</v>
       </c>
       <c r="B52" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C52" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D52" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="E52" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -2937,16 +2946,16 @@
         <v>31</v>
       </c>
       <c r="B53" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C53" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D53" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="E53" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -2954,16 +2963,16 @@
         <v>31</v>
       </c>
       <c r="B54" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C54" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D54" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E54" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -2971,16 +2980,16 @@
         <v>31</v>
       </c>
       <c r="B55" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C55" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D55" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="E55" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -2988,16 +2997,16 @@
         <v>32</v>
       </c>
       <c r="B56" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C56" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D56" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E56" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -3005,16 +3014,16 @@
         <v>33</v>
       </c>
       <c r="B57" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C57" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D57" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="E57" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -3022,16 +3031,16 @@
         <v>33</v>
       </c>
       <c r="B58" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C58" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D58" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="E58" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -3039,16 +3048,16 @@
         <v>34</v>
       </c>
       <c r="B59" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C59" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D59" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="E59" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -3056,16 +3065,16 @@
         <v>34</v>
       </c>
       <c r="B60" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C60" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="D60" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="E60" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -3073,16 +3082,16 @@
         <v>34</v>
       </c>
       <c r="B61" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C61" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D61" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E61" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -3090,16 +3099,16 @@
         <v>34</v>
       </c>
       <c r="B62" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C62" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D62" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="E62" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -3107,16 +3116,16 @@
         <v>35</v>
       </c>
       <c r="B63" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C63" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D63" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E63" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -3124,16 +3133,16 @@
         <v>35</v>
       </c>
       <c r="B64" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C64" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D64" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="E64" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -3141,16 +3150,16 @@
         <v>35</v>
       </c>
       <c r="B65" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C65" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D65" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="E65" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -3158,16 +3167,16 @@
         <v>36</v>
       </c>
       <c r="B66" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C66" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="D66" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="E66" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -3175,16 +3184,16 @@
         <v>36</v>
       </c>
       <c r="B67" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C67" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="D67" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="E67" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -3192,16 +3201,16 @@
         <v>37</v>
       </c>
       <c r="B68" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C68" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D68" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="E68" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -3209,16 +3218,16 @@
         <v>37</v>
       </c>
       <c r="B69" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C69" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="D69" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="E69" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -3226,16 +3235,16 @@
         <v>37</v>
       </c>
       <c r="B70" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C70" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="D70" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="E70" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -3243,16 +3252,16 @@
         <v>37</v>
       </c>
       <c r="B71" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C71" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D71" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="E71" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -3260,16 +3269,16 @@
         <v>37</v>
       </c>
       <c r="B72" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C72" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D72" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="E72" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -3277,16 +3286,16 @@
         <v>37</v>
       </c>
       <c r="B73" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C73" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D73" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E73" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -3294,16 +3303,16 @@
         <v>38</v>
       </c>
       <c r="B74" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C74" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="D74" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E74" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -3311,16 +3320,16 @@
         <v>38</v>
       </c>
       <c r="B75" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C75" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D75" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="E75" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -3328,16 +3337,16 @@
         <v>38</v>
       </c>
       <c r="B76" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C76" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D76" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E76" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -3345,16 +3354,16 @@
         <v>39</v>
       </c>
       <c r="B77" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C77" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D77" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E77" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -3362,16 +3371,16 @@
         <v>40</v>
       </c>
       <c r="B78" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C78" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="D78" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E78" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="79" spans="1:5">
@@ -3379,16 +3388,16 @@
         <v>40</v>
       </c>
       <c r="B79" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C79" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D79" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="E79" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="80" spans="1:5">
@@ -3396,16 +3405,16 @@
         <v>40</v>
       </c>
       <c r="B80" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C80" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D80" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E80" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="81" spans="1:5">
@@ -3413,16 +3422,16 @@
         <v>41</v>
       </c>
       <c r="B81" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C81" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="D81" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E81" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -3430,16 +3439,16 @@
         <v>42</v>
       </c>
       <c r="B82" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C82" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="D82" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E82" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -3447,16 +3456,16 @@
         <v>42</v>
       </c>
       <c r="B83" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C83" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="D83" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E83" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="84" spans="1:5">
@@ -3464,16 +3473,16 @@
         <v>43</v>
       </c>
       <c r="B84" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C84" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D84" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="E84" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="85" spans="1:5">
@@ -3481,16 +3490,16 @@
         <v>43</v>
       </c>
       <c r="B85" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C85" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="D85" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="E85" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="86" spans="1:5">
@@ -3498,16 +3507,16 @@
         <v>43</v>
       </c>
       <c r="B86" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C86" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="D86" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E86" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -3515,16 +3524,16 @@
         <v>44</v>
       </c>
       <c r="B87" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C87" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="D87" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E87" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -3532,16 +3541,16 @@
         <v>44</v>
       </c>
       <c r="B88" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C88" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="D88" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E88" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="89" spans="1:5">
@@ -3549,16 +3558,16 @@
         <v>44</v>
       </c>
       <c r="B89" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C89" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="D89" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="E89" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="90" spans="1:5">
@@ -3566,16 +3575,16 @@
         <v>45</v>
       </c>
       <c r="B90" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C90" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D90" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="E90" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="91" spans="1:5">
@@ -3583,16 +3592,16 @@
         <v>45</v>
       </c>
       <c r="B91" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C91" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D91" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="E91" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -3600,16 +3609,16 @@
         <v>46</v>
       </c>
       <c r="B92" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C92" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="D92" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="E92" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="93" spans="1:5">
@@ -3617,16 +3626,16 @@
         <v>46</v>
       </c>
       <c r="B93" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C93" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="D93" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="E93" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="94" spans="1:5">
@@ -3634,16 +3643,16 @@
         <v>46</v>
       </c>
       <c r="B94" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C94" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="D94" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="E94" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="95" spans="1:5">
@@ -3651,16 +3660,16 @@
         <v>47</v>
       </c>
       <c r="B95" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C95" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="D95" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E95" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="96" spans="1:5">
@@ -3668,16 +3677,16 @@
         <v>47</v>
       </c>
       <c r="B96" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C96" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="D96" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="E96" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="97" spans="1:5">
@@ -3685,16 +3694,16 @@
         <v>48</v>
       </c>
       <c r="B97" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C97" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="D97" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E97" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="98" spans="1:5">
@@ -3702,16 +3711,16 @@
         <v>48</v>
       </c>
       <c r="B98" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C98" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="D98" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="E98" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="99" spans="1:5">
@@ -3719,16 +3728,16 @@
         <v>49</v>
       </c>
       <c r="B99" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C99" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="D99" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E99" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="100" spans="1:5">
@@ -3736,16 +3745,16 @@
         <v>49</v>
       </c>
       <c r="B100" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C100" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="D100" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="E100" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="101" spans="1:5">
@@ -3753,16 +3762,16 @@
         <v>49</v>
       </c>
       <c r="B101" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C101" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="D101" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="E101" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="102" spans="1:5">
@@ -3770,16 +3779,16 @@
         <v>50</v>
       </c>
       <c r="B102" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C102" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="D102" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E102" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="103" spans="1:5">
@@ -3787,16 +3796,16 @@
         <v>50</v>
       </c>
       <c r="B103" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C103" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="D103" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="E103" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="104" spans="1:5">
@@ -3804,16 +3813,16 @@
         <v>50</v>
       </c>
       <c r="B104" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C104" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D104" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="E104" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="105" spans="1:5">
@@ -3821,16 +3830,16 @@
         <v>51</v>
       </c>
       <c r="B105" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C105" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="D105" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="E105" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="106" spans="1:5">
@@ -3838,16 +3847,16 @@
         <v>51</v>
       </c>
       <c r="B106" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C106" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="D106" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E106" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="107" spans="1:5">
@@ -3855,16 +3864,16 @@
         <v>52</v>
       </c>
       <c r="B107" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C107" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="D107" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E107" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="108" spans="1:5">
@@ -3872,16 +3881,16 @@
         <v>53</v>
       </c>
       <c r="B108" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C108" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="D108" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E108" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="109" spans="1:5">
@@ -3889,16 +3898,16 @@
         <v>53</v>
       </c>
       <c r="B109" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C109" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="D109" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="E109" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="110" spans="1:5">
@@ -3906,16 +3915,16 @@
         <v>54</v>
       </c>
       <c r="B110" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C110" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="D110" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E110" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="111" spans="1:5">
@@ -3923,16 +3932,16 @@
         <v>54</v>
       </c>
       <c r="B111" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C111" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="D111" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E111" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="112" spans="1:5">
@@ -3940,16 +3949,16 @@
         <v>55</v>
       </c>
       <c r="B112" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C112" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="D112" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="E112" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="113" spans="1:5">
@@ -3957,16 +3966,16 @@
         <v>55</v>
       </c>
       <c r="B113" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C113" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D113" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="E113" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="114" spans="1:5">
@@ -3974,16 +3983,16 @@
         <v>55</v>
       </c>
       <c r="B114" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C114" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="D114" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E114" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="115" spans="1:5">
@@ -3991,16 +4000,16 @@
         <v>56</v>
       </c>
       <c r="B115" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C115" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D115" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="E115" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="116" spans="1:5">
@@ -4008,16 +4017,16 @@
         <v>56</v>
       </c>
       <c r="B116" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C116" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D116" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="E116" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="117" spans="1:5">
@@ -4025,16 +4034,16 @@
         <v>57</v>
       </c>
       <c r="B117" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C117" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="D117" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="E117" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="118" spans="1:5">
@@ -4042,16 +4051,16 @@
         <v>57</v>
       </c>
       <c r="B118" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C118" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D118" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E118" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="119" spans="1:5">
@@ -4059,16 +4068,16 @@
         <v>57</v>
       </c>
       <c r="B119" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C119" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D119" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="E119" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="120" spans="1:5">
@@ -4076,16 +4085,16 @@
         <v>57</v>
       </c>
       <c r="B120" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C120" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="D120" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E120" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="121" spans="1:5">
@@ -4093,16 +4102,16 @@
         <v>58</v>
       </c>
       <c r="B121" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C121" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D121" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E121" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="122" spans="1:5">
@@ -4110,16 +4119,16 @@
         <v>58</v>
       </c>
       <c r="B122" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C122" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D122" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="E122" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="123" spans="1:5">
@@ -4127,16 +4136,16 @@
         <v>59</v>
       </c>
       <c r="B123" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C123" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D123" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="E123" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="124" spans="1:5">
@@ -4144,16 +4153,16 @@
         <v>59</v>
       </c>
       <c r="B124" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C124" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="D124" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="E124" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
     </row>
     <row r="125" spans="1:5">
@@ -4161,16 +4170,16 @@
         <v>59</v>
       </c>
       <c r="B125" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C125" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D125" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E125" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="126" spans="1:5">
@@ -4178,16 +4187,16 @@
         <v>60</v>
       </c>
       <c r="B126" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C126" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="D126" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E126" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="127" spans="1:5">
@@ -4195,16 +4204,16 @@
         <v>60</v>
       </c>
       <c r="B127" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C127" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="D127" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="E127" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="128" spans="1:5">
@@ -4212,16 +4221,16 @@
         <v>61</v>
       </c>
       <c r="B128" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C128" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="D128" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="E128" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="129" spans="1:5">
@@ -4229,16 +4238,16 @@
         <v>61</v>
       </c>
       <c r="B129" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C129" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="D129" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E129" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="130" spans="1:5">
@@ -4246,16 +4255,16 @@
         <v>61</v>
       </c>
       <c r="B130" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C130" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D130" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E130" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="131" spans="1:5">
@@ -4263,16 +4272,16 @@
         <v>62</v>
       </c>
       <c r="B131" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C131" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="D131" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E131" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="132" spans="1:5">
@@ -4280,16 +4289,16 @@
         <v>62</v>
       </c>
       <c r="B132" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C132" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="D132" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="E132" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="133" spans="1:5">
@@ -4297,16 +4306,16 @@
         <v>62</v>
       </c>
       <c r="B133" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C133" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="D133" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="E133" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="134" spans="1:5">
@@ -4314,16 +4323,16 @@
         <v>63</v>
       </c>
       <c r="B134" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C134" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="D134" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="E134" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="135" spans="1:5">
@@ -4331,16 +4340,16 @@
         <v>63</v>
       </c>
       <c r="B135" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C135" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D135" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="E135" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="136" spans="1:5">
@@ -4348,16 +4357,16 @@
         <v>63</v>
       </c>
       <c r="B136" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C136" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="D136" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E136" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="137" spans="1:5">
@@ -4365,16 +4374,16 @@
         <v>64</v>
       </c>
       <c r="B137" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C137" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D137" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E137" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="138" spans="1:5">
@@ -4382,16 +4391,16 @@
         <v>64</v>
       </c>
       <c r="B138" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C138" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D138" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E138" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="139" spans="1:5">
@@ -4399,16 +4408,16 @@
         <v>64</v>
       </c>
       <c r="B139" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C139" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="D139" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="E139" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="140" spans="1:5">
@@ -4416,16 +4425,16 @@
         <v>65</v>
       </c>
       <c r="B140" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C140" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D140" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E140" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="141" spans="1:5">
@@ -4433,16 +4442,16 @@
         <v>65</v>
       </c>
       <c r="B141" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C141" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D141" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E141" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="142" spans="1:5">
@@ -4450,16 +4459,16 @@
         <v>65</v>
       </c>
       <c r="B142" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C142" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="D142" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="E142" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="143" spans="1:5">
@@ -4467,16 +4476,16 @@
         <v>66</v>
       </c>
       <c r="B143" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C143" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="D143" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E143" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="144" spans="1:5">
@@ -4484,16 +4493,16 @@
         <v>66</v>
       </c>
       <c r="B144" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C144" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="D144" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E144" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="145" spans="1:5">
@@ -4501,16 +4510,16 @@
         <v>66</v>
       </c>
       <c r="B145" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C145" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D145" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="E145" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="146" spans="1:5">
@@ -4518,16 +4527,16 @@
         <v>67</v>
       </c>
       <c r="B146" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C146" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D146" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E146" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="147" spans="1:5">
@@ -4535,16 +4544,16 @@
         <v>67</v>
       </c>
       <c r="B147" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C147" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="D147" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="E147" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="148" spans="1:5">
@@ -4552,16 +4561,16 @@
         <v>67</v>
       </c>
       <c r="B148" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C148" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D148" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="E148" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="149" spans="1:5">
@@ -4569,16 +4578,16 @@
         <v>68</v>
       </c>
       <c r="B149" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C149" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="D149" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E149" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="150" spans="1:5">
@@ -4586,16 +4595,16 @@
         <v>68</v>
       </c>
       <c r="B150" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C150" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="D150" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="E150" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="151" spans="1:5">
@@ -4603,16 +4612,16 @@
         <v>68</v>
       </c>
       <c r="B151" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C151" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="D151" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E151" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="152" spans="1:5">
@@ -4620,16 +4629,16 @@
         <v>69</v>
       </c>
       <c r="B152" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C152" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="D152" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E152" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="153" spans="1:5">
@@ -4637,16 +4646,16 @@
         <v>69</v>
       </c>
       <c r="B153" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C153" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="D153" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="E153" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="154" spans="1:5">
@@ -4654,16 +4663,16 @@
         <v>69</v>
       </c>
       <c r="B154" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C154" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="D154" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E154" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="155" spans="1:5">
@@ -4671,16 +4680,16 @@
         <v>70</v>
       </c>
       <c r="B155" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C155" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D155" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="E155" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="156" spans="1:5">
@@ -4688,16 +4697,16 @@
         <v>70</v>
       </c>
       <c r="B156" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C156" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D156" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E156" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="157" spans="1:5">
@@ -4705,16 +4714,16 @@
         <v>70</v>
       </c>
       <c r="B157" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C157" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D157" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E157" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="158" spans="1:5">
@@ -4722,16 +4731,16 @@
         <v>71</v>
       </c>
       <c r="B158" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C158" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D158" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E158" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="159" spans="1:5">
@@ -4739,16 +4748,16 @@
         <v>71</v>
       </c>
       <c r="B159" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C159" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="D159" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="E159" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="160" spans="1:5">
@@ -4756,16 +4765,16 @@
         <v>72</v>
       </c>
       <c r="B160" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C160" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="D160" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="E160" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="161" spans="1:5">
@@ -4773,16 +4782,16 @@
         <v>72</v>
       </c>
       <c r="B161" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C161" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="D161" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="E161" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="162" spans="1:5">
@@ -4790,16 +4799,16 @@
         <v>73</v>
       </c>
       <c r="B162" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C162" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="D162" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="E162" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="163" spans="1:5">
@@ -4807,16 +4816,16 @@
         <v>73</v>
       </c>
       <c r="B163" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C163" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="D163" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="E163" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="164" spans="1:5">
@@ -4824,16 +4833,16 @@
         <v>73</v>
       </c>
       <c r="B164" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C164" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="D164" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E164" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="165" spans="1:5">
@@ -4841,16 +4850,16 @@
         <v>74</v>
       </c>
       <c r="B165" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C165" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="D165" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E165" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="166" spans="1:5">
@@ -4858,16 +4867,16 @@
         <v>74</v>
       </c>
       <c r="B166" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C166" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="D166" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="E166" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
     </row>
     <row r="167" spans="1:5">
@@ -4875,16 +4884,16 @@
         <v>75</v>
       </c>
       <c r="B167" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C167" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D167" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E167" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="168" spans="1:5">
@@ -4892,16 +4901,16 @@
         <v>75</v>
       </c>
       <c r="B168" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C168" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="D168" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="E168" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="169" spans="1:5">
@@ -4909,16 +4918,16 @@
         <v>76</v>
       </c>
       <c r="B169" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C169" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="D169" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E169" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="170" spans="1:5">
@@ -4926,16 +4935,16 @@
         <v>76</v>
       </c>
       <c r="B170" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C170" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="D170" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="E170" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="171" spans="1:5">
@@ -4943,16 +4952,16 @@
         <v>76</v>
       </c>
       <c r="B171" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C171" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="D171" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E171" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="172" spans="1:5">
@@ -4960,16 +4969,16 @@
         <v>77</v>
       </c>
       <c r="B172" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C172" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="D172" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E172" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="173" spans="1:5">
@@ -4977,16 +4986,16 @@
         <v>77</v>
       </c>
       <c r="B173" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C173" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D173" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="E173" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="174" spans="1:5">
@@ -4994,16 +5003,16 @@
         <v>77</v>
       </c>
       <c r="B174" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C174" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="D174" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="E174" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="175" spans="1:5">
@@ -5011,16 +5020,16 @@
         <v>78</v>
       </c>
       <c r="B175" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C175" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="D175" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="E175" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="176" spans="1:5">
@@ -5028,16 +5037,16 @@
         <v>78</v>
       </c>
       <c r="B176" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C176" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="D176" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E176" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="177" spans="1:5">
@@ -5045,16 +5054,16 @@
         <v>79</v>
       </c>
       <c r="B177" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C177" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D177" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="E177" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="178" spans="1:5">
@@ -5062,16 +5071,16 @@
         <v>79</v>
       </c>
       <c r="B178" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C178" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="D178" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="E178" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="179" spans="1:5">
@@ -5079,16 +5088,16 @@
         <v>80</v>
       </c>
       <c r="B179" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C179" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="D179" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E179" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="180" spans="1:5">
@@ -5096,16 +5105,16 @@
         <v>80</v>
       </c>
       <c r="B180" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C180" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D180" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="E180" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="181" spans="1:5">
@@ -5113,16 +5122,16 @@
         <v>80</v>
       </c>
       <c r="B181" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C181" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D181" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E181" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="182" spans="1:5">
@@ -5130,16 +5139,16 @@
         <v>81</v>
       </c>
       <c r="B182" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C182" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="D182" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="E182" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="183" spans="1:5">
@@ -5147,16 +5156,16 @@
         <v>81</v>
       </c>
       <c r="B183" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C183" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D183" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E183" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="184" spans="1:5">
@@ -5164,16 +5173,16 @@
         <v>81</v>
       </c>
       <c r="B184" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C184" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="D184" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="E184" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="185" spans="1:5">
@@ -5181,16 +5190,16 @@
         <v>81</v>
       </c>
       <c r="B185" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C185" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="D185" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E185" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="186" spans="1:5">
@@ -5198,16 +5207,16 @@
         <v>82</v>
       </c>
       <c r="B186" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C186" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="D186" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="E186" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="187" spans="1:5">
@@ -5215,16 +5224,16 @@
         <v>82</v>
       </c>
       <c r="B187" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C187" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="D187" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E187" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="188" spans="1:5">
@@ -5232,16 +5241,16 @@
         <v>83</v>
       </c>
       <c r="B188" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C188" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="D188" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E188" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="189" spans="1:5">
@@ -5249,16 +5258,16 @@
         <v>84</v>
       </c>
       <c r="B189" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C189" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D189" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="E189" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="190" spans="1:5">
@@ -5266,16 +5275,16 @@
         <v>84</v>
       </c>
       <c r="B190" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C190" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="D190" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="E190" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="191" spans="1:5">
@@ -5283,16 +5292,16 @@
         <v>85</v>
       </c>
       <c r="B191" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C191" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="D191" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E191" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="192" spans="1:5">
@@ -5300,16 +5309,16 @@
         <v>85</v>
       </c>
       <c r="B192" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C192" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="D192" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E192" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="193" spans="1:5">
@@ -5317,16 +5326,16 @@
         <v>85</v>
       </c>
       <c r="B193" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C193" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="D193" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E193" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="194" spans="1:5">
@@ -5334,16 +5343,16 @@
         <v>86</v>
       </c>
       <c r="B194" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C194" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D194" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E194" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="195" spans="1:5">
@@ -5351,16 +5360,16 @@
         <v>86</v>
       </c>
       <c r="B195" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C195" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="D195" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E195" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="196" spans="1:5">
@@ -5368,16 +5377,16 @@
         <v>86</v>
       </c>
       <c r="B196" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C196" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="D196" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E196" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="197" spans="1:5">
@@ -5385,16 +5394,16 @@
         <v>87</v>
       </c>
       <c r="B197" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C197" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="D197" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E197" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="198" spans="1:5">
@@ -5402,16 +5411,16 @@
         <v>88</v>
       </c>
       <c r="B198" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C198" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D198" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="E198" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="199" spans="1:5">
@@ -5419,16 +5428,16 @@
         <v>88</v>
       </c>
       <c r="B199" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C199" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="D199" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E199" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="200" spans="1:5">
@@ -5436,16 +5445,16 @@
         <v>88</v>
       </c>
       <c r="B200" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C200" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="D200" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="E200" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="201" spans="1:5">
@@ -5453,16 +5462,16 @@
         <v>89</v>
       </c>
       <c r="B201" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C201" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D201" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E201" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="202" spans="1:5">
@@ -5470,16 +5479,16 @@
         <v>89</v>
       </c>
       <c r="B202" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C202" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D202" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="E202" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="203" spans="1:5">
@@ -5487,16 +5496,16 @@
         <v>89</v>
       </c>
       <c r="B203" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C203" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="D203" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="E203" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="204" spans="1:5">
@@ -5504,16 +5513,16 @@
         <v>89</v>
       </c>
       <c r="B204" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C204" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D204" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E204" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="205" spans="1:5">
@@ -5521,16 +5530,16 @@
         <v>89</v>
       </c>
       <c r="B205" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C205" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="D205" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="E205" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="206" spans="1:5">
@@ -5538,16 +5547,16 @@
         <v>90</v>
       </c>
       <c r="B206" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C206" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D206" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E206" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="207" spans="1:5">
@@ -5555,16 +5564,16 @@
         <v>90</v>
       </c>
       <c r="B207" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C207" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="D207" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="E207" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="208" spans="1:5">
@@ -5572,16 +5581,16 @@
         <v>91</v>
       </c>
       <c r="B208" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C208" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="D208" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E208" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="209" spans="1:5">
@@ -5589,16 +5598,16 @@
         <v>91</v>
       </c>
       <c r="B209" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C209" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="D209" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="E209" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="210" spans="1:5">
@@ -5606,16 +5615,16 @@
         <v>92</v>
       </c>
       <c r="B210" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C210" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="D210" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E210" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="211" spans="1:5">
@@ -5623,16 +5632,16 @@
         <v>92</v>
       </c>
       <c r="B211" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C211" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="D211" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="E211" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="212" spans="1:5">
@@ -5640,16 +5649,16 @@
         <v>92</v>
       </c>
       <c r="B212" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C212" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D212" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="E212" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="213" spans="1:5">
@@ -5657,16 +5666,16 @@
         <v>93</v>
       </c>
       <c r="B213" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C213" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="D213" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E213" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="214" spans="1:5">
@@ -5674,16 +5683,16 @@
         <v>93</v>
       </c>
       <c r="B214" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C214" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="D214" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E214" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="215" spans="1:5">
@@ -5691,16 +5700,16 @@
         <v>93</v>
       </c>
       <c r="B215" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C215" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D215" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E215" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="216" spans="1:5">
@@ -5708,16 +5717,16 @@
         <v>93</v>
       </c>
       <c r="B216" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C216" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="D216" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="E216" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="217" spans="1:5">
@@ -5725,16 +5734,16 @@
         <v>94</v>
       </c>
       <c r="B217" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C217" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="D217" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="E217" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="218" spans="1:5">
@@ -5742,16 +5751,16 @@
         <v>94</v>
       </c>
       <c r="B218" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C218" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="D218" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E218" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="219" spans="1:5">
@@ -5759,16 +5768,16 @@
         <v>95</v>
       </c>
       <c r="B219" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C219" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="D219" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E219" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
     </row>
     <row r="220" spans="1:5">
@@ -5776,16 +5785,16 @@
         <v>95</v>
       </c>
       <c r="B220" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C220" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="D220" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E220" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="221" spans="1:5">
@@ -5793,16 +5802,16 @@
         <v>95</v>
       </c>
       <c r="B221" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C221" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="D221" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E221" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="222" spans="1:5">
@@ -5810,16 +5819,16 @@
         <v>95</v>
       </c>
       <c r="B222" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C222" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="D222" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="E222" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="223" spans="1:5">
@@ -5827,16 +5836,16 @@
         <v>96</v>
       </c>
       <c r="B223" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C223" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="D223" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E223" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="224" spans="1:5">
@@ -5844,16 +5853,16 @@
         <v>96</v>
       </c>
       <c r="B224" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C224" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D224" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E224" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="225" spans="1:5">
@@ -5861,16 +5870,16 @@
         <v>96</v>
       </c>
       <c r="B225" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C225" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="D225" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E225" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
     </row>
     <row r="226" spans="1:5">
@@ -5878,16 +5887,16 @@
         <v>97</v>
       </c>
       <c r="B226" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C226" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D226" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E226" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="227" spans="1:5">
@@ -5895,16 +5904,16 @@
         <v>97</v>
       </c>
       <c r="B227" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C227" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D227" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E227" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="228" spans="1:5">
@@ -5912,16 +5921,16 @@
         <v>98</v>
       </c>
       <c r="B228" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C228" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="D228" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="E228" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="229" spans="1:5">
@@ -5929,16 +5938,16 @@
         <v>99</v>
       </c>
       <c r="B229" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C229" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D229" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="E229" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="230" spans="1:5">
@@ -5946,16 +5955,16 @@
         <v>99</v>
       </c>
       <c r="B230" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C230" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="D230" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="E230" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="231" spans="1:5">
@@ -5963,16 +5972,16 @@
         <v>99</v>
       </c>
       <c r="B231" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C231" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="D231" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="E231" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="232" spans="1:5">
@@ -5980,16 +5989,16 @@
         <v>100</v>
       </c>
       <c r="B232" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C232" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="D232" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="E232" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="233" spans="1:5">
@@ -5997,16 +6006,16 @@
         <v>100</v>
       </c>
       <c r="B233" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C233" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D233" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="E233" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="234" spans="1:5">
@@ -6014,16 +6023,16 @@
         <v>101</v>
       </c>
       <c r="B234" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C234" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="D234" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E234" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="235" spans="1:5">
@@ -6031,16 +6040,16 @@
         <v>101</v>
       </c>
       <c r="B235" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C235" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="D235" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="E235" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="236" spans="1:5">
@@ -6048,16 +6057,16 @@
         <v>101</v>
       </c>
       <c r="B236" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C236" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="D236" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="E236" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="237" spans="1:5">
@@ -6065,16 +6074,16 @@
         <v>101</v>
       </c>
       <c r="B237" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C237" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="D237" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="E237" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="238" spans="1:5">
@@ -6082,16 +6091,16 @@
         <v>101</v>
       </c>
       <c r="B238" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C238" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D238" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="E238" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="239" spans="1:5">
@@ -6099,16 +6108,16 @@
         <v>101</v>
       </c>
       <c r="B239" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C239" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="D239" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="E239" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="240" spans="1:5">
@@ -6116,16 +6125,16 @@
         <v>102</v>
       </c>
       <c r="B240" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C240" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="D240" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E240" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="241" spans="1:5">
@@ -6133,16 +6142,16 @@
         <v>102</v>
       </c>
       <c r="B241" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C241" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="D241" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="E241" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="242" spans="1:5">
@@ -6150,16 +6159,16 @@
         <v>102</v>
       </c>
       <c r="B242" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C242" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D242" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="E242" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="243" spans="1:5">
@@ -6167,16 +6176,16 @@
         <v>102</v>
       </c>
       <c r="B243" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C243" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D243" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="E243" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="244" spans="1:5">
@@ -6184,16 +6193,16 @@
         <v>103</v>
       </c>
       <c r="B244" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C244" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="D244" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="E244" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="245" spans="1:5">
@@ -6201,16 +6210,16 @@
         <v>104</v>
       </c>
       <c r="B245" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C245" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D245" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E245" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="246" spans="1:5">
@@ -6218,16 +6227,16 @@
         <v>104</v>
       </c>
       <c r="B246" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C246" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="D246" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E246" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="247" spans="1:5">
@@ -6235,16 +6244,16 @@
         <v>104</v>
       </c>
       <c r="B247" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C247" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="D247" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E247" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="248" spans="1:5">
@@ -6252,16 +6261,16 @@
         <v>105</v>
       </c>
       <c r="B248" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C248" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D248" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E248" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="249" spans="1:5">
@@ -6269,16 +6278,16 @@
         <v>105</v>
       </c>
       <c r="B249" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C249" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="D249" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="E249" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="250" spans="1:5">
@@ -6286,16 +6295,16 @@
         <v>106</v>
       </c>
       <c r="B250" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C250" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="D250" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E250" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="251" spans="1:5">
@@ -6303,16 +6312,16 @@
         <v>106</v>
       </c>
       <c r="B251" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C251" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D251" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="E251" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="252" spans="1:5">
@@ -6320,16 +6329,16 @@
         <v>106</v>
       </c>
       <c r="B252" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C252" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D252" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E252" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="253" spans="1:5">
@@ -6337,16 +6346,16 @@
         <v>107</v>
       </c>
       <c r="B253" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C253" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="D253" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="E253" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="254" spans="1:5">
@@ -6354,16 +6363,16 @@
         <v>107</v>
       </c>
       <c r="B254" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C254" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="D254" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="E254" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="255" spans="1:5">
@@ -6371,16 +6380,16 @@
         <v>107</v>
       </c>
       <c r="B255" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C255" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="D255" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="E255" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="256" spans="1:5">
@@ -6388,16 +6397,16 @@
         <v>108</v>
       </c>
       <c r="B256" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C256" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="D256" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E256" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="257" spans="1:5">
@@ -6405,16 +6414,16 @@
         <v>108</v>
       </c>
       <c r="B257" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C257" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D257" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E257" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="258" spans="1:5">
@@ -6422,16 +6431,16 @@
         <v>108</v>
       </c>
       <c r="B258" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C258" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="D258" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E258" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="259" spans="1:5">
@@ -6439,16 +6448,16 @@
         <v>109</v>
       </c>
       <c r="B259" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C259" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D259" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E259" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="260" spans="1:5">
@@ -6456,16 +6465,16 @@
         <v>109</v>
       </c>
       <c r="B260" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C260" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="D260" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="E260" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="261" spans="1:5">
@@ -6473,16 +6482,16 @@
         <v>110</v>
       </c>
       <c r="B261" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C261" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D261" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="E261" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="262" spans="1:5">
@@ -6490,16 +6499,16 @@
         <v>110</v>
       </c>
       <c r="B262" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C262" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D262" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="E262" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="263" spans="1:5">
@@ -6507,16 +6516,16 @@
         <v>111</v>
       </c>
       <c r="B263" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C263" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="D263" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E263" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
     </row>
     <row r="264" spans="1:5">
@@ -6524,16 +6533,16 @@
         <v>111</v>
       </c>
       <c r="B264" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C264" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="D264" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="E264" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="265" spans="1:5">
@@ -6541,16 +6550,16 @@
         <v>111</v>
       </c>
       <c r="B265" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C265" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D265" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E265" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="266" spans="1:5">
@@ -6558,16 +6567,16 @@
         <v>111</v>
       </c>
       <c r="B266" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C266" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D266" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="E266" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="267" spans="1:5">
@@ -6575,16 +6584,16 @@
         <v>111</v>
       </c>
       <c r="B267" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C267" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="D267" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="E267" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="268" spans="1:5">
@@ -6592,16 +6601,16 @@
         <v>112</v>
       </c>
       <c r="B268" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C268" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D268" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E268" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="269" spans="1:5">
@@ -6609,16 +6618,16 @@
         <v>112</v>
       </c>
       <c r="B269" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C269" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D269" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E269" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
     </row>
     <row r="270" spans="1:5">
@@ -6626,16 +6635,16 @@
         <v>113</v>
       </c>
       <c r="B270" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C270" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="D270" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E270" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="271" spans="1:5">
@@ -6643,16 +6652,16 @@
         <v>113</v>
       </c>
       <c r="B271" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C271" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="D271" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="E271" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="272" spans="1:5">
@@ -6660,16 +6669,16 @@
         <v>113</v>
       </c>
       <c r="B272" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C272" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D272" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="E272" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="273" spans="1:5">
@@ -6677,16 +6686,16 @@
         <v>113</v>
       </c>
       <c r="B273" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C273" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="D273" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="E273" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="274" spans="1:5">
@@ -6694,16 +6703,16 @@
         <v>113</v>
       </c>
       <c r="B274" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C274" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="D274" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E274" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="275" spans="1:5">
@@ -6711,16 +6720,16 @@
         <v>113</v>
       </c>
       <c r="B275" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C275" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="D275" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="E275" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="276" spans="1:5">
@@ -6728,16 +6737,16 @@
         <v>113</v>
       </c>
       <c r="B276" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C276" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="D276" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E276" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="277" spans="1:5">
@@ -6745,16 +6754,16 @@
         <v>113</v>
       </c>
       <c r="B277" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C277" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="D277" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="E277" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="278" spans="1:5">
@@ -6762,16 +6771,16 @@
         <v>113</v>
       </c>
       <c r="B278" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C278" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="D278" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="E278" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="279" spans="1:5">
@@ -6779,16 +6788,16 @@
         <v>114</v>
       </c>
       <c r="B279" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C279" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="D279" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="E279" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="280" spans="1:5">
@@ -6796,16 +6805,16 @@
         <v>114</v>
       </c>
       <c r="B280" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C280" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="D280" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="E280" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="281" spans="1:5">
@@ -6813,16 +6822,16 @@
         <v>114</v>
       </c>
       <c r="B281" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C281" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="D281" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="E281" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="282" spans="1:5">
@@ -6830,16 +6839,16 @@
         <v>114</v>
       </c>
       <c r="B282" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C282" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="D282" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="E282" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="283" spans="1:5">
@@ -6847,16 +6856,16 @@
         <v>114</v>
       </c>
       <c r="B283" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C283" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="D283" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E283" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="284" spans="1:5">
@@ -6864,16 +6873,16 @@
         <v>114</v>
       </c>
       <c r="B284" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C284" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="D284" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E284" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="285" spans="1:5">
@@ -6881,16 +6890,16 @@
         <v>114</v>
       </c>
       <c r="B285" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C285" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="D285" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E285" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="286" spans="1:5">
@@ -6898,16 +6907,16 @@
         <v>114</v>
       </c>
       <c r="B286" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C286" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="D286" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="E286" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="287" spans="1:5">
@@ -6915,16 +6924,16 @@
         <v>115</v>
       </c>
       <c r="B287" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C287" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D287" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E287" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="288" spans="1:5">
@@ -6932,16 +6941,16 @@
         <v>115</v>
       </c>
       <c r="B288" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C288" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D288" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E288" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="289" spans="1:5">
@@ -6949,16 +6958,16 @@
         <v>115</v>
       </c>
       <c r="B289" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C289" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="D289" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="E289" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="290" spans="1:5">
@@ -6966,16 +6975,16 @@
         <v>115</v>
       </c>
       <c r="B290" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C290" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="D290" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E290" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="291" spans="1:5">
@@ -6983,16 +6992,16 @@
         <v>115</v>
       </c>
       <c r="B291" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C291" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="D291" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E291" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="292" spans="1:5">
@@ -7000,16 +7009,16 @@
         <v>115</v>
       </c>
       <c r="B292" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C292" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="D292" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="E292" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="293" spans="1:5">
@@ -7017,16 +7026,16 @@
         <v>115</v>
       </c>
       <c r="B293" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C293" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="D293" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E293" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="294" spans="1:5">
@@ -7034,16 +7043,16 @@
         <v>116</v>
       </c>
       <c r="B294" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C294" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="D294" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="E294" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="295" spans="1:5">
@@ -7051,16 +7060,16 @@
         <v>116</v>
       </c>
       <c r="B295" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C295" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="D295" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="E295" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="296" spans="1:5">
@@ -7068,16 +7077,16 @@
         <v>116</v>
       </c>
       <c r="B296" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C296" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="D296" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E296" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="297" spans="1:5">
@@ -7085,16 +7094,16 @@
         <v>116</v>
       </c>
       <c r="B297" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C297" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="D297" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="E297" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="298" spans="1:5">
@@ -7102,16 +7111,16 @@
         <v>116</v>
       </c>
       <c r="B298" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C298" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="D298" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="E298" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="299" spans="1:5">
@@ -7119,16 +7128,16 @@
         <v>117</v>
       </c>
       <c r="B299" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C299" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="D299" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E299" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="300" spans="1:5">
@@ -7136,16 +7145,16 @@
         <v>117</v>
       </c>
       <c r="B300" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C300" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="D300" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="E300" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="301" spans="1:5">
@@ -7153,16 +7162,16 @@
         <v>117</v>
       </c>
       <c r="B301" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C301" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="D301" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="E301" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="302" spans="1:5">
@@ -7170,16 +7179,16 @@
         <v>118</v>
       </c>
       <c r="B302" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C302" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D302" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E302" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
     </row>
     <row r="303" spans="1:5">
@@ -7187,16 +7196,16 @@
         <v>119</v>
       </c>
       <c r="B303" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C303" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D303" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E303" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="304" spans="1:5">
@@ -7204,16 +7213,16 @@
         <v>120</v>
       </c>
       <c r="B304" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C304" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D304" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E304" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="305" spans="1:5">
@@ -7221,16 +7230,16 @@
         <v>120</v>
       </c>
       <c r="B305" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C305" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D305" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E305" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="306" spans="1:5">
@@ -7238,16 +7247,16 @@
         <v>121</v>
       </c>
       <c r="B306" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C306" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D306" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="E306" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="307" spans="1:5">
@@ -7255,16 +7264,16 @@
         <v>122</v>
       </c>
       <c r="B307" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C307" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D307" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="E307" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="308" spans="1:5">
@@ -7272,16 +7281,16 @@
         <v>123</v>
       </c>
       <c r="B308" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="C308" t="s">
-        <v>233</v>
+        <v>269</v>
       </c>
       <c r="D308" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E308" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="309" spans="1:5">
@@ -7289,16 +7298,16 @@
         <v>124</v>
       </c>
       <c r="B309" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C309" t="s">
-        <v>173</v>
+        <v>234</v>
       </c>
       <c r="D309" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E309" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="310" spans="1:5">
@@ -7306,16 +7315,16 @@
         <v>125</v>
       </c>
       <c r="B310" t="s">
-        <v>166</v>
+        <v>268</v>
       </c>
       <c r="C310" t="s">
-        <v>307</v>
+        <v>174</v>
       </c>
       <c r="D310" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E310" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
     </row>
     <row r="311" spans="1:5">
@@ -7323,16 +7332,16 @@
         <v>126</v>
       </c>
       <c r="B311" t="s">
-        <v>267</v>
+        <v>167</v>
       </c>
       <c r="C311" t="s">
-        <v>391</v>
+        <v>309</v>
       </c>
       <c r="D311" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E311" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
     </row>
     <row r="312" spans="1:5">
@@ -7340,16 +7349,16 @@
         <v>127</v>
       </c>
       <c r="B312" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="C312" t="s">
-        <v>233</v>
+        <v>393</v>
       </c>
       <c r="D312" t="s">
-        <v>424</v>
+        <v>265</v>
       </c>
       <c r="E312" t="s">
-        <v>487</v>
+        <v>559</v>
       </c>
     </row>
     <row r="313" spans="1:5">
@@ -7360,30 +7369,47 @@
         <v>264</v>
       </c>
       <c r="C313" t="s">
-        <v>390</v>
+        <v>234</v>
       </c>
       <c r="D313" t="s">
-        <v>264</v>
+        <v>426</v>
       </c>
       <c r="E313" t="s">
-        <v>519</v>
+        <v>489</v>
       </c>
     </row>
     <row r="314" spans="1:5">
       <c r="A314" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B314" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="C314" t="s">
         <v>392</v>
       </c>
       <c r="D314" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E314" t="s">
-        <v>486</v>
+        <v>521</v>
+      </c>
+    </row>
+    <row r="315" spans="1:5">
+      <c r="A315" t="s">
+        <v>129</v>
+      </c>
+      <c r="B315" t="s">
+        <v>270</v>
+      </c>
+      <c r="C315" t="s">
+        <v>394</v>
+      </c>
+      <c r="D315" t="s">
+        <v>265</v>
+      </c>
+      <c r="E315" t="s">
+        <v>488</v>
       </c>
     </row>
   </sheetData>
